--- a/database/event/5257/event_5257_evp_summary.xlsx
+++ b/database/event/5257/event_5257_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>1.1639</v>
       </c>
       <c r="D2" t="n">
-        <v>2.1285</v>
+        <v>2.0707</v>
       </c>
       <c r="E2" t="n">
         <v>6.3118</v>
@@ -548,7 +548,7 @@
         <v>0.7968</v>
       </c>
       <c r="D3" t="n">
-        <v>1.3241</v>
+        <v>1.2775</v>
       </c>
       <c r="E3" t="n">
         <v>4.3207</v>
@@ -594,7 +594,7 @@
         <v>0.7818000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2913</v>
+        <v>1.2451</v>
       </c>
       <c r="E4" t="n">
         <v>4.2395</v>
@@ -640,7 +640,7 @@
         <v>0.7628</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2497</v>
+        <v>1.2041</v>
       </c>
       <c r="E5" t="n">
         <v>4.1366</v>
@@ -686,7 +686,7 @@
         <v>0.7569</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2367</v>
+        <v>1.1913</v>
       </c>
       <c r="E6" t="n">
         <v>4.1044</v>
@@ -732,7 +732,7 @@
         <v>0.744</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2085</v>
+        <v>1.1634</v>
       </c>
       <c r="E7" t="n">
         <v>4.0345</v>
@@ -778,7 +778,7 @@
         <v>0.598</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8887</v>
+        <v>0.8481</v>
       </c>
       <c r="E8" t="n">
         <v>3.2429</v>
@@ -824,7 +824,7 @@
         <v>0.5703</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8279</v>
+        <v>0.7881</v>
       </c>
       <c r="E9" t="n">
         <v>3.0924</v>
@@ -870,7 +870,7 @@
         <v>0.5605</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8066</v>
+        <v>0.7671</v>
       </c>
       <c r="E10" t="n">
         <v>3.0397</v>
@@ -916,7 +916,7 @@
         <v>0.5548999999999999</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7942</v>
+        <v>0.7548</v>
       </c>
       <c r="E11" t="n">
         <v>3.0089</v>
@@ -962,7 +962,7 @@
         <v>0.4667</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6011</v>
+        <v>0.5644</v>
       </c>
       <c r="E12" t="n">
         <v>2.531</v>
@@ -1008,7 +1008,7 @@
         <v>0.4289</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5182</v>
+        <v>0.4826</v>
       </c>
       <c r="E13" t="n">
         <v>2.3257</v>
@@ -1054,7 +1054,7 @@
         <v>0.4062</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4686</v>
+        <v>0.4337</v>
       </c>
       <c r="E14" t="n">
         <v>2.2029</v>
@@ -1100,7 +1100,7 @@
         <v>0.3239</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2881</v>
+        <v>0.2558</v>
       </c>
       <c r="E15" t="n">
         <v>1.7562</v>
@@ -1146,7 +1146,7 @@
         <v>0.2947</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2242</v>
+        <v>0.1927</v>
       </c>
       <c r="E16" t="n">
         <v>1.598</v>
@@ -1192,7 +1192,7 @@
         <v>0.2892</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2121</v>
+        <v>0.1808</v>
       </c>
       <c r="E17" t="n">
         <v>1.5681</v>
@@ -1238,7 +1238,7 @@
         <v>0.2358</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0951</v>
+        <v>0.0654</v>
       </c>
       <c r="E18" t="n">
         <v>1.2785</v>
@@ -1284,7 +1284,7 @@
         <v>0.2212</v>
       </c>
       <c r="D19" t="n">
-        <v>0.06320000000000001</v>
+        <v>0.034</v>
       </c>
       <c r="E19" t="n">
         <v>1.1996</v>
@@ -1330,7 +1330,7 @@
         <v>0.2045</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0266</v>
+        <v>-0.0021</v>
       </c>
       <c r="E20" t="n">
         <v>1.109</v>
@@ -1376,7 +1376,7 @@
         <v>0.1582</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.07489999999999999</v>
+        <v>-0.1022</v>
       </c>
       <c r="E21" t="n">
         <v>0.8577</v>
@@ -1422,7 +1422,7 @@
         <v>0.1481</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.097</v>
+        <v>-0.124</v>
       </c>
       <c r="E22" t="n">
         <v>0.8028999999999999</v>
@@ -1468,7 +1468,7 @@
         <v>0.1478</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.09760000000000001</v>
+        <v>-0.1246</v>
       </c>
       <c r="E23" t="n">
         <v>0.8014</v>
@@ -1514,7 +1514,7 @@
         <v>0.08550000000000001</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2342</v>
+        <v>-0.2593</v>
       </c>
       <c r="E24" t="n">
         <v>0.4634</v>
@@ -1560,7 +1560,7 @@
         <v>0.0517</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3081</v>
+        <v>-0.3322</v>
       </c>
       <c r="E25" t="n">
         <v>0.2804</v>
@@ -1606,7 +1606,7 @@
         <v>0.0411</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3314</v>
+        <v>-0.3552</v>
       </c>
       <c r="E26" t="n">
         <v>0.2227</v>
@@ -1652,7 +1652,7 @@
         <v>0.0403</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.3331</v>
+        <v>-0.3569</v>
       </c>
       <c r="E27" t="n">
         <v>0.2185</v>
@@ -1698,7 +1698,7 @@
         <v>0.0157</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.3869</v>
+        <v>-0.41</v>
       </c>
       <c r="E28" t="n">
         <v>0.0852</v>
@@ -1744,7 +1744,7 @@
         <v>-0.0036</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.4292</v>
+        <v>-0.4516</v>
       </c>
       <c r="E29" t="n">
         <v>-0.0193</v>
@@ -1790,7 +1790,7 @@
         <v>-0.0231</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.472</v>
+        <v>-0.4938</v>
       </c>
       <c r="E30" t="n">
         <v>-0.1253</v>
@@ -1836,7 +1836,7 @@
         <v>-0.1002</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6408</v>
+        <v>-0.6603</v>
       </c>
       <c r="E31" t="n">
         <v>-0.5432</v>
@@ -1882,7 +1882,7 @@
         <v>-0.1581</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7677</v>
+        <v>-0.7854</v>
       </c>
       <c r="E32" t="n">
         <v>-0.8572</v>
@@ -1928,7 +1928,7 @@
         <v>-0.1671</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7873</v>
+        <v>-0.8048</v>
       </c>
       <c r="E33" t="n">
         <v>-0.9059</v>
@@ -1974,7 +1974,7 @@
         <v>-0.1715</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.7971</v>
+        <v>-0.8144</v>
       </c>
       <c r="E34" t="n">
         <v>-0.93</v>
@@ -2020,7 +2020,7 @@
         <v>-0.2017</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8632</v>
+        <v>-0.8796</v>
       </c>
       <c r="E35" t="n">
         <v>-1.0936</v>
@@ -2066,7 +2066,7 @@
         <v>-0.2507</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9706</v>
+        <v>-0.9855</v>
       </c>
       <c r="E36" t="n">
         <v>-1.3595</v>
@@ -2112,7 +2112,7 @@
         <v>-0.3121</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.105</v>
+        <v>-1.1181</v>
       </c>
       <c r="E37" t="n">
         <v>-1.6923</v>
@@ -2158,7 +2158,7 @@
         <v>-0.3556</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.2005</v>
+        <v>-1.2123</v>
       </c>
       <c r="E38" t="n">
         <v>-1.9286</v>
@@ -2204,7 +2204,7 @@
         <v>-0.3622</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.2149</v>
+        <v>-1.2264</v>
       </c>
       <c r="E39" t="n">
         <v>-1.9642</v>
@@ -2250,7 +2250,7 @@
         <v>-0.4093</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.3179</v>
+        <v>-1.3281</v>
       </c>
       <c r="E40" t="n">
         <v>-2.2193</v>
@@ -2296,7 +2296,7 @@
         <v>-0.4645</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.4389</v>
+        <v>-1.4474</v>
       </c>
       <c r="E41" t="n">
         <v>-2.5187</v>

--- a/database/event/5257/event_5257_evp_summary.xlsx
+++ b/database/event/5257/event_5257_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.3118</v>
+        <v>5.5298</v>
       </c>
       <c r="C2" t="n">
-        <v>1.1639</v>
+        <v>1.0197</v>
       </c>
       <c r="D2" t="n">
-        <v>2.0707</v>
+        <v>1.8584</v>
       </c>
       <c r="E2" t="n">
-        <v>6.3118</v>
+        <v>5.5298</v>
       </c>
       <c r="F2" t="n">
-        <v>3.3169</v>
+        <v>2.9655</v>
       </c>
       <c r="G2" t="n">
-        <v>2.9949</v>
+        <v>2.5643</v>
       </c>
       <c r="H2" t="n">
-        <v>3.3169</v>
+        <v>4.9624</v>
       </c>
       <c r="I2" t="n">
-        <v>2.6885</v>
+        <v>2.5802</v>
       </c>
       <c r="J2" t="n">
-        <v>2.9949</v>
+        <v>2.5643</v>
       </c>
       <c r="K2" t="n">
         <v>144</v>
@@ -529,7 +529,7 @@
         <v>136</v>
       </c>
       <c r="M2" t="n">
-        <v>5.6834</v>
+        <v>5.1445</v>
       </c>
       <c r="N2" t="n">
         <v>280</v>
@@ -538,35 +538,35 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>cadiaN</t>
+          <t>niko</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.3207</v>
+        <v>4.3524</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7968</v>
+        <v>0.8026</v>
       </c>
       <c r="D3" t="n">
-        <v>1.2775</v>
+        <v>1.3269</v>
       </c>
       <c r="E3" t="n">
-        <v>4.3207</v>
+        <v>4.3524</v>
       </c>
       <c r="F3" t="n">
-        <v>4.0602</v>
+        <v>2.3912</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2605</v>
+        <v>1.9612</v>
       </c>
       <c r="H3" t="n">
-        <v>4.0602</v>
+        <v>2.9389</v>
       </c>
       <c r="I3" t="n">
-        <v>3.2909</v>
+        <v>1.5281</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2605</v>
+        <v>1.9612</v>
       </c>
       <c r="K3" t="n">
         <v>154</v>
@@ -575,7 +575,7 @@
         <v>132</v>
       </c>
       <c r="M3" t="n">
-        <v>3.5514</v>
+        <v>3.4893</v>
       </c>
       <c r="N3" t="n">
         <v>286</v>
@@ -584,139 +584,139 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>niko</t>
+          <t>syrsoN</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.2395</v>
+        <v>4.214</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7818000000000001</v>
+        <v>0.7771</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2451</v>
+        <v>1.2644</v>
       </c>
       <c r="E4" t="n">
-        <v>4.2395</v>
+        <v>4.214</v>
       </c>
       <c r="F4" t="n">
-        <v>1.7437</v>
+        <v>2.8609</v>
       </c>
       <c r="G4" t="n">
-        <v>2.4958</v>
+        <v>1.3531</v>
       </c>
       <c r="H4" t="n">
-        <v>1.7437</v>
+        <v>4.5939</v>
       </c>
       <c r="I4" t="n">
-        <v>1.4133</v>
+        <v>2.3886</v>
       </c>
       <c r="J4" t="n">
-        <v>2.4958</v>
+        <v>1.3531</v>
       </c>
       <c r="K4" t="n">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="L4" t="n">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="M4" t="n">
-        <v>3.9091</v>
+        <v>3.7417</v>
       </c>
       <c r="N4" t="n">
-        <v>286</v>
+        <v>280</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>syrsoN</t>
+          <t>blameF</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.1366</v>
+        <v>4.1988</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7628</v>
+        <v>0.7743</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2041</v>
+        <v>1.2575</v>
       </c>
       <c r="E5" t="n">
-        <v>4.1366</v>
+        <v>4.1988</v>
       </c>
       <c r="F5" t="n">
-        <v>2.5993</v>
+        <v>2.8976</v>
       </c>
       <c r="G5" t="n">
-        <v>1.5373</v>
+        <v>1.3012</v>
       </c>
       <c r="H5" t="n">
-        <v>2.5993</v>
+        <v>4.7231</v>
       </c>
       <c r="I5" t="n">
-        <v>2.1068</v>
+        <v>2.4558</v>
       </c>
       <c r="J5" t="n">
-        <v>1.5373</v>
+        <v>1.3012</v>
       </c>
       <c r="K5" t="n">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="L5" t="n">
-        <v>136</v>
+        <v>77</v>
       </c>
       <c r="M5" t="n">
-        <v>3.6441</v>
+        <v>3.757</v>
       </c>
       <c r="N5" t="n">
-        <v>280</v>
+        <v>223</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>blameF</t>
+          <t>cadiaN</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.1044</v>
+        <v>3.8982</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7569</v>
+        <v>0.7188</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1913</v>
+        <v>1.1218</v>
       </c>
       <c r="E6" t="n">
-        <v>4.1044</v>
+        <v>3.8982</v>
       </c>
       <c r="F6" t="n">
-        <v>2.7778</v>
+        <v>3.5946</v>
       </c>
       <c r="G6" t="n">
-        <v>1.3266</v>
+        <v>0.3036</v>
       </c>
       <c r="H6" t="n">
-        <v>2.7778</v>
+        <v>7.1789</v>
       </c>
       <c r="I6" t="n">
-        <v>2.2515</v>
+        <v>3.7327</v>
       </c>
       <c r="J6" t="n">
-        <v>1.3266</v>
+        <v>0.3036</v>
       </c>
       <c r="K6" t="n">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="L6" t="n">
-        <v>77</v>
+        <v>132</v>
       </c>
       <c r="M6" t="n">
-        <v>3.5781</v>
+        <v>4.0363</v>
       </c>
       <c r="N6" t="n">
-        <v>223</v>
+        <v>286</v>
       </c>
     </row>
     <row r="7">
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.0345</v>
+        <v>3.6528</v>
       </c>
       <c r="C7" t="n">
-        <v>0.744</v>
+        <v>0.6736</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1634</v>
+        <v>1.011</v>
       </c>
       <c r="E7" t="n">
-        <v>4.0345</v>
+        <v>3.6528</v>
       </c>
       <c r="F7" t="n">
-        <v>3.2631</v>
+        <v>3.128</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7714</v>
+        <v>0.5248</v>
       </c>
       <c r="H7" t="n">
-        <v>3.2631</v>
+        <v>5.5347</v>
       </c>
       <c r="I7" t="n">
-        <v>2.6448</v>
+        <v>2.8778</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7714</v>
+        <v>0.5248</v>
       </c>
       <c r="K7" t="n">
         <v>197</v>
@@ -759,7 +759,7 @@
         <v>81</v>
       </c>
       <c r="M7" t="n">
-        <v>3.4162</v>
+        <v>3.4026</v>
       </c>
       <c r="N7" t="n">
         <v>278</v>
@@ -768,35 +768,35 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>poizon</t>
+          <t>oBo</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.2429</v>
+        <v>3.236</v>
       </c>
       <c r="C8" t="n">
-        <v>0.598</v>
+        <v>0.5967</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8481</v>
+        <v>0.8229</v>
       </c>
       <c r="E8" t="n">
-        <v>3.2429</v>
+        <v>3.236</v>
       </c>
       <c r="F8" t="n">
-        <v>3.5321</v>
+        <v>3.0826</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.2892</v>
+        <v>0.1534</v>
       </c>
       <c r="H8" t="n">
-        <v>3.5321</v>
+        <v>5.3749</v>
       </c>
       <c r="I8" t="n">
-        <v>2.8629</v>
+        <v>2.7947</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.2892</v>
+        <v>0.1534</v>
       </c>
       <c r="K8" t="n">
         <v>146</v>
@@ -805,7 +805,7 @@
         <v>77</v>
       </c>
       <c r="M8" t="n">
-        <v>2.5737</v>
+        <v>2.9481</v>
       </c>
       <c r="N8" t="n">
         <v>223</v>
@@ -814,814 +814,814 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>k1to</t>
+          <t>mantuu</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.0924</v>
+        <v>3.1996</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5703</v>
+        <v>0.59</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7881</v>
+        <v>0.8064</v>
       </c>
       <c r="E9" t="n">
-        <v>3.0924</v>
+        <v>3.1996</v>
       </c>
       <c r="F9" t="n">
-        <v>3.3496</v>
+        <v>2.2301</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.2572</v>
+        <v>0.9695</v>
       </c>
       <c r="H9" t="n">
-        <v>3.3496</v>
+        <v>2.3712</v>
       </c>
       <c r="I9" t="n">
-        <v>2.715</v>
+        <v>1.2329</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.2572</v>
+        <v>0.9695</v>
       </c>
       <c r="K9" t="n">
-        <v>144</v>
+        <v>197</v>
       </c>
       <c r="L9" t="n">
-        <v>136</v>
+        <v>81</v>
       </c>
       <c r="M9" t="n">
-        <v>2.4578</v>
+        <v>2.2024</v>
       </c>
       <c r="N9" t="n">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>valde</t>
+          <t>stavn</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.0397</v>
+        <v>3.1146</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5605</v>
+        <v>0.5743</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7671</v>
+        <v>0.7681</v>
       </c>
       <c r="E10" t="n">
-        <v>3.0397</v>
+        <v>3.1146</v>
       </c>
       <c r="F10" t="n">
-        <v>3.5058</v>
+        <v>2.5377</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.4661</v>
+        <v>0.5769</v>
       </c>
       <c r="H10" t="n">
-        <v>3.5058</v>
+        <v>3.4551</v>
       </c>
       <c r="I10" t="n">
-        <v>2.8415</v>
+        <v>1.7965</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.4661</v>
+        <v>0.5769</v>
       </c>
       <c r="K10" t="n">
-        <v>197</v>
+        <v>154</v>
       </c>
       <c r="L10" t="n">
-        <v>81</v>
+        <v>132</v>
       </c>
       <c r="M10" t="n">
-        <v>2.3754</v>
+        <v>2.3734</v>
       </c>
       <c r="N10" t="n">
-        <v>278</v>
+        <v>286</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>oBo</t>
+          <t>k1to</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.0089</v>
+        <v>3.0594</v>
       </c>
       <c r="C11" t="n">
-        <v>0.5548999999999999</v>
+        <v>0.5642</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7548</v>
+        <v>0.7432</v>
       </c>
       <c r="E11" t="n">
-        <v>3.0089</v>
+        <v>3.0594</v>
       </c>
       <c r="F11" t="n">
-        <v>2.914</v>
+        <v>3.1247</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0949</v>
+        <v>-0.0653</v>
       </c>
       <c r="H11" t="n">
-        <v>2.914</v>
+        <v>5.5232</v>
       </c>
       <c r="I11" t="n">
-        <v>2.3619</v>
+        <v>2.8718</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0949</v>
+        <v>-0.0653</v>
       </c>
       <c r="K11" t="n">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="L11" t="n">
-        <v>77</v>
+        <v>136</v>
       </c>
       <c r="M11" t="n">
-        <v>2.4568</v>
+        <v>2.8065</v>
       </c>
       <c r="N11" t="n">
-        <v>223</v>
+        <v>280</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>stavn</t>
+          <t>poizon</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.531</v>
+        <v>3.0318</v>
       </c>
       <c r="C12" t="n">
-        <v>0.4667</v>
+        <v>0.5591</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5644</v>
+        <v>0.7307</v>
       </c>
       <c r="E12" t="n">
-        <v>2.531</v>
+        <v>3.0318</v>
       </c>
       <c r="F12" t="n">
-        <v>2.0615</v>
+        <v>3.1307</v>
       </c>
       <c r="G12" t="n">
-        <v>0.4695</v>
+        <v>-0.0989</v>
       </c>
       <c r="H12" t="n">
-        <v>2.0615</v>
+        <v>5.5443</v>
       </c>
       <c r="I12" t="n">
-        <v>1.6709</v>
+        <v>2.8828</v>
       </c>
       <c r="J12" t="n">
-        <v>0.4695</v>
+        <v>-0.0989</v>
       </c>
       <c r="K12" t="n">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="L12" t="n">
-        <v>132</v>
+        <v>77</v>
       </c>
       <c r="M12" t="n">
-        <v>2.1404</v>
+        <v>2.7839</v>
       </c>
       <c r="N12" t="n">
-        <v>286</v>
+        <v>223</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>tabseN</t>
+          <t>valde</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.3257</v>
+        <v>2.8627</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4289</v>
+        <v>0.5279</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4826</v>
+        <v>0.6544</v>
       </c>
       <c r="E13" t="n">
-        <v>2.3257</v>
+        <v>2.8627</v>
       </c>
       <c r="F13" t="n">
-        <v>2.6333</v>
+        <v>3.1058</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.3076</v>
+        <v>-0.2431</v>
       </c>
       <c r="H13" t="n">
-        <v>2.6333</v>
+        <v>5.4566</v>
       </c>
       <c r="I13" t="n">
-        <v>2.1344</v>
+        <v>2.8372</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.3076</v>
+        <v>-0.2431</v>
       </c>
       <c r="K13" t="n">
-        <v>144</v>
+        <v>197</v>
       </c>
       <c r="L13" t="n">
-        <v>136</v>
+        <v>81</v>
       </c>
       <c r="M13" t="n">
-        <v>1.8268</v>
+        <v>2.5941</v>
       </c>
       <c r="N13" t="n">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>mantuu</t>
+          <t>tabseN</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.2029</v>
+        <v>2.5854</v>
       </c>
       <c r="C14" t="n">
-        <v>0.4062</v>
+        <v>0.4768</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4337</v>
+        <v>0.5292</v>
       </c>
       <c r="E14" t="n">
-        <v>2.2029</v>
+        <v>2.5854</v>
       </c>
       <c r="F14" t="n">
-        <v>1.1179</v>
+        <v>2.8464</v>
       </c>
       <c r="G14" t="n">
-        <v>1.085</v>
+        <v>-0.261</v>
       </c>
       <c r="H14" t="n">
-        <v>1.1179</v>
+        <v>4.5427</v>
       </c>
       <c r="I14" t="n">
-        <v>0.9061</v>
+        <v>2.362</v>
       </c>
       <c r="J14" t="n">
-        <v>1.085</v>
+        <v>-0.261</v>
       </c>
       <c r="K14" t="n">
-        <v>197</v>
+        <v>144</v>
       </c>
       <c r="L14" t="n">
-        <v>81</v>
+        <v>136</v>
       </c>
       <c r="M14" t="n">
-        <v>1.9911</v>
+        <v>2.101</v>
       </c>
       <c r="N14" t="n">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>acoR</t>
+          <t>Aleksib</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.7562</v>
+        <v>2.0383</v>
       </c>
       <c r="C15" t="n">
-        <v>0.3239</v>
+        <v>0.3759</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2558</v>
+        <v>0.2822</v>
       </c>
       <c r="E15" t="n">
-        <v>1.7562</v>
+        <v>2.0383</v>
       </c>
       <c r="F15" t="n">
-        <v>1.7562</v>
+        <v>2.9507</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>-0.9124</v>
       </c>
       <c r="H15" t="n">
-        <v>1.7562</v>
+        <v>4.9102</v>
       </c>
       <c r="I15" t="n">
-        <v>1.7562</v>
+        <v>2.5531</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>-0.9124</v>
       </c>
       <c r="K15" t="n">
-        <v>119</v>
+        <v>197</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="M15" t="n">
-        <v>1.7562</v>
+        <v>1.6407</v>
       </c>
       <c r="N15" t="n">
-        <v>119</v>
+        <v>278</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>mir</t>
+          <t>FL1T</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.598</v>
+        <v>1.7471</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2947</v>
+        <v>0.3222</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1927</v>
+        <v>0.1507</v>
       </c>
       <c r="E16" t="n">
-        <v>1.598</v>
+        <v>1.7471</v>
       </c>
       <c r="F16" t="n">
-        <v>1.598</v>
+        <v>1.7471</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>1.598</v>
+        <v>1.7471</v>
       </c>
       <c r="I16" t="n">
-        <v>1.598</v>
+        <v>1.7471</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>157</v>
+        <v>218</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1.598</v>
+        <v>1.7471</v>
       </c>
       <c r="N16" t="n">
-        <v>157</v>
+        <v>218</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Aleksib</t>
+          <t>acoR</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.5681</v>
+        <v>1.691</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2892</v>
+        <v>0.3118</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1808</v>
+        <v>0.1254</v>
       </c>
       <c r="E17" t="n">
-        <v>1.5681</v>
+        <v>1.691</v>
       </c>
       <c r="F17" t="n">
-        <v>2.5681</v>
+        <v>1.691</v>
       </c>
       <c r="G17" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>2.5681</v>
+        <v>1.691</v>
       </c>
       <c r="I17" t="n">
-        <v>2.0815</v>
+        <v>1.691</v>
       </c>
       <c r="J17" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>197</v>
+        <v>119</v>
       </c>
       <c r="L17" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.0815</v>
+        <v>1.691</v>
       </c>
       <c r="N17" t="n">
-        <v>278</v>
+        <v>119</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CRUC1AL</t>
+          <t>mir</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.2785</v>
+        <v>1.6313</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2358</v>
+        <v>0.3008</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0654</v>
+        <v>0.0984</v>
       </c>
       <c r="E18" t="n">
-        <v>1.2785</v>
+        <v>1.6313</v>
       </c>
       <c r="F18" t="n">
-        <v>1.2785</v>
+        <v>1.6313</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1.2785</v>
+        <v>1.6313</v>
       </c>
       <c r="I18" t="n">
-        <v>1.2785</v>
+        <v>1.6313</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>207</v>
+        <v>157</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1.2785</v>
+        <v>1.6313</v>
       </c>
       <c r="N18" t="n">
-        <v>207</v>
+        <v>157</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>FL1T</t>
+          <t>CRUC1AL</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.1996</v>
+        <v>1.6269</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2212</v>
+        <v>0.3</v>
       </c>
       <c r="D19" t="n">
-        <v>0.034</v>
+        <v>0.0965</v>
       </c>
       <c r="E19" t="n">
-        <v>1.1996</v>
+        <v>1.6269</v>
       </c>
       <c r="F19" t="n">
-        <v>1.1996</v>
+        <v>1.6269</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.1996</v>
+        <v>1.6269</v>
       </c>
       <c r="I19" t="n">
-        <v>1.1996</v>
+        <v>1.6269</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.1996</v>
+        <v>1.6269</v>
       </c>
       <c r="N19" t="n">
-        <v>218</v>
+        <v>207</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>xsepower</t>
+          <t>k0nfig</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.109</v>
+        <v>1.6083</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2045</v>
+        <v>0.2966</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0021</v>
+        <v>0.0881</v>
       </c>
       <c r="E20" t="n">
-        <v>1.109</v>
+        <v>1.6083</v>
       </c>
       <c r="F20" t="n">
-        <v>1.109</v>
+        <v>1.3057</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>0.3026</v>
       </c>
       <c r="H20" t="n">
-        <v>1.109</v>
+        <v>1.3057</v>
       </c>
       <c r="I20" t="n">
-        <v>1.109</v>
+        <v>0.6788999999999999</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>0.3026</v>
       </c>
       <c r="K20" t="n">
-        <v>218</v>
+        <v>146</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="M20" t="n">
-        <v>1.109</v>
+        <v>0.9814999999999999</v>
       </c>
       <c r="N20" t="n">
-        <v>218</v>
+        <v>223</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>k0nfig</t>
+          <t>xsepower</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.8577</v>
+        <v>1.3419</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1582</v>
+        <v>0.2475</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1022</v>
+        <v>-0.0322</v>
       </c>
       <c r="E21" t="n">
-        <v>0.8577</v>
+        <v>1.3419</v>
       </c>
       <c r="F21" t="n">
-        <v>0.444</v>
+        <v>1.3419</v>
       </c>
       <c r="G21" t="n">
-        <v>0.4137</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.444</v>
+        <v>1.3419</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3599</v>
+        <v>1.3419</v>
       </c>
       <c r="J21" t="n">
-        <v>0.4137</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>146</v>
+        <v>218</v>
       </c>
       <c r="L21" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.7736000000000001</v>
+        <v>1.3419</v>
       </c>
       <c r="N21" t="n">
-        <v>223</v>
+        <v>218</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>robiin</t>
+          <t>almazer</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.8028999999999999</v>
+        <v>1.3184</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1481</v>
+        <v>0.2431</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.124</v>
+        <v>-0.0428</v>
       </c>
       <c r="E22" t="n">
-        <v>0.8028999999999999</v>
+        <v>1.3184</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8028999999999999</v>
+        <v>1.3184</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.8028999999999999</v>
+        <v>1.3184</v>
       </c>
       <c r="I22" t="n">
-        <v>0.8028999999999999</v>
+        <v>1.3184</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>207</v>
+        <v>218</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.8028999999999999</v>
+        <v>1.3184</v>
       </c>
       <c r="N22" t="n">
-        <v>207</v>
+        <v>218</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>innocent</t>
+          <t>robiin</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.8014</v>
+        <v>1.3101</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1478</v>
+        <v>0.2416</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1246</v>
+        <v>-0.0466</v>
       </c>
       <c r="E23" t="n">
-        <v>0.8014</v>
+        <v>1.3101</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8014</v>
+        <v>1.3101</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.8014</v>
+        <v>1.3101</v>
       </c>
       <c r="I23" t="n">
-        <v>0.8014</v>
+        <v>1.3101</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>119</v>
+        <v>207</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.8014</v>
+        <v>1.3101</v>
       </c>
       <c r="N23" t="n">
-        <v>119</v>
+        <v>207</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>facecrack</t>
+          <t>TeSeS</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.4634</v>
+        <v>1.2454</v>
       </c>
       <c r="C24" t="n">
-        <v>0.08550000000000001</v>
+        <v>0.2297</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2593</v>
+        <v>-0.07580000000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>0.4634</v>
+        <v>1.2454</v>
       </c>
       <c r="F24" t="n">
-        <v>0.4634</v>
+        <v>2.4243</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>-1.1789</v>
       </c>
       <c r="H24" t="n">
-        <v>0.4634</v>
+        <v>3.0555</v>
       </c>
       <c r="I24" t="n">
-        <v>0.4634</v>
+        <v>1.5887</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>-1.1789</v>
       </c>
       <c r="K24" t="n">
-        <v>218</v>
+        <v>154</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="M24" t="n">
-        <v>0.4634</v>
+        <v>0.4097999999999999</v>
       </c>
       <c r="N24" t="n">
-        <v>218</v>
+        <v>286</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>TeSeS</t>
+          <t>innocent</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.2804</v>
+        <v>1.1252</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0517</v>
+        <v>0.2075</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3322</v>
+        <v>-0.13</v>
       </c>
       <c r="E25" t="n">
-        <v>0.2804</v>
+        <v>1.1252</v>
       </c>
       <c r="F25" t="n">
-        <v>1.7511</v>
+        <v>1.1252</v>
       </c>
       <c r="G25" t="n">
-        <v>-1.4707</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1.7511</v>
+        <v>1.1252</v>
       </c>
       <c r="I25" t="n">
-        <v>1.4193</v>
+        <v>1.1252</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.4707</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>154</v>
+        <v>119</v>
       </c>
       <c r="L25" t="n">
-        <v>132</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.05139999999999989</v>
+        <v>1.1252</v>
       </c>
       <c r="N25" t="n">
-        <v>286</v>
+        <v>119</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>almazer</t>
+          <t>facecrack</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.2227</v>
+        <v>0.9464</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0411</v>
+        <v>0.1745</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3552</v>
+        <v>-0.2108</v>
       </c>
       <c r="E26" t="n">
-        <v>0.2227</v>
+        <v>0.9464</v>
       </c>
       <c r="F26" t="n">
-        <v>0.2227</v>
+        <v>0.9464</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.2227</v>
+        <v>0.9464</v>
       </c>
       <c r="I26" t="n">
-        <v>0.2227</v>
+        <v>0.9464</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.2227</v>
+        <v>0.9464</v>
       </c>
       <c r="N26" t="n">
         <v>218</v>
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.2185</v>
+        <v>0.4547</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0403</v>
+        <v>0.0838</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.3569</v>
+        <v>-0.4327</v>
       </c>
       <c r="E27" t="n">
-        <v>0.2185</v>
+        <v>0.4547</v>
       </c>
       <c r="F27" t="n">
-        <v>0.2185</v>
+        <v>0.4547</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2185</v>
+        <v>0.4547</v>
       </c>
       <c r="I27" t="n">
-        <v>0.2185</v>
+        <v>0.4547</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.2185</v>
+        <v>0.4547</v>
       </c>
       <c r="N27" t="n">
         <v>119</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.0852</v>
+        <v>0.4176</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0157</v>
+        <v>0.077</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.41</v>
+        <v>-0.4495</v>
       </c>
       <c r="E28" t="n">
-        <v>0.0852</v>
+        <v>0.4176</v>
       </c>
       <c r="F28" t="n">
-        <v>0.0852</v>
+        <v>0.4176</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.0852</v>
+        <v>0.4176</v>
       </c>
       <c r="I28" t="n">
-        <v>0.0852</v>
+        <v>0.4176</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.0852</v>
+        <v>0.4176</v>
       </c>
       <c r="N28" t="n">
         <v>157</v>
@@ -1734,93 +1734,93 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>sdy</t>
+          <t>Thomas</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.0193</v>
+        <v>0.3926</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0036</v>
+        <v>0.07240000000000001</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.4516</v>
+        <v>-0.4608</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.0193</v>
+        <v>0.3926</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.0193</v>
+        <v>0.3926</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.0193</v>
+        <v>0.3926</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.0193</v>
+        <v>0.3926</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>157</v>
+        <v>207</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.0193</v>
+        <v>0.3926</v>
       </c>
       <c r="N29" t="n">
-        <v>157</v>
+        <v>207</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Thomas</t>
+          <t>sdy</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.1253</v>
+        <v>0.2354</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0231</v>
+        <v>0.0434</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.4938</v>
+        <v>-0.5317</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.1253</v>
+        <v>0.2354</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.1253</v>
+        <v>0.2354</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.1253</v>
+        <v>0.2354</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1253</v>
+        <v>0.2354</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>207</v>
+        <v>157</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.1253</v>
+        <v>0.2354</v>
       </c>
       <c r="N30" t="n">
-        <v>207</v>
+        <v>157</v>
       </c>
     </row>
     <row r="31">
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.5432</v>
+        <v>-0.1301</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.1002</v>
+        <v>-0.024</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6603</v>
+        <v>-0.6967</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.5432</v>
+        <v>-0.1301</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.5432</v>
+        <v>-0.1301</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.5432</v>
+        <v>-0.1301</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.5432</v>
+        <v>-0.1301</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.5432</v>
+        <v>-0.1301</v>
       </c>
       <c r="N31" t="n">
         <v>119</v>
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.8572</v>
+        <v>-0.3912</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.1581</v>
+        <v>-0.0721</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7854</v>
+        <v>-0.8146</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.8572</v>
+        <v>-0.3912</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.8572</v>
+        <v>-0.3912</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.8572</v>
+        <v>-0.3912</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.8572</v>
+        <v>-0.3912</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.8572</v>
+        <v>-0.3912</v>
       </c>
       <c r="N32" t="n">
         <v>119</v>
@@ -1918,32 +1918,32 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>chopper</t>
+          <t>magixx</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.9059</v>
+        <v>-0.4363</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.1671</v>
+        <v>-0.0805</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8048</v>
+        <v>-0.835</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.9059</v>
+        <v>-0.4363</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.9059</v>
+        <v>-0.4363</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.9059</v>
+        <v>-0.4363</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.9059</v>
+        <v>-0.4363</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.9059</v>
+        <v>-0.4363</v>
       </c>
       <c r="N33" t="n">
         <v>157</v>
@@ -1964,32 +1964,32 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>magixx</t>
+          <t>chopper</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.93</v>
+        <v>-0.4457</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.1715</v>
+        <v>-0.0822</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8144</v>
+        <v>-0.8391999999999999</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.93</v>
+        <v>-0.4457</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.93</v>
+        <v>-0.4457</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.93</v>
+        <v>-0.4457</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.93</v>
+        <v>-0.4457</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.93</v>
+        <v>-0.4457</v>
       </c>
       <c r="N34" t="n">
         <v>157</v>
@@ -2014,31 +2014,31 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.0936</v>
+        <v>-0.5474</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.2017</v>
+        <v>-0.1009</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8796</v>
+        <v>-0.8851</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.0936</v>
+        <v>-0.5474</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.3182</v>
+        <v>-0.8137</v>
       </c>
       <c r="G35" t="n">
-        <v>0.2246</v>
+        <v>0.2663</v>
       </c>
       <c r="H35" t="n">
-        <v>-1.3182</v>
+        <v>-0.8137</v>
       </c>
       <c r="I35" t="n">
-        <v>-1.0684</v>
+        <v>-0.4231</v>
       </c>
       <c r="J35" t="n">
-        <v>0.2246</v>
+        <v>0.2663</v>
       </c>
       <c r="K35" t="n">
         <v>197</v>
@@ -2047,7 +2047,7 @@
         <v>81</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.8438</v>
+        <v>-0.1568</v>
       </c>
       <c r="N35" t="n">
         <v>278</v>
@@ -2060,31 +2060,31 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.3595</v>
+        <v>-0.5668</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.2507</v>
+        <v>-0.1045</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9855</v>
+        <v>-0.8939</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.3595</v>
+        <v>-0.5668</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.3269</v>
+        <v>0.0383</v>
       </c>
       <c r="G36" t="n">
-        <v>-1.0326</v>
+        <v>-0.6051</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.3269</v>
+        <v>0.0383</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.265</v>
+        <v>0.0199</v>
       </c>
       <c r="J36" t="n">
-        <v>-1.0326</v>
+        <v>-0.6051</v>
       </c>
       <c r="K36" t="n">
         <v>154</v>
@@ -2093,7 +2093,7 @@
         <v>132</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.2976</v>
+        <v>-0.5851999999999999</v>
       </c>
       <c r="N36" t="n">
         <v>286</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.6923</v>
+        <v>-0.9302</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.3121</v>
+        <v>-0.1715</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.1181</v>
+        <v>-1.058</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.6923</v>
+        <v>-0.9302</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.6923</v>
+        <v>-0.9302</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.6923</v>
+        <v>-0.9302</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.6923</v>
+        <v>-0.9302</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.6923</v>
+        <v>-0.9302</v>
       </c>
       <c r="N37" t="n">
         <v>207</v>
@@ -2148,139 +2148,139 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>RUSH</t>
+          <t>Jerry</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.9286</v>
+        <v>-1.2221</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.3556</v>
+        <v>-0.2254</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.2123</v>
+        <v>-1.1897</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.9286</v>
+        <v>-1.2221</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.9898</v>
+        <v>-1.2221</v>
       </c>
       <c r="G38" t="n">
-        <v>0.0612</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.9898</v>
+        <v>-1.2221</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.6128</v>
+        <v>-1.2221</v>
       </c>
       <c r="J38" t="n">
-        <v>0.0612</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>146</v>
+        <v>218</v>
       </c>
       <c r="L38" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.5516</v>
+        <v>-1.2221</v>
       </c>
       <c r="N38" t="n">
-        <v>223</v>
+        <v>218</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Jerry</t>
+          <t>MiGHTYMAX</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.9642</v>
+        <v>-1.7578</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.3622</v>
+        <v>-0.3241</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.2264</v>
+        <v>-1.4316</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.9642</v>
+        <v>-1.7578</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.9642</v>
+        <v>-1.7578</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.9642</v>
+        <v>-1.7578</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.9642</v>
+        <v>-1.7578</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.9642</v>
+        <v>-1.7578</v>
       </c>
       <c r="N39" t="n">
-        <v>218</v>
+        <v>207</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>MiGHTYMAX</t>
+          <t>RUSH</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-2.2193</v>
+        <v>-2.1667</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.4093</v>
+        <v>-0.3996</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.3281</v>
+        <v>-1.6162</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.2193</v>
+        <v>-2.1667</v>
       </c>
       <c r="F40" t="n">
-        <v>-2.2193</v>
+        <v>-2.3191</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>0.1524</v>
       </c>
       <c r="H40" t="n">
-        <v>-2.2193</v>
+        <v>-2.3191</v>
       </c>
       <c r="I40" t="n">
-        <v>-2.2193</v>
+        <v>-1.2058</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>0.1524</v>
       </c>
       <c r="K40" t="n">
-        <v>207</v>
+        <v>146</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="M40" t="n">
-        <v>-2.2193</v>
+        <v>-1.0534</v>
       </c>
       <c r="N40" t="n">
-        <v>207</v>
+        <v>223</v>
       </c>
     </row>
     <row r="41">
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.5187</v>
+        <v>-4.5023</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.4645</v>
+        <v>-0.8302</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.4474</v>
+        <v>-2.6706</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.5187</v>
+        <v>-4.5023</v>
       </c>
       <c r="F41" t="n">
-        <v>-4.8327</v>
+        <v>-6.7441</v>
       </c>
       <c r="G41" t="n">
-        <v>2.314</v>
+        <v>2.2418</v>
       </c>
       <c r="H41" t="n">
-        <v>-4.8327</v>
+        <v>-6.7441</v>
       </c>
       <c r="I41" t="n">
-        <v>-3.917</v>
+        <v>-3.5066</v>
       </c>
       <c r="J41" t="n">
-        <v>2.314</v>
+        <v>2.2418</v>
       </c>
       <c r="K41" t="n">
         <v>144</v>
@@ -2323,7 +2323,7 @@
         <v>136</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.603</v>
+        <v>-1.2648</v>
       </c>
       <c r="N41" t="n">
         <v>280</v>
@@ -2429,10 +2429,10 @@
         <v>1.1</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2356</v>
+        <v>0.2516</v>
       </c>
       <c r="J2" t="n">
-        <v>6.3612</v>
+        <v>6.7932</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.09</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2184</v>
+        <v>0.2309</v>
       </c>
       <c r="J3" t="n">
-        <v>5.8968</v>
+        <v>6.2343</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.04</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1236</v>
+        <v>0.1201</v>
       </c>
       <c r="J4" t="n">
-        <v>3.3372</v>
+        <v>3.2427</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.85</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3035</v>
+        <v>-0.1856</v>
       </c>
       <c r="J5" t="n">
-        <v>-8.1945</v>
+        <v>-5.0112</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.82</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3493</v>
+        <v>-0.2165</v>
       </c>
       <c r="J6" t="n">
-        <v>-9.431100000000001</v>
+        <v>-5.8455</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.44</v>
       </c>
       <c r="I7" t="n">
-        <v>1.1326</v>
+        <v>1.0796</v>
       </c>
       <c r="J7" t="n">
-        <v>30.5802</v>
+        <v>29.1492</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.4</v>
       </c>
       <c r="I8" t="n">
-        <v>1.0489</v>
+        <v>1.0231</v>
       </c>
       <c r="J8" t="n">
-        <v>28.3203</v>
+        <v>27.6237</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.09719999999999999</v>
+        <v>-0.0322</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.6244</v>
+        <v>-0.8694</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.09719999999999999</v>
+        <v>-0.0322</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.6244</v>
+        <v>-0.8694</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.84</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.6147</v>
+        <v>-0.5538999999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>-16.5969</v>
+        <v>-14.9553</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.13</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3131</v>
+        <v>0.3378</v>
       </c>
       <c r="J12" t="n">
-        <v>8.7668</v>
+        <v>9.458399999999999</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>0.99</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0163</v>
+        <v>-0.0106</v>
       </c>
       <c r="J13" t="n">
-        <v>0.4564</v>
+        <v>-0.2968</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.98</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.009299999999999999</v>
+        <v>-0.0266</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.2604</v>
+        <v>-0.7448</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.82</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3261</v>
+        <v>-0.2073</v>
       </c>
       <c r="J15" t="n">
-        <v>-9.130800000000001</v>
+        <v>-5.8044</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.6</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6302</v>
+        <v>-0.4185</v>
       </c>
       <c r="J16" t="n">
-        <v>-17.6456</v>
+        <v>-11.718</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.28</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7896</v>
+        <v>0.7712</v>
       </c>
       <c r="J17" t="n">
-        <v>22.1088</v>
+        <v>21.5936</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.16</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4839</v>
+        <v>0.4759</v>
       </c>
       <c r="J18" t="n">
-        <v>13.5492</v>
+        <v>13.3252</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.08</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2205</v>
+        <v>0.263</v>
       </c>
       <c r="J19" t="n">
-        <v>6.174</v>
+        <v>7.364</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.05</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1217</v>
+        <v>0.1715</v>
       </c>
       <c r="J20" t="n">
-        <v>3.4076</v>
+        <v>4.802</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>1.04</v>
       </c>
       <c r="I21" t="n">
-        <v>0.08690000000000001</v>
+        <v>0.1386</v>
       </c>
       <c r="J21" t="n">
-        <v>2.4332</v>
+        <v>3.8808</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.14</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3073</v>
+        <v>0.258</v>
       </c>
       <c r="J22" t="n">
-        <v>7.6825</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.14</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3073</v>
+        <v>0.258</v>
       </c>
       <c r="J23" t="n">
-        <v>7.6825</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.87</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.2658</v>
+        <v>-0.1625</v>
       </c>
       <c r="J24" t="n">
-        <v>-6.645</v>
+        <v>-4.0625</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.83</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.3292</v>
+        <v>-0.2042</v>
       </c>
       <c r="J25" t="n">
-        <v>-8.23</v>
+        <v>-5.105</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.83</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.3292</v>
+        <v>-0.2042</v>
       </c>
       <c r="J26" t="n">
-        <v>-8.23</v>
+        <v>-5.105</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.64</v>
       </c>
       <c r="I27" t="n">
-        <v>0.8635</v>
+        <v>0.5965</v>
       </c>
       <c r="J27" t="n">
-        <v>21.5875</v>
+        <v>14.9125</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.39</v>
       </c>
       <c r="I28" t="n">
-        <v>0.5773</v>
+        <v>0.4349</v>
       </c>
       <c r="J28" t="n">
-        <v>14.4325</v>
+        <v>10.8725</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.19</v>
       </c>
       <c r="I29" t="n">
-        <v>0.2995</v>
+        <v>0.2711</v>
       </c>
       <c r="J29" t="n">
-        <v>7.4875</v>
+        <v>6.7775</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>1.07</v>
       </c>
       <c r="I30" t="n">
-        <v>0.0897</v>
+        <v>0.1105</v>
       </c>
       <c r="J30" t="n">
-        <v>2.2425</v>
+        <v>2.7625</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.61</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.6554</v>
+        <v>-0.4364</v>
       </c>
       <c r="J31" t="n">
-        <v>-16.385</v>
+        <v>-10.91</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.55</v>
       </c>
       <c r="I32" t="n">
-        <v>1.3229</v>
+        <v>0.9324</v>
       </c>
       <c r="J32" t="n">
-        <v>34.3954</v>
+        <v>24.2424</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.34</v>
       </c>
       <c r="I33" t="n">
-        <v>0.8862</v>
+        <v>0.6593</v>
       </c>
       <c r="J33" t="n">
-        <v>23.0412</v>
+        <v>17.1418</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.2</v>
       </c>
       <c r="I34" t="n">
-        <v>0.5343</v>
+        <v>0.4675</v>
       </c>
       <c r="J34" t="n">
-        <v>13.8918</v>
+        <v>12.155</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.12</v>
       </c>
       <c r="I35" t="n">
-        <v>0.2957</v>
+        <v>0.3483</v>
       </c>
       <c r="J35" t="n">
-        <v>7.6882</v>
+        <v>9.0558</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.77</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.7989000000000001</v>
+        <v>-0.7507</v>
       </c>
       <c r="J36" t="n">
-        <v>-20.7714</v>
+        <v>-19.5182</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.05</v>
       </c>
       <c r="I37" t="n">
-        <v>0.1908</v>
+        <v>0.1788</v>
       </c>
       <c r="J37" t="n">
-        <v>4.9608</v>
+        <v>4.6488</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>0.96</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.0362</v>
+        <v>-0.0487</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.9412</v>
+        <v>-1.2662</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.96</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.0362</v>
+        <v>-0.0487</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.9412</v>
+        <v>-1.2662</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.68</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.5173</v>
+        <v>-0.3384</v>
       </c>
       <c r="J40" t="n">
-        <v>-13.4498</v>
+        <v>-8.798400000000001</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.67</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.5309</v>
+        <v>-0.3479</v>
       </c>
       <c r="J41" t="n">
-        <v>-13.8034</v>
+        <v>-9.045400000000001</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.21</v>
       </c>
       <c r="I42" t="n">
-        <v>0.6684</v>
+        <v>0.5083</v>
       </c>
       <c r="J42" t="n">
-        <v>20.052</v>
+        <v>15.249</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.13</v>
       </c>
       <c r="I43" t="n">
-        <v>0.4567</v>
+        <v>0.3844</v>
       </c>
       <c r="J43" t="n">
-        <v>13.701</v>
+        <v>11.532</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.02</v>
       </c>
       <c r="I44" t="n">
-        <v>0.0655</v>
+        <v>0.0867</v>
       </c>
       <c r="J44" t="n">
-        <v>1.965</v>
+        <v>2.601</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.0429</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="J45" t="n">
-        <v>-1.287</v>
+        <v>-0.237</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.84</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.5814</v>
+        <v>-0.5273</v>
       </c>
       <c r="J46" t="n">
-        <v>-17.442</v>
+        <v>-15.819</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.56</v>
       </c>
       <c r="I47" t="n">
-        <v>0.8217</v>
+        <v>0.7471</v>
       </c>
       <c r="J47" t="n">
-        <v>24.651</v>
+        <v>22.413</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>0.99</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.0559</v>
+        <v>-0.023</v>
       </c>
       <c r="J48" t="n">
-        <v>-1.677</v>
+        <v>-0.6899999999999999</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.99</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.0559</v>
+        <v>-0.023</v>
       </c>
       <c r="J49" t="n">
-        <v>-1.677</v>
+        <v>-0.6899999999999999</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.9</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.2368</v>
+        <v>-0.1376</v>
       </c>
       <c r="J50" t="n">
-        <v>-7.104</v>
+        <v>-4.128</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.71</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.5125</v>
+        <v>-0.3301</v>
       </c>
       <c r="J51" t="n">
-        <v>-15.375</v>
+        <v>-9.903</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.74</v>
       </c>
       <c r="I52" t="n">
-        <v>0.9197</v>
+        <v>0.6329</v>
       </c>
       <c r="J52" t="n">
-        <v>18.394</v>
+        <v>12.658</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.42</v>
       </c>
       <c r="I53" t="n">
-        <v>0.5573</v>
+        <v>0.4388</v>
       </c>
       <c r="J53" t="n">
-        <v>11.146</v>
+        <v>8.776</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.3</v>
       </c>
       <c r="I54" t="n">
-        <v>0.383</v>
+        <v>0.3632</v>
       </c>
       <c r="J54" t="n">
-        <v>7.66</v>
+        <v>7.264</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1.2</v>
       </c>
       <c r="I55" t="n">
-        <v>0.2463</v>
+        <v>0.2652</v>
       </c>
       <c r="J55" t="n">
-        <v>4.926</v>
+        <v>5.304</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>1.17</v>
       </c>
       <c r="I56" t="n">
-        <v>0.204</v>
+        <v>0.2273</v>
       </c>
       <c r="J56" t="n">
-        <v>4.08</v>
+        <v>4.546</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.2182</v>
+        <v>-0.1872</v>
       </c>
       <c r="J57" t="n">
-        <v>-4.364</v>
+        <v>-3.744</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>0.79</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.2501</v>
+        <v>-0.2084</v>
       </c>
       <c r="J58" t="n">
-        <v>-5.002</v>
+        <v>-4.168</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.72</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.3641</v>
+        <v>-0.2781</v>
       </c>
       <c r="J59" t="n">
-        <v>-7.282</v>
+        <v>-5.562</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.4225</v>
+        <v>-0.3053</v>
       </c>
       <c r="J60" t="n">
-        <v>-8.449999999999999</v>
+        <v>-6.106</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.44</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.7861</v>
+        <v>-0.5373</v>
       </c>
       <c r="J61" t="n">
-        <v>-15.722</v>
+        <v>-10.746</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.43</v>
       </c>
       <c r="I62" t="n">
-        <v>0.6956</v>
+        <v>0.6423</v>
       </c>
       <c r="J62" t="n">
-        <v>15.9988</v>
+        <v>14.7729</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>0.99</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.0098</v>
+        <v>-0.0176</v>
       </c>
       <c r="J63" t="n">
-        <v>-0.2254</v>
+        <v>-0.4048</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>0.97</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.062</v>
+        <v>-0.0472</v>
       </c>
       <c r="J64" t="n">
-        <v>-1.426</v>
+        <v>-1.0856</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.74</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.4587</v>
+        <v>-0.2933</v>
       </c>
       <c r="J65" t="n">
-        <v>-10.5501</v>
+        <v>-6.7459</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.67</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.5518</v>
+        <v>-0.36</v>
       </c>
       <c r="J66" t="n">
-        <v>-12.6914</v>
+        <v>-8.279999999999999</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.63</v>
       </c>
       <c r="I67" t="n">
-        <v>1.4701</v>
+        <v>1.0297</v>
       </c>
       <c r="J67" t="n">
-        <v>33.8123</v>
+        <v>23.6831</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.25</v>
       </c>
       <c r="I68" t="n">
-        <v>0.6642</v>
+        <v>0.5353</v>
       </c>
       <c r="J68" t="n">
-        <v>15.2766</v>
+        <v>12.3119</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.16</v>
       </c>
       <c r="I69" t="n">
-        <v>0.4007</v>
+        <v>0.4089</v>
       </c>
       <c r="J69" t="n">
-        <v>9.216100000000001</v>
+        <v>9.4047</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>1.02</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.0258</v>
+        <v>0.0454</v>
       </c>
       <c r="J70" t="n">
-        <v>-0.5934</v>
+        <v>1.0442</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.98</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.2264</v>
+        <v>-0.1467</v>
       </c>
       <c r="J71" t="n">
-        <v>-5.2072</v>
+        <v>-3.3741</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.19</v>
       </c>
       <c r="I72" t="n">
-        <v>0.3847</v>
+        <v>0.3937</v>
       </c>
       <c r="J72" t="n">
-        <v>13.0798</v>
+        <v>13.3858</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.02</v>
       </c>
       <c r="I73" t="n">
-        <v>0.08939999999999999</v>
+        <v>0.0746</v>
       </c>
       <c r="J73" t="n">
-        <v>3.0396</v>
+        <v>2.5364</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.98</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.0345</v>
+        <v>-0.0329</v>
       </c>
       <c r="J74" t="n">
-        <v>-1.173</v>
+        <v>-1.1186</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.84</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.312</v>
+        <v>-0.1932</v>
       </c>
       <c r="J75" t="n">
-        <v>-10.608</v>
+        <v>-6.5688</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.75</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.444</v>
+        <v>-0.2831</v>
       </c>
       <c r="J76" t="n">
-        <v>-15.096</v>
+        <v>-9.625400000000001</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.23</v>
       </c>
       <c r="I77" t="n">
-        <v>0.6952</v>
+        <v>0.5293</v>
       </c>
       <c r="J77" t="n">
-        <v>23.6368</v>
+        <v>17.9962</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.2</v>
       </c>
       <c r="I78" t="n">
-        <v>0.6202</v>
+        <v>0.485</v>
       </c>
       <c r="J78" t="n">
-        <v>21.0868</v>
+        <v>16.49</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.19</v>
       </c>
       <c r="I79" t="n">
-        <v>0.5945</v>
+        <v>0.47</v>
       </c>
       <c r="J79" t="n">
-        <v>20.213</v>
+        <v>15.98</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1.06</v>
       </c>
       <c r="I80" t="n">
-        <v>0.1875</v>
+        <v>0.2126</v>
       </c>
       <c r="J80" t="n">
-        <v>6.375</v>
+        <v>7.2284</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.71</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.9053</v>
+        <v>-0.8708</v>
       </c>
       <c r="J81" t="n">
-        <v>-30.7802</v>
+        <v>-29.6072</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.17</v>
       </c>
       <c r="I82" t="n">
-        <v>0.3574</v>
+        <v>0.3994</v>
       </c>
       <c r="J82" t="n">
-        <v>10.722</v>
+        <v>11.982</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>0.99</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.0047</v>
+        <v>-0.0166</v>
       </c>
       <c r="J83" t="n">
-        <v>-0.141</v>
+        <v>-0.498</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.96</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.0794</v>
+        <v>-0.0594</v>
       </c>
       <c r="J84" t="n">
-        <v>-2.382</v>
+        <v>-1.782</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.84</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.3101</v>
+        <v>-0.1925</v>
       </c>
       <c r="J85" t="n">
-        <v>-9.303000000000001</v>
+        <v>-5.775</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.79</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.3857</v>
+        <v>-0.243</v>
       </c>
       <c r="J86" t="n">
-        <v>-11.571</v>
+        <v>-7.29</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.53</v>
       </c>
       <c r="I87" t="n">
-        <v>1.2808</v>
+        <v>1.1792</v>
       </c>
       <c r="J87" t="n">
-        <v>38.424</v>
+        <v>35.376</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.36</v>
       </c>
       <c r="I88" t="n">
-        <v>0.9275</v>
+        <v>0.9284</v>
       </c>
       <c r="J88" t="n">
-        <v>27.825</v>
+        <v>27.852</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.15</v>
       </c>
       <c r="I89" t="n">
-        <v>0.3767</v>
+        <v>0.4367</v>
       </c>
       <c r="J89" t="n">
-        <v>11.301</v>
+        <v>13.101</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>1.13</v>
       </c>
       <c r="I90" t="n">
-        <v>0.3207</v>
+        <v>0.3843</v>
       </c>
       <c r="J90" t="n">
-        <v>9.621</v>
+        <v>11.529</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.84</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.6334</v>
+        <v>-0.5705</v>
       </c>
       <c r="J91" t="n">
-        <v>-19.002</v>
+        <v>-17.115</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.08</v>
       </c>
       <c r="I92" t="n">
-        <v>0.2124</v>
+        <v>0.218</v>
       </c>
       <c r="J92" t="n">
-        <v>5.5224</v>
+        <v>5.668</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.04</v>
       </c>
       <c r="I93" t="n">
-        <v>0.1363</v>
+        <v>0.1273</v>
       </c>
       <c r="J93" t="n">
-        <v>3.5438</v>
+        <v>3.3098</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.98</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.0312</v>
+        <v>-0.0323</v>
       </c>
       <c r="J94" t="n">
-        <v>-0.8112</v>
+        <v>-0.8398</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.9</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.2097</v>
+        <v>-0.1288</v>
       </c>
       <c r="J95" t="n">
-        <v>-5.4522</v>
+        <v>-3.3488</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.75</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.4426</v>
+        <v>-0.2824</v>
       </c>
       <c r="J96" t="n">
-        <v>-11.5076</v>
+        <v>-7.3424</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.34</v>
       </c>
       <c r="I97" t="n">
-        <v>0.8927</v>
+        <v>0.89</v>
       </c>
       <c r="J97" t="n">
-        <v>23.2102</v>
+        <v>23.14</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.24</v>
       </c>
       <c r="I98" t="n">
-        <v>0.655</v>
+        <v>0.6576</v>
       </c>
       <c r="J98" t="n">
-        <v>17.03</v>
+        <v>17.0976</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.17</v>
       </c>
       <c r="I99" t="n">
-        <v>0.4473</v>
+        <v>0.4905</v>
       </c>
       <c r="J99" t="n">
-        <v>11.6298</v>
+        <v>12.753</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>1.14</v>
       </c>
       <c r="I100" t="n">
-        <v>0.3599</v>
+        <v>0.4145</v>
       </c>
       <c r="J100" t="n">
-        <v>9.3574</v>
+        <v>10.777</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>1.03</v>
       </c>
       <c r="I101" t="n">
-        <v>0.0214</v>
+        <v>0.0885</v>
       </c>
       <c r="J101" t="n">
-        <v>0.5564</v>
+        <v>2.301</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>0.74</v>
       </c>
       <c r="I102" t="n">
-        <v>-0.2595</v>
+        <v>-0.2255</v>
       </c>
       <c r="J102" t="n">
-        <v>-4.9305</v>
+        <v>-4.2845</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>0.62</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.4457</v>
+        <v>-0.3495</v>
       </c>
       <c r="J103" t="n">
-        <v>-8.468299999999999</v>
+        <v>-6.6405</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.53</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.6151</v>
+        <v>-0.4305</v>
       </c>
       <c r="J104" t="n">
-        <v>-11.6869</v>
+        <v>-8.179500000000001</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.52</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.6313</v>
+        <v>-0.4397</v>
       </c>
       <c r="J105" t="n">
-        <v>-11.9947</v>
+        <v>-8.3543</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.42</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.7771</v>
+        <v>-0.5342</v>
       </c>
       <c r="J106" t="n">
-        <v>-14.7649</v>
+        <v>-10.1498</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.79</v>
       </c>
       <c r="I107" t="n">
-        <v>1.6257</v>
+        <v>1.4242</v>
       </c>
       <c r="J107" t="n">
-        <v>30.8883</v>
+        <v>27.0598</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.73</v>
       </c>
       <c r="I108" t="n">
-        <v>1.5171</v>
+        <v>1.3562</v>
       </c>
       <c r="J108" t="n">
-        <v>28.8249</v>
+        <v>25.7678</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.63</v>
       </c>
       <c r="I109" t="n">
-        <v>1.3278</v>
+        <v>1.2418</v>
       </c>
       <c r="J109" t="n">
-        <v>25.2282</v>
+        <v>23.5942</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>1.4</v>
       </c>
       <c r="I110" t="n">
-        <v>0.8202</v>
+        <v>0.9492</v>
       </c>
       <c r="J110" t="n">
-        <v>15.5838</v>
+        <v>18.0348</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>1.05</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.0086</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="J111" t="n">
-        <v>-0.1634</v>
+        <v>1.5504</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.35</v>
       </c>
       <c r="I112" t="n">
-        <v>0.5875</v>
+        <v>0.7074</v>
       </c>
       <c r="J112" t="n">
-        <v>17.625</v>
+        <v>21.222</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.01</v>
       </c>
       <c r="I113" t="n">
-        <v>0.0466</v>
+        <v>0.0392</v>
       </c>
       <c r="J113" t="n">
-        <v>1.398</v>
+        <v>1.176</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.99</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.0311</v>
+        <v>-0.02</v>
       </c>
       <c r="J114" t="n">
-        <v>-0.9330000000000001</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.85</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.3063</v>
+        <v>-0.1868</v>
       </c>
       <c r="J115" t="n">
-        <v>-9.189</v>
+        <v>-5.604</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.75</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.4516</v>
+        <v>-0.2871</v>
       </c>
       <c r="J116" t="n">
-        <v>-13.548</v>
+        <v>-8.613</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.1</v>
       </c>
       <c r="I117" t="n">
-        <v>0.3979</v>
+        <v>0.3496</v>
       </c>
       <c r="J117" t="n">
-        <v>11.937</v>
+        <v>10.488</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.01</v>
       </c>
       <c r="I118" t="n">
-        <v>0.0727</v>
+        <v>0.0538</v>
       </c>
       <c r="J118" t="n">
-        <v>2.181</v>
+        <v>1.614</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>0.97</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.1588</v>
+        <v>-0.1295</v>
       </c>
       <c r="J119" t="n">
-        <v>-4.764</v>
+        <v>-3.885</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.96</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.1977</v>
+        <v>-0.1638</v>
       </c>
       <c r="J120" t="n">
-        <v>-5.931</v>
+        <v>-4.914</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.95</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.2342</v>
+        <v>-0.1967</v>
       </c>
       <c r="J121" t="n">
-        <v>-7.026</v>
+        <v>-5.901</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.63</v>
       </c>
       <c r="I122" t="n">
-        <v>1.5258</v>
+        <v>1.3394</v>
       </c>
       <c r="J122" t="n">
-        <v>45.774</v>
+        <v>40.182</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.03</v>
       </c>
       <c r="I123" t="n">
-        <v>0.0641</v>
+        <v>0.11</v>
       </c>
       <c r="J123" t="n">
-        <v>1.923</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.01</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.0188</v>
+        <v>0.0323</v>
       </c>
       <c r="J124" t="n">
-        <v>-0.5639999999999999</v>
+        <v>0.969</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.92</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.3835</v>
+        <v>-0.3176</v>
       </c>
       <c r="J125" t="n">
-        <v>-11.505</v>
+        <v>-9.528</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.9</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.4416</v>
+        <v>-0.3767</v>
       </c>
       <c r="J126" t="n">
-        <v>-13.248</v>
+        <v>-11.301</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.36</v>
       </c>
       <c r="I127" t="n">
-        <v>0.596</v>
+        <v>0.7194</v>
       </c>
       <c r="J127" t="n">
-        <v>17.88</v>
+        <v>21.582</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.18</v>
       </c>
       <c r="I128" t="n">
-        <v>0.3537</v>
+        <v>0.4011</v>
       </c>
       <c r="J128" t="n">
-        <v>10.611</v>
+        <v>12.033</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.03</v>
       </c>
       <c r="I129" t="n">
-        <v>0.0912</v>
+        <v>0.0915</v>
       </c>
       <c r="J129" t="n">
-        <v>2.736</v>
+        <v>2.745</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1.01</v>
       </c>
       <c r="I130" t="n">
-        <v>0.039</v>
+        <v>0.0375</v>
       </c>
       <c r="J130" t="n">
-        <v>1.17</v>
+        <v>1.125</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.43</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.843</v>
+        <v>-0.5814</v>
       </c>
       <c r="J131" t="n">
-        <v>-25.29</v>
+        <v>-17.442</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.3</v>
       </c>
       <c r="I132" t="n">
-        <v>0.8204</v>
+        <v>0.8088</v>
       </c>
       <c r="J132" t="n">
-        <v>23.7916</v>
+        <v>23.4552</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.16</v>
       </c>
       <c r="I133" t="n">
-        <v>0.4594</v>
+        <v>0.4705</v>
       </c>
       <c r="J133" t="n">
-        <v>13.3226</v>
+        <v>13.6445</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.16</v>
       </c>
       <c r="I134" t="n">
-        <v>0.4594</v>
+        <v>0.4705</v>
       </c>
       <c r="J134" t="n">
-        <v>13.3226</v>
+        <v>13.6445</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.08</v>
       </c>
       <c r="I135" t="n">
-        <v>0.2028</v>
+        <v>0.2567</v>
       </c>
       <c r="J135" t="n">
-        <v>5.8812</v>
+        <v>7.4443</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>1.05</v>
       </c>
       <c r="I136" t="n">
-        <v>0.1065</v>
+        <v>0.1646</v>
       </c>
       <c r="J136" t="n">
-        <v>3.0885</v>
+        <v>4.7734</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>0.9</v>
       </c>
       <c r="I137" t="n">
-        <v>-0.1268</v>
+        <v>-0.1134</v>
       </c>
       <c r="J137" t="n">
-        <v>-3.6772</v>
+        <v>-3.2886</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>0.83</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.251</v>
+        <v>-0.1879</v>
       </c>
       <c r="J138" t="n">
-        <v>-7.279</v>
+        <v>-5.4491</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.82</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.2702</v>
+        <v>-0.1977</v>
       </c>
       <c r="J139" t="n">
-        <v>-7.8358</v>
+        <v>-5.7333</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.8</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.3152</v>
+        <v>-0.2165</v>
       </c>
       <c r="J140" t="n">
-        <v>-9.1408</v>
+        <v>-6.2785</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.71</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.4594</v>
+        <v>-0.3027</v>
       </c>
       <c r="J141" t="n">
-        <v>-13.3226</v>
+        <v>-8.7783</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.22</v>
       </c>
       <c r="I142" t="n">
-        <v>0.6765</v>
+        <v>0.6442</v>
       </c>
       <c r="J142" t="n">
-        <v>20.295</v>
+        <v>19.326</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.21</v>
       </c>
       <c r="I143" t="n">
-        <v>0.6516</v>
+        <v>0.619</v>
       </c>
       <c r="J143" t="n">
-        <v>19.548</v>
+        <v>18.57</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.18</v>
       </c>
       <c r="I144" t="n">
-        <v>0.5747</v>
+        <v>0.5426</v>
       </c>
       <c r="J144" t="n">
-        <v>17.241</v>
+        <v>16.278</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1.16</v>
       </c>
       <c r="I145" t="n">
-        <v>0.5214</v>
+        <v>0.4906</v>
       </c>
       <c r="J145" t="n">
-        <v>15.642</v>
+        <v>14.718</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.57</v>
       </c>
       <c r="I146" t="n">
-        <v>-1.2011</v>
+        <v>-1.2031</v>
       </c>
       <c r="J146" t="n">
-        <v>-36.033</v>
+        <v>-36.093</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.19</v>
       </c>
       <c r="I147" t="n">
-        <v>0.3663</v>
+        <v>0.4178</v>
       </c>
       <c r="J147" t="n">
-        <v>10.989</v>
+        <v>12.534</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.04</v>
       </c>
       <c r="I148" t="n">
-        <v>0.1106</v>
+        <v>0.1146</v>
       </c>
       <c r="J148" t="n">
-        <v>3.318</v>
+        <v>3.438</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.04</v>
       </c>
       <c r="I149" t="n">
-        <v>0.1106</v>
+        <v>0.1146</v>
       </c>
       <c r="J149" t="n">
-        <v>3.318</v>
+        <v>3.438</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.89</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.2472</v>
+        <v>-0.1462</v>
       </c>
       <c r="J150" t="n">
-        <v>-7.416</v>
+        <v>-4.386</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.88</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.2637</v>
+        <v>-0.157</v>
       </c>
       <c r="J151" t="n">
-        <v>-7.911</v>
+        <v>-4.71</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.71</v>
       </c>
       <c r="I152" t="n">
-        <v>1.5905</v>
+        <v>1.3855</v>
       </c>
       <c r="J152" t="n">
-        <v>41.353</v>
+        <v>36.023</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.65</v>
       </c>
       <c r="I153" t="n">
-        <v>1.4801</v>
+        <v>1.3125</v>
       </c>
       <c r="J153" t="n">
-        <v>38.4826</v>
+        <v>34.125</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.16</v>
       </c>
       <c r="I154" t="n">
-        <v>0.3695</v>
+        <v>0.4485</v>
       </c>
       <c r="J154" t="n">
-        <v>9.606999999999999</v>
+        <v>11.661</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.93</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.4096</v>
+        <v>-0.33</v>
       </c>
       <c r="J155" t="n">
-        <v>-10.6496</v>
+        <v>-8.58</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.88</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.5478</v>
+        <v>-0.4763</v>
       </c>
       <c r="J156" t="n">
-        <v>-14.2428</v>
+        <v>-12.3838</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.17</v>
       </c>
       <c r="I157" t="n">
-        <v>0.3849</v>
+        <v>0.4296</v>
       </c>
       <c r="J157" t="n">
-        <v>10.0074</v>
+        <v>11.1696</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>0.97</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.02</v>
+        <v>-0.037</v>
       </c>
       <c r="J158" t="n">
-        <v>-0.52</v>
+        <v>-0.962</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>0.85</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.2638</v>
+        <v>-0.1737</v>
       </c>
       <c r="J159" t="n">
-        <v>-6.8588</v>
+        <v>-4.5162</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.72</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.4654</v>
+        <v>-0.3019</v>
       </c>
       <c r="J160" t="n">
-        <v>-12.1004</v>
+        <v>-7.8494</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.67</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.5338000000000001</v>
+        <v>-0.3495</v>
       </c>
       <c r="J161" t="n">
-        <v>-13.8788</v>
+        <v>-9.087</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.54</v>
       </c>
       <c r="I162" t="n">
-        <v>1.2975</v>
+        <v>1.1904</v>
       </c>
       <c r="J162" t="n">
-        <v>37.6275</v>
+        <v>34.5216</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.33</v>
       </c>
       <c r="I163" t="n">
-        <v>0.8569</v>
+        <v>0.8598</v>
       </c>
       <c r="J163" t="n">
-        <v>24.8501</v>
+        <v>24.9342</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.3</v>
       </c>
       <c r="I164" t="n">
-        <v>0.7872</v>
+        <v>0.7913</v>
       </c>
       <c r="J164" t="n">
-        <v>22.8288</v>
+        <v>22.9477</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1.04</v>
       </c>
       <c r="I165" t="n">
-        <v>0.0468</v>
+        <v>0.1172</v>
       </c>
       <c r="J165" t="n">
-        <v>1.3572</v>
+        <v>3.3988</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.83</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.6597</v>
+        <v>-0.5986</v>
       </c>
       <c r="J166" t="n">
-        <v>-19.1313</v>
+        <v>-17.3594</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.12</v>
       </c>
       <c r="I167" t="n">
-        <v>0.2904</v>
+        <v>0.3108</v>
       </c>
       <c r="J167" t="n">
-        <v>8.4216</v>
+        <v>9.013199999999999</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>0.98</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.0175</v>
+        <v>-0.0291</v>
       </c>
       <c r="J168" t="n">
-        <v>-0.5075</v>
+        <v>-0.8439</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.9</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.1963</v>
+        <v>-0.126</v>
       </c>
       <c r="J169" t="n">
-        <v>-5.6927</v>
+        <v>-3.654</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.84</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.3007</v>
+        <v>-0.1891</v>
       </c>
       <c r="J170" t="n">
-        <v>-8.7203</v>
+        <v>-5.4839</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.77</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.4071</v>
+        <v>-0.2593</v>
       </c>
       <c r="J171" t="n">
-        <v>-11.8059</v>
+        <v>-7.5197</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.22</v>
       </c>
       <c r="I172" t="n">
-        <v>0.5012</v>
+        <v>0.4523</v>
       </c>
       <c r="J172" t="n">
-        <v>10.5252</v>
+        <v>9.4983</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>0.8</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.2767</v>
+        <v>-0.2122</v>
       </c>
       <c r="J173" t="n">
-        <v>-5.8107</v>
+        <v>-4.4562</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.74</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.3934</v>
+        <v>-0.2683</v>
       </c>
       <c r="J174" t="n">
-        <v>-8.2614</v>
+        <v>-5.6343</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.72</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.426</v>
+        <v>-0.2871</v>
       </c>
       <c r="J175" t="n">
-        <v>-8.946</v>
+        <v>-6.0291</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.36</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.8961</v>
+        <v>-0.6217</v>
       </c>
       <c r="J176" t="n">
-        <v>-18.8181</v>
+        <v>-13.0557</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.6</v>
       </c>
       <c r="I177" t="n">
-        <v>0.7927</v>
+        <v>0.7145</v>
       </c>
       <c r="J177" t="n">
-        <v>16.6467</v>
+        <v>15.0045</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.44</v>
       </c>
       <c r="I178" t="n">
-        <v>0.6089</v>
+        <v>0.544</v>
       </c>
       <c r="J178" t="n">
-        <v>12.7869</v>
+        <v>11.424</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.34</v>
       </c>
       <c r="I179" t="n">
-        <v>0.4817</v>
+        <v>0.4344</v>
       </c>
       <c r="J179" t="n">
-        <v>10.1157</v>
+        <v>9.122400000000001</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.04</v>
       </c>
       <c r="I180" t="n">
-        <v>0.012</v>
+        <v>0.0502</v>
       </c>
       <c r="J180" t="n">
-        <v>0.252</v>
+        <v>1.0542</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.98</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.1432</v>
+        <v>-0.06320000000000001</v>
       </c>
       <c r="J181" t="n">
-        <v>-3.0072</v>
+        <v>-1.3272</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.43</v>
       </c>
       <c r="I182" t="n">
-        <v>1.0424</v>
+        <v>1.0351</v>
       </c>
       <c r="J182" t="n">
-        <v>26.06</v>
+        <v>25.8775</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.26</v>
       </c>
       <c r="I183" t="n">
-        <v>0.6274999999999999</v>
+        <v>0.6886</v>
       </c>
       <c r="J183" t="n">
-        <v>15.6875</v>
+        <v>17.215</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.24</v>
       </c>
       <c r="I184" t="n">
-        <v>0.5735</v>
+        <v>0.6428</v>
       </c>
       <c r="J184" t="n">
-        <v>14.3375</v>
+        <v>16.07</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>1.24</v>
       </c>
       <c r="I185" t="n">
-        <v>0.5735</v>
+        <v>0.6428</v>
       </c>
       <c r="J185" t="n">
-        <v>14.3375</v>
+        <v>16.07</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>1.19</v>
       </c>
       <c r="I186" t="n">
-        <v>0.4445</v>
+        <v>0.5229</v>
       </c>
       <c r="J186" t="n">
-        <v>11.1125</v>
+        <v>13.0725</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.23</v>
       </c>
       <c r="I187" t="n">
-        <v>0.4602</v>
+        <v>0.5316</v>
       </c>
       <c r="J187" t="n">
-        <v>11.505</v>
+        <v>13.29</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>0.99</v>
       </c>
       <c r="I188" t="n">
-        <v>0.0163</v>
+        <v>-0.0106</v>
       </c>
       <c r="J188" t="n">
-        <v>0.4075</v>
+        <v>-0.265</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.86</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.2601</v>
+        <v>-0.1665</v>
       </c>
       <c r="J189" t="n">
-        <v>-6.5025</v>
+        <v>-4.1625</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.74</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.445</v>
+        <v>-0.2863</v>
       </c>
       <c r="J190" t="n">
-        <v>-11.125</v>
+        <v>-7.1575</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.7</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.5002</v>
+        <v>-0.3247</v>
       </c>
       <c r="J191" t="n">
-        <v>-12.505</v>
+        <v>-8.1175</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>0.65</v>
       </c>
       <c r="I192" t="n">
-        <v>-0.3524</v>
+        <v>-0.2957</v>
       </c>
       <c r="J192" t="n">
-        <v>-5.6384</v>
+        <v>-4.7312</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>0.63</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.383</v>
+        <v>-0.3173</v>
       </c>
       <c r="J193" t="n">
-        <v>-6.128</v>
+        <v>-5.0768</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>0.43</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.7314000000000001</v>
+        <v>-0.5093</v>
       </c>
       <c r="J194" t="n">
-        <v>-11.7024</v>
+        <v>-8.1488</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.39</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.7914</v>
+        <v>-0.548</v>
       </c>
       <c r="J195" t="n">
-        <v>-12.6624</v>
+        <v>-8.768000000000001</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.38</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.8058999999999999</v>
+        <v>-0.5578</v>
       </c>
       <c r="J196" t="n">
-        <v>-12.8944</v>
+        <v>-8.924799999999999</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>2.11</v>
       </c>
       <c r="I197" t="n">
-        <v>1.2172</v>
+        <v>1.0858</v>
       </c>
       <c r="J197" t="n">
-        <v>19.4752</v>
+        <v>17.3728</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.65</v>
       </c>
       <c r="I198" t="n">
-        <v>0.745</v>
+        <v>0.7184</v>
       </c>
       <c r="J198" t="n">
-        <v>11.92</v>
+        <v>11.4944</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.54</v>
       </c>
       <c r="I199" t="n">
-        <v>0.6084000000000001</v>
+        <v>0.6124000000000001</v>
       </c>
       <c r="J199" t="n">
-        <v>9.734400000000001</v>
+        <v>9.798400000000001</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>1.52</v>
       </c>
       <c r="I200" t="n">
-        <v>0.5854</v>
+        <v>0.5923</v>
       </c>
       <c r="J200" t="n">
-        <v>9.366400000000001</v>
+        <v>9.476800000000001</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>1.41</v>
       </c>
       <c r="I201" t="n">
-        <v>0.4589</v>
+        <v>0.4779</v>
       </c>
       <c r="J201" t="n">
-        <v>7.3424</v>
+        <v>7.6464</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.7</v>
       </c>
       <c r="I202" t="n">
-        <v>1.5668</v>
+        <v>1.3702</v>
       </c>
       <c r="J202" t="n">
-        <v>37.6032</v>
+        <v>32.8848</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.54</v>
       </c>
       <c r="I203" t="n">
-        <v>1.2639</v>
+        <v>1.1742</v>
       </c>
       <c r="J203" t="n">
-        <v>30.3336</v>
+        <v>28.1808</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.2</v>
       </c>
       <c r="I204" t="n">
-        <v>0.467</v>
+        <v>0.5462</v>
       </c>
       <c r="J204" t="n">
-        <v>11.208</v>
+        <v>13.1088</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>1.07</v>
       </c>
       <c r="I205" t="n">
-        <v>0.116</v>
+        <v>0.1962</v>
       </c>
       <c r="J205" t="n">
-        <v>2.784</v>
+        <v>4.7088</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.88</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.5507</v>
+        <v>-0.479</v>
       </c>
       <c r="J206" t="n">
-        <v>-13.2168</v>
+        <v>-11.496</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>0.98</v>
       </c>
       <c r="I207" t="n">
-        <v>0.0165</v>
+        <v>-0.0167</v>
       </c>
       <c r="J207" t="n">
-        <v>0.396</v>
+        <v>-0.4008</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I208" t="n">
-        <v>-0.0674</v>
+        <v>-0.0712</v>
       </c>
       <c r="J208" t="n">
-        <v>-1.6176</v>
+        <v>-1.7088</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>0.85</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.236</v>
+        <v>-0.1712</v>
       </c>
       <c r="J209" t="n">
-        <v>-5.664</v>
+        <v>-4.1088</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.79</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.3498</v>
+        <v>-0.2298</v>
       </c>
       <c r="J210" t="n">
-        <v>-8.395200000000001</v>
+        <v>-5.5152</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.66</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.5392</v>
+        <v>-0.3546</v>
       </c>
       <c r="J211" t="n">
-        <v>-12.9408</v>
+        <v>-8.510400000000001</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.3</v>
       </c>
       <c r="I212" t="n">
-        <v>0.9052</v>
+        <v>0.8738</v>
       </c>
       <c r="J212" t="n">
-        <v>27.156</v>
+        <v>26.214</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.05</v>
       </c>
       <c r="I213" t="n">
-        <v>0.2356</v>
+        <v>0.1972</v>
       </c>
       <c r="J213" t="n">
-        <v>7.068</v>
+        <v>5.916</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.93</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.3033</v>
+        <v>-0.2599</v>
       </c>
       <c r="J214" t="n">
-        <v>-9.099</v>
+        <v>-7.797</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.88</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.4547</v>
+        <v>-0.4057</v>
       </c>
       <c r="J215" t="n">
-        <v>-13.641</v>
+        <v>-12.171</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.84</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.5644</v>
+        <v>-0.5154</v>
       </c>
       <c r="J216" t="n">
-        <v>-16.932</v>
+        <v>-15.462</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.46</v>
       </c>
       <c r="I217" t="n">
-        <v>0.6972</v>
+        <v>0.8604000000000001</v>
       </c>
       <c r="J217" t="n">
-        <v>20.916</v>
+        <v>25.812</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.11</v>
       </c>
       <c r="I218" t="n">
-        <v>0.22</v>
+        <v>0.2529</v>
       </c>
       <c r="J218" t="n">
-        <v>6.6</v>
+        <v>7.587</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.02</v>
       </c>
       <c r="I219" t="n">
-        <v>0.0274</v>
+        <v>0.0578</v>
       </c>
       <c r="J219" t="n">
-        <v>0.822</v>
+        <v>1.734</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.99</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.0682</v>
+        <v>-0.0261</v>
       </c>
       <c r="J220" t="n">
-        <v>-2.046</v>
+        <v>-0.783</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.73</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.4918</v>
+        <v>-0.3144</v>
       </c>
       <c r="J221" t="n">
-        <v>-14.754</v>
+        <v>-9.432</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.34</v>
       </c>
       <c r="I222" t="n">
-        <v>0.8872</v>
+        <v>0.8868</v>
       </c>
       <c r="J222" t="n">
-        <v>23.9544</v>
+        <v>23.9436</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.29</v>
       </c>
       <c r="I223" t="n">
-        <v>0.7718</v>
+        <v>0.7721</v>
       </c>
       <c r="J223" t="n">
-        <v>20.8386</v>
+        <v>20.8467</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.27</v>
       </c>
       <c r="I224" t="n">
-        <v>0.7235</v>
+        <v>0.7256</v>
       </c>
       <c r="J224" t="n">
-        <v>19.5345</v>
+        <v>19.5912</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>1.15</v>
       </c>
       <c r="I225" t="n">
-        <v>0.3818</v>
+        <v>0.4383</v>
       </c>
       <c r="J225" t="n">
-        <v>10.3086</v>
+        <v>11.8341</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.92</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.4178</v>
+        <v>-0.3429</v>
       </c>
       <c r="J226" t="n">
-        <v>-11.2806</v>
+        <v>-9.2583</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>0.97</v>
       </c>
       <c r="I227" t="n">
-        <v>-0.0381</v>
+        <v>-0.0426</v>
       </c>
       <c r="J227" t="n">
-        <v>-1.0287</v>
+        <v>-1.1502</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>0.96</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.0602</v>
+        <v>-0.0561</v>
       </c>
       <c r="J228" t="n">
-        <v>-1.6254</v>
+        <v>-1.5147</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.91</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.172</v>
+        <v>-0.1147</v>
       </c>
       <c r="J229" t="n">
-        <v>-4.644</v>
+        <v>-3.0969</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.88</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.2304</v>
+        <v>-0.1468</v>
       </c>
       <c r="J230" t="n">
-        <v>-6.2208</v>
+        <v>-3.9636</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.86</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.2654</v>
+        <v>-0.1678</v>
       </c>
       <c r="J231" t="n">
-        <v>-7.1658</v>
+        <v>-4.5306</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.13</v>
       </c>
       <c r="I232" t="n">
-        <v>0.3071</v>
+        <v>0.2539</v>
       </c>
       <c r="J232" t="n">
-        <v>8.291700000000001</v>
+        <v>6.8553</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>0.97</v>
       </c>
       <c r="I233" t="n">
-        <v>-0.04</v>
+        <v>-0.0431</v>
       </c>
       <c r="J233" t="n">
-        <v>-1.08</v>
+        <v>-1.1637</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>0.88</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.2323</v>
+        <v>-0.1472</v>
       </c>
       <c r="J234" t="n">
-        <v>-6.2721</v>
+        <v>-3.9744</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.88</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.2323</v>
+        <v>-0.1472</v>
       </c>
       <c r="J235" t="n">
-        <v>-6.2721</v>
+        <v>-3.9744</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.74</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.4492</v>
+        <v>-0.2883</v>
       </c>
       <c r="J236" t="n">
-        <v>-12.1284</v>
+        <v>-7.7841</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.67</v>
       </c>
       <c r="I237" t="n">
-        <v>0.8922</v>
+        <v>0.8084</v>
       </c>
       <c r="J237" t="n">
-        <v>24.0894</v>
+        <v>21.8268</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.49</v>
       </c>
       <c r="I238" t="n">
-        <v>0.6932</v>
+        <v>0.6143</v>
       </c>
       <c r="J238" t="n">
-        <v>18.7164</v>
+        <v>16.5861</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>1.11</v>
       </c>
       <c r="I239" t="n">
-        <v>0.1547</v>
+        <v>0.1671</v>
       </c>
       <c r="J239" t="n">
-        <v>4.1769</v>
+        <v>4.5117</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.98</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.1269</v>
+        <v>-0.0549</v>
       </c>
       <c r="J240" t="n">
-        <v>-3.4263</v>
+        <v>-1.4823</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.71</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.5357</v>
+        <v>-0.3457</v>
       </c>
       <c r="J241" t="n">
-        <v>-14.4639</v>
+        <v>-9.3339</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.3</v>
       </c>
       <c r="I242" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.8017</v>
       </c>
       <c r="J242" t="n">
-        <v>22.624</v>
+        <v>22.4476</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.23</v>
       </c>
       <c r="I243" t="n">
-        <v>0.6374</v>
+        <v>0.6367</v>
       </c>
       <c r="J243" t="n">
-        <v>17.8472</v>
+        <v>17.8276</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.17</v>
       </c>
       <c r="I244" t="n">
-        <v>0.4611</v>
+        <v>0.4922</v>
       </c>
       <c r="J244" t="n">
-        <v>12.9108</v>
+        <v>13.7816</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>1.12</v>
       </c>
       <c r="I245" t="n">
-        <v>0.3098</v>
+        <v>0.364</v>
       </c>
       <c r="J245" t="n">
-        <v>8.6744</v>
+        <v>10.192</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>1.04</v>
       </c>
       <c r="I246" t="n">
-        <v>0.062</v>
+        <v>0.1262</v>
       </c>
       <c r="J246" t="n">
-        <v>1.736</v>
+        <v>3.5336</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.09</v>
       </c>
       <c r="I247" t="n">
-        <v>0.2631</v>
+        <v>0.2699</v>
       </c>
       <c r="J247" t="n">
-        <v>7.3668</v>
+        <v>7.5572</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.08</v>
       </c>
       <c r="I248" t="n">
-        <v>0.2458</v>
+        <v>0.2479</v>
       </c>
       <c r="J248" t="n">
-        <v>6.8824</v>
+        <v>6.9412</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>0.79</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.3581</v>
+        <v>-0.2323</v>
       </c>
       <c r="J249" t="n">
-        <v>-10.0268</v>
+        <v>-6.5044</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.76</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.4039</v>
+        <v>-0.2616</v>
       </c>
       <c r="J250" t="n">
-        <v>-11.3092</v>
+        <v>-7.3248</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.6</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.6224</v>
+        <v>-0.4135</v>
       </c>
       <c r="J251" t="n">
-        <v>-17.4272</v>
+        <v>-11.578</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.53</v>
       </c>
       <c r="I252" t="n">
-        <v>1.2947</v>
+        <v>1.1866</v>
       </c>
       <c r="J252" t="n">
-        <v>34.9569</v>
+        <v>32.0382</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.44</v>
       </c>
       <c r="I253" t="n">
-        <v>1.1131</v>
+        <v>1.0701</v>
       </c>
       <c r="J253" t="n">
-        <v>30.0537</v>
+        <v>28.8927</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>1.16</v>
       </c>
       <c r="I254" t="n">
-        <v>0.4262</v>
+        <v>0.4674</v>
       </c>
       <c r="J254" t="n">
-        <v>11.5074</v>
+        <v>12.6198</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.3513</v>
+        <v>-0.276</v>
       </c>
       <c r="J255" t="n">
-        <v>-9.485099999999999</v>
+        <v>-7.452</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.8</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.7234</v>
+        <v>-0.6688</v>
       </c>
       <c r="J256" t="n">
-        <v>-19.5318</v>
+        <v>-18.0576</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>0.98</v>
       </c>
       <c r="I257" t="n">
-        <v>0.0114</v>
+        <v>-0.0189</v>
       </c>
       <c r="J257" t="n">
-        <v>0.3078</v>
+        <v>-0.5103</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>0.91</v>
       </c>
       <c r="I258" t="n">
-        <v>-0.1298</v>
+        <v>-0.1087</v>
       </c>
       <c r="J258" t="n">
-        <v>-3.5046</v>
+        <v>-2.9349</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>0.85</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.2506</v>
+        <v>-0.1719</v>
       </c>
       <c r="J259" t="n">
-        <v>-6.7662</v>
+        <v>-4.6413</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.85</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.2506</v>
+        <v>-0.1719</v>
       </c>
       <c r="J260" t="n">
-        <v>-6.7662</v>
+        <v>-4.6413</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.5014999999999999</v>
+        <v>-0.3279</v>
       </c>
       <c r="J261" t="n">
-        <v>-13.5405</v>
+        <v>-8.853300000000001</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.26</v>
       </c>
       <c r="I262" t="n">
-        <v>0.4571</v>
+        <v>0.4106</v>
       </c>
       <c r="J262" t="n">
-        <v>16.4556</v>
+        <v>14.7816</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.21</v>
       </c>
       <c r="I263" t="n">
-        <v>0.3876</v>
+        <v>0.3426</v>
       </c>
       <c r="J263" t="n">
-        <v>13.9536</v>
+        <v>12.3336</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>1.13</v>
       </c>
       <c r="I264" t="n">
-        <v>0.2663</v>
+        <v>0.2285</v>
       </c>
       <c r="J264" t="n">
-        <v>9.5868</v>
+        <v>8.226000000000001</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>0.89</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.2534</v>
+        <v>-0.1486</v>
       </c>
       <c r="J265" t="n">
-        <v>-9.122400000000001</v>
+        <v>-5.3496</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.66</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.5763</v>
+        <v>-0.377</v>
       </c>
       <c r="J266" t="n">
-        <v>-20.7468</v>
+        <v>-13.572</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.35</v>
       </c>
       <c r="I267" t="n">
-        <v>0.5588</v>
+        <v>0.4802</v>
       </c>
       <c r="J267" t="n">
-        <v>20.1168</v>
+        <v>17.2872</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>1.27</v>
       </c>
       <c r="I268" t="n">
-        <v>0.4547</v>
+        <v>0.3841</v>
       </c>
       <c r="J268" t="n">
-        <v>16.3692</v>
+        <v>13.8276</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>1</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.0389</v>
+        <v>-0.0066</v>
       </c>
       <c r="J269" t="n">
-        <v>-1.4004</v>
+        <v>-0.2376</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.92</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.2155</v>
+        <v>-0.1201</v>
       </c>
       <c r="J270" t="n">
-        <v>-7.758</v>
+        <v>-4.3236</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.85</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.3275</v>
+        <v>-0.1967</v>
       </c>
       <c r="J271" t="n">
-        <v>-11.79</v>
+        <v>-7.0812</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.4</v>
       </c>
       <c r="I272" t="n">
-        <v>1.0176</v>
+        <v>1.0063</v>
       </c>
       <c r="J272" t="n">
-        <v>24.4224</v>
+        <v>24.1512</v>
       </c>
     </row>
     <row r="273">
@@ -13309,10 +13309,10 @@
         <v>1.27</v>
       </c>
       <c r="I274" t="n">
-        <v>0.7223000000000001</v>
+        <v>0.7251</v>
       </c>
       <c r="J274" t="n">
-        <v>17.3352</v>
+        <v>17.4024</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>1.03</v>
       </c>
       <c r="I275" t="n">
-        <v>0.0165</v>
+        <v>0.08550000000000001</v>
       </c>
       <c r="J275" t="n">
-        <v>0.396</v>
+        <v>2.052</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.93</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.389</v>
+        <v>-0.3129</v>
       </c>
       <c r="J276" t="n">
-        <v>-9.336</v>
+        <v>-7.5096</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.28</v>
       </c>
       <c r="I277" t="n">
-        <v>0.5384</v>
+        <v>0.6383</v>
       </c>
       <c r="J277" t="n">
-        <v>12.9216</v>
+        <v>15.3192</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>0.83</v>
       </c>
       <c r="I278" t="n">
-        <v>-0.2985</v>
+        <v>-0.1939</v>
       </c>
       <c r="J278" t="n">
-        <v>-7.164</v>
+        <v>-4.6536</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>0.76</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.4079</v>
+        <v>-0.2632</v>
       </c>
       <c r="J279" t="n">
-        <v>-9.7896</v>
+        <v>-6.3168</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.76</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.4079</v>
+        <v>-0.2632</v>
       </c>
       <c r="J280" t="n">
-        <v>-9.7896</v>
+        <v>-6.3168</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.75</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.4225</v>
+        <v>-0.2729</v>
       </c>
       <c r="J281" t="n">
-        <v>-10.14</v>
+        <v>-6.5496</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.61</v>
       </c>
       <c r="I282" t="n">
-        <v>1.459</v>
+        <v>1.2945</v>
       </c>
       <c r="J282" t="n">
-        <v>35.016</v>
+        <v>31.068</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>1.48</v>
       </c>
       <c r="I283" t="n">
-        <v>1.2051</v>
+        <v>1.1274</v>
       </c>
       <c r="J283" t="n">
-        <v>28.9224</v>
+        <v>27.0576</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>1.06</v>
       </c>
       <c r="I284" t="n">
-        <v>0.1373</v>
+        <v>0.1954</v>
       </c>
       <c r="J284" t="n">
-        <v>3.2952</v>
+        <v>4.6896</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>0.86</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.5691000000000001</v>
+        <v>-0.5043</v>
       </c>
       <c r="J285" t="n">
-        <v>-13.6584</v>
+        <v>-12.1032</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.76</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.8117</v>
+        <v>-0.7658</v>
       </c>
       <c r="J286" t="n">
-        <v>-19.4808</v>
+        <v>-18.3792</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.26</v>
       </c>
       <c r="I287" t="n">
-        <v>0.5004</v>
+        <v>0.5862000000000001</v>
       </c>
       <c r="J287" t="n">
-        <v>12.0096</v>
+        <v>14.0688</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>0.96</v>
       </c>
       <c r="I288" t="n">
-        <v>-0.0553</v>
+        <v>-0.0548</v>
       </c>
       <c r="J288" t="n">
-        <v>-1.3272</v>
+        <v>-1.3152</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.097</v>
+        <v>-0.0799</v>
       </c>
       <c r="J289" t="n">
-        <v>-2.328</v>
+        <v>-1.9176</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.79</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.3729</v>
+        <v>-0.2376</v>
       </c>
       <c r="J290" t="n">
-        <v>-8.9496</v>
+        <v>-5.7024</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.58</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.6554</v>
+        <v>-0.4372</v>
       </c>
       <c r="J291" t="n">
-        <v>-15.7296</v>
+        <v>-10.4928</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.65</v>
       </c>
       <c r="I292" t="n">
-        <v>1.4979</v>
+        <v>1.3226</v>
       </c>
       <c r="J292" t="n">
-        <v>37.4475</v>
+        <v>33.065</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.4</v>
       </c>
       <c r="I293" t="n">
-        <v>1.001</v>
+        <v>0.9981</v>
       </c>
       <c r="J293" t="n">
-        <v>25.025</v>
+        <v>24.9525</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>1.13</v>
       </c>
       <c r="I294" t="n">
-        <v>0.3072</v>
+        <v>0.3784</v>
       </c>
       <c r="J294" t="n">
-        <v>7.68</v>
+        <v>9.460000000000001</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>1.01</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.075</v>
+        <v>-0.0007</v>
       </c>
       <c r="J295" t="n">
-        <v>-1.875</v>
+        <v>-0.0175</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>0.95</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.3374</v>
+        <v>-0.2574</v>
       </c>
       <c r="J296" t="n">
-        <v>-8.435</v>
+        <v>-6.435</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>1.01</v>
       </c>
       <c r="I297" t="n">
-        <v>0.09030000000000001</v>
+        <v>0.0618</v>
       </c>
       <c r="J297" t="n">
-        <v>2.2575</v>
+        <v>1.545</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>1.01</v>
       </c>
       <c r="I298" t="n">
-        <v>0.09030000000000001</v>
+        <v>0.0618</v>
       </c>
       <c r="J298" t="n">
-        <v>2.2575</v>
+        <v>1.545</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>0.91</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.1508</v>
+        <v>-0.1132</v>
       </c>
       <c r="J299" t="n">
-        <v>-3.77</v>
+        <v>-2.83</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.78</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.384</v>
+        <v>-0.2459</v>
       </c>
       <c r="J300" t="n">
-        <v>-9.6</v>
+        <v>-6.1475</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.76</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.4135</v>
+        <v>-0.2655</v>
       </c>
       <c r="J301" t="n">
-        <v>-10.3375</v>
+        <v>-6.6375</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>1.27</v>
       </c>
       <c r="I302" t="n">
-        <v>0.4909</v>
+        <v>0.4408</v>
       </c>
       <c r="J302" t="n">
-        <v>14.2361</v>
+        <v>12.7832</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>1.07</v>
       </c>
       <c r="I303" t="n">
-        <v>0.1865</v>
+        <v>0.146</v>
       </c>
       <c r="J303" t="n">
-        <v>5.4085</v>
+        <v>4.234</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>1.03</v>
       </c>
       <c r="I304" t="n">
-        <v>0.1064</v>
+        <v>0.07480000000000001</v>
       </c>
       <c r="J304" t="n">
-        <v>3.0856</v>
+        <v>2.1692</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>0.96</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.0987</v>
+        <v>-0.0606</v>
       </c>
       <c r="J305" t="n">
-        <v>-2.8623</v>
+        <v>-1.7574</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>0.52</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.737</v>
+        <v>-0.4987</v>
       </c>
       <c r="J306" t="n">
-        <v>-21.373</v>
+        <v>-14.4623</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>1.47</v>
       </c>
       <c r="I307" t="n">
-        <v>0.6659</v>
+        <v>0.5895</v>
       </c>
       <c r="J307" t="n">
-        <v>19.3111</v>
+        <v>17.0955</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>1.46</v>
       </c>
       <c r="I308" t="n">
-        <v>0.6541</v>
+        <v>0.5785</v>
       </c>
       <c r="J308" t="n">
-        <v>18.9689</v>
+        <v>16.7765</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>1.27</v>
       </c>
       <c r="I309" t="n">
-        <v>0.4115</v>
+        <v>0.3634</v>
       </c>
       <c r="J309" t="n">
-        <v>11.9335</v>
+        <v>10.5386</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>1.13</v>
       </c>
       <c r="I310" t="n">
-        <v>0.1831</v>
+        <v>0.1928</v>
       </c>
       <c r="J310" t="n">
-        <v>5.3099</v>
+        <v>5.5912</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.7</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.5498</v>
+        <v>-0.3563</v>
       </c>
       <c r="J311" t="n">
-        <v>-15.9442</v>
+        <v>-10.3327</v>
       </c>
     </row>
     <row r="312">
@@ -14829,10 +14829,10 @@
         <v>1.56</v>
       </c>
       <c r="I312" t="n">
-        <v>1.4354</v>
+        <v>1.2786</v>
       </c>
       <c r="J312" t="n">
-        <v>57.416</v>
+        <v>51.144</v>
       </c>
     </row>
     <row r="313">
@@ -14869,10 +14869,10 @@
         <v>0.96</v>
       </c>
       <c r="I313" t="n">
-        <v>-0.2134</v>
+        <v>-0.1694</v>
       </c>
       <c r="J313" t="n">
-        <v>-8.536</v>
+        <v>-6.776</v>
       </c>
     </row>
     <row r="314">
@@ -14909,10 +14909,10 @@
         <v>0.92</v>
       </c>
       <c r="I314" t="n">
-        <v>-0.3468</v>
+        <v>-0.2958</v>
       </c>
       <c r="J314" t="n">
-        <v>-13.872</v>
+        <v>-11.832</v>
       </c>
     </row>
     <row r="315">
@@ -14949,10 +14949,10 @@
         <v>0.86</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.5198</v>
+        <v>-0.4671</v>
       </c>
       <c r="J315" t="n">
-        <v>-20.792</v>
+        <v>-18.684</v>
       </c>
     </row>
     <row r="316">
@@ -14989,10 +14989,10 @@
         <v>0.8</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.6753</v>
+        <v>-0.6271</v>
       </c>
       <c r="J316" t="n">
-        <v>-27.012</v>
+        <v>-25.084</v>
       </c>
     </row>
     <row r="317">
@@ -15029,10 +15029,10 @@
         <v>1.22</v>
       </c>
       <c r="I317" t="n">
-        <v>0.3771</v>
+        <v>0.4466</v>
       </c>
       <c r="J317" t="n">
-        <v>15.084</v>
+        <v>17.864</v>
       </c>
     </row>
     <row r="318">
@@ -15069,10 +15069,10 @@
         <v>1.15</v>
       </c>
       <c r="I318" t="n">
-        <v>0.2703</v>
+        <v>0.3213</v>
       </c>
       <c r="J318" t="n">
-        <v>10.812</v>
+        <v>12.852</v>
       </c>
     </row>
     <row r="319">
@@ -15109,10 +15109,10 @@
         <v>1.14</v>
       </c>
       <c r="I319" t="n">
-        <v>0.2537</v>
+        <v>0.3029</v>
       </c>
       <c r="J319" t="n">
-        <v>10.148</v>
+        <v>12.116</v>
       </c>
     </row>
     <row r="320">
@@ -15149,10 +15149,10 @@
         <v>1.11</v>
       </c>
       <c r="I320" t="n">
-        <v>0.1997</v>
+        <v>0.2468</v>
       </c>
       <c r="J320" t="n">
-        <v>7.988</v>
+        <v>9.872</v>
       </c>
     </row>
     <row r="321">
@@ -15189,10 +15189,10 @@
         <v>0.89</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.2708</v>
+        <v>-0.1564</v>
       </c>
       <c r="J321" t="n">
-        <v>-10.832</v>
+        <v>-6.256</v>
       </c>
     </row>
     <row r="322">
@@ -15229,10 +15229,10 @@
         <v>2.51</v>
       </c>
       <c r="I322" t="n">
-        <v>2.0593</v>
+        <v>1.8338</v>
       </c>
       <c r="J322" t="n">
-        <v>39.1267</v>
+        <v>34.8422</v>
       </c>
     </row>
     <row r="323">
@@ -15269,10 +15269,10 @@
         <v>1.43</v>
       </c>
       <c r="I323" t="n">
-        <v>0.9193</v>
+        <v>1.0097</v>
       </c>
       <c r="J323" t="n">
-        <v>17.4667</v>
+        <v>19.1843</v>
       </c>
     </row>
     <row r="324">
@@ -15309,10 +15309,10 @@
         <v>1.32</v>
       </c>
       <c r="I324" t="n">
-        <v>0.6725</v>
+        <v>0.7903</v>
       </c>
       <c r="J324" t="n">
-        <v>12.7775</v>
+        <v>15.0157</v>
       </c>
     </row>
     <row r="325">
@@ -15349,10 +15349,10 @@
         <v>1.2</v>
       </c>
       <c r="I325" t="n">
-        <v>0.3993</v>
+        <v>0.5086000000000001</v>
       </c>
       <c r="J325" t="n">
-        <v>7.5867</v>
+        <v>9.663399999999999</v>
       </c>
     </row>
     <row r="326">
@@ -15389,10 +15389,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.7558</v>
+        <v>-0.7014</v>
       </c>
       <c r="J326" t="n">
-        <v>-14.3602</v>
+        <v>-13.3266</v>
       </c>
     </row>
     <row r="327">
@@ -15429,10 +15429,10 @@
         <v>1.34</v>
       </c>
       <c r="I327" t="n">
-        <v>0.6677</v>
+        <v>0.8351</v>
       </c>
       <c r="J327" t="n">
-        <v>12.6863</v>
+        <v>15.8669</v>
       </c>
     </row>
     <row r="328">
@@ -15469,10 +15469,10 @@
         <v>0.75</v>
       </c>
       <c r="I328" t="n">
-        <v>-0.3647</v>
+        <v>-0.2576</v>
       </c>
       <c r="J328" t="n">
-        <v>-6.9293</v>
+        <v>-4.8944</v>
       </c>
     </row>
     <row r="329">
@@ -15509,10 +15509,10 @@
         <v>0.67</v>
       </c>
       <c r="I329" t="n">
-        <v>-0.4961</v>
+        <v>-0.3322</v>
       </c>
       <c r="J329" t="n">
-        <v>-9.4259</v>
+        <v>-6.3118</v>
       </c>
     </row>
     <row r="330">
@@ -15549,10 +15549,10 @@
         <v>0.61</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.5812</v>
+        <v>-0.3885</v>
       </c>
       <c r="J330" t="n">
-        <v>-11.0428</v>
+        <v>-7.3815</v>
       </c>
     </row>
     <row r="331">
@@ -15589,10 +15589,10 @@
         <v>0.4</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.8471</v>
+        <v>-0.5834</v>
       </c>
       <c r="J331" t="n">
-        <v>-16.0949</v>
+        <v>-11.0846</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/5257/event_5257_evp_summary.xlsx
+++ b/database/event/5257/event_5257_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.5298</v>
+        <v>5.6309</v>
       </c>
       <c r="C2" t="n">
-        <v>1.0197</v>
+        <v>1.0384</v>
       </c>
       <c r="D2" t="n">
-        <v>1.8584</v>
+        <v>1.9391</v>
       </c>
       <c r="E2" t="n">
-        <v>5.5298</v>
+        <v>5.6309</v>
       </c>
       <c r="F2" t="n">
-        <v>2.9655</v>
+        <v>2.9881</v>
       </c>
       <c r="G2" t="n">
-        <v>2.5643</v>
+        <v>2.6428</v>
       </c>
       <c r="H2" t="n">
-        <v>4.9624</v>
+        <v>4.9647</v>
       </c>
       <c r="I2" t="n">
-        <v>2.5802</v>
+        <v>2.6809</v>
       </c>
       <c r="J2" t="n">
-        <v>2.5643</v>
+        <v>2.6428</v>
       </c>
       <c r="K2" t="n">
         <v>144</v>
@@ -529,7 +529,7 @@
         <v>136</v>
       </c>
       <c r="M2" t="n">
-        <v>5.1445</v>
+        <v>5.3237</v>
       </c>
       <c r="N2" t="n">
         <v>280</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.3524</v>
+        <v>4.4187</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8026</v>
+        <v>0.8148</v>
       </c>
       <c r="D3" t="n">
-        <v>1.3269</v>
+        <v>1.3873</v>
       </c>
       <c r="E3" t="n">
-        <v>4.3524</v>
+        <v>4.4187</v>
       </c>
       <c r="F3" t="n">
-        <v>2.3912</v>
+        <v>2.3277</v>
       </c>
       <c r="G3" t="n">
-        <v>1.9612</v>
+        <v>2.091</v>
       </c>
       <c r="H3" t="n">
-        <v>2.9389</v>
+        <v>2.7856</v>
       </c>
       <c r="I3" t="n">
-        <v>1.5281</v>
+        <v>1.5042</v>
       </c>
       <c r="J3" t="n">
-        <v>1.9612</v>
+        <v>2.091</v>
       </c>
       <c r="K3" t="n">
         <v>154</v>
@@ -575,7 +575,7 @@
         <v>132</v>
       </c>
       <c r="M3" t="n">
-        <v>3.4893</v>
+        <v>3.5952</v>
       </c>
       <c r="N3" t="n">
         <v>286</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.214</v>
+        <v>4.2373</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7771</v>
+        <v>0.7814</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2644</v>
+        <v>1.3047</v>
       </c>
       <c r="E4" t="n">
-        <v>4.214</v>
+        <v>4.2373</v>
       </c>
       <c r="F4" t="n">
-        <v>2.8609</v>
+        <v>2.8046</v>
       </c>
       <c r="G4" t="n">
-        <v>1.3531</v>
+        <v>1.4327</v>
       </c>
       <c r="H4" t="n">
-        <v>4.5939</v>
+        <v>4.3593</v>
       </c>
       <c r="I4" t="n">
-        <v>2.3886</v>
+        <v>2.354</v>
       </c>
       <c r="J4" t="n">
-        <v>1.3531</v>
+        <v>1.4327</v>
       </c>
       <c r="K4" t="n">
         <v>144</v>
@@ -621,7 +621,7 @@
         <v>136</v>
       </c>
       <c r="M4" t="n">
-        <v>3.7417</v>
+        <v>3.7867</v>
       </c>
       <c r="N4" t="n">
         <v>280</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.1988</v>
+        <v>4.2321</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7743</v>
+        <v>0.7804</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2575</v>
+        <v>1.3023</v>
       </c>
       <c r="E5" t="n">
-        <v>4.1988</v>
+        <v>4.2321</v>
       </c>
       <c r="F5" t="n">
-        <v>2.8976</v>
+        <v>2.8058</v>
       </c>
       <c r="G5" t="n">
-        <v>1.3012</v>
+        <v>1.4263</v>
       </c>
       <c r="H5" t="n">
-        <v>4.7231</v>
+        <v>4.363</v>
       </c>
       <c r="I5" t="n">
-        <v>2.4558</v>
+        <v>2.356</v>
       </c>
       <c r="J5" t="n">
-        <v>1.3012</v>
+        <v>1.4263</v>
       </c>
       <c r="K5" t="n">
         <v>146</v>
@@ -667,7 +667,7 @@
         <v>77</v>
       </c>
       <c r="M5" t="n">
-        <v>3.757</v>
+        <v>3.7823</v>
       </c>
       <c r="N5" t="n">
         <v>223</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.8982</v>
+        <v>3.854</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7188</v>
+        <v>0.7107</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1218</v>
+        <v>1.1302</v>
       </c>
       <c r="E6" t="n">
-        <v>3.8982</v>
+        <v>3.854</v>
       </c>
       <c r="F6" t="n">
-        <v>3.5946</v>
+        <v>3.5054</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3036</v>
+        <v>0.3486</v>
       </c>
       <c r="H6" t="n">
-        <v>7.1789</v>
+        <v>6.6716</v>
       </c>
       <c r="I6" t="n">
-        <v>3.7327</v>
+        <v>3.6026</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3036</v>
+        <v>0.3486</v>
       </c>
       <c r="K6" t="n">
         <v>154</v>
@@ -713,7 +713,7 @@
         <v>132</v>
       </c>
       <c r="M6" t="n">
-        <v>4.0363</v>
+        <v>3.9512</v>
       </c>
       <c r="N6" t="n">
         <v>286</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.6528</v>
+        <v>3.6197</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6736</v>
+        <v>0.6675</v>
       </c>
       <c r="D7" t="n">
-        <v>1.011</v>
+        <v>1.0236</v>
       </c>
       <c r="E7" t="n">
-        <v>3.6528</v>
+        <v>3.6197</v>
       </c>
       <c r="F7" t="n">
-        <v>3.128</v>
+        <v>3.0254</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5248</v>
+        <v>0.5943000000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>5.5347</v>
+        <v>5.0879</v>
       </c>
       <c r="I7" t="n">
-        <v>2.8778</v>
+        <v>2.7474</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5248</v>
+        <v>0.5943000000000001</v>
       </c>
       <c r="K7" t="n">
         <v>197</v>
@@ -759,7 +759,7 @@
         <v>81</v>
       </c>
       <c r="M7" t="n">
-        <v>3.4026</v>
+        <v>3.3417</v>
       </c>
       <c r="N7" t="n">
         <v>278</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.236</v>
+        <v>3.2237</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5967</v>
+        <v>0.5945</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8229</v>
+        <v>0.8433</v>
       </c>
       <c r="E8" t="n">
-        <v>3.236</v>
+        <v>3.2237</v>
       </c>
       <c r="F8" t="n">
-        <v>3.0826</v>
+        <v>3.0135</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1534</v>
+        <v>0.2102</v>
       </c>
       <c r="H8" t="n">
-        <v>5.3749</v>
+        <v>5.0484</v>
       </c>
       <c r="I8" t="n">
-        <v>2.7947</v>
+        <v>2.7261</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1534</v>
+        <v>0.2102</v>
       </c>
       <c r="K8" t="n">
         <v>146</v>
@@ -805,7 +805,7 @@
         <v>77</v>
       </c>
       <c r="M8" t="n">
-        <v>2.9481</v>
+        <v>2.9363</v>
       </c>
       <c r="N8" t="n">
         <v>223</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.1996</v>
+        <v>3.2058</v>
       </c>
       <c r="C9" t="n">
-        <v>0.59</v>
+        <v>0.5911999999999999</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8064</v>
+        <v>0.8351</v>
       </c>
       <c r="E9" t="n">
-        <v>3.1996</v>
+        <v>3.2058</v>
       </c>
       <c r="F9" t="n">
-        <v>2.2301</v>
+        <v>2.145</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9695</v>
+        <v>1.0608</v>
       </c>
       <c r="H9" t="n">
-        <v>2.3712</v>
+        <v>2.1828</v>
       </c>
       <c r="I9" t="n">
-        <v>1.2329</v>
+        <v>1.1787</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9695</v>
+        <v>1.0608</v>
       </c>
       <c r="K9" t="n">
         <v>197</v>
@@ -851,7 +851,7 @@
         <v>81</v>
       </c>
       <c r="M9" t="n">
-        <v>2.2024</v>
+        <v>2.2395</v>
       </c>
       <c r="N9" t="n">
         <v>278</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.1146</v>
+        <v>3.1499</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5743</v>
+        <v>0.5809</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7681</v>
+        <v>0.8097</v>
       </c>
       <c r="E10" t="n">
-        <v>3.1146</v>
+        <v>3.1499</v>
       </c>
       <c r="F10" t="n">
-        <v>2.5377</v>
+        <v>2.4936</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5769</v>
+        <v>0.6563</v>
       </c>
       <c r="H10" t="n">
-        <v>3.4551</v>
+        <v>3.333</v>
       </c>
       <c r="I10" t="n">
-        <v>1.7965</v>
+        <v>1.7998</v>
       </c>
       <c r="J10" t="n">
-        <v>0.5769</v>
+        <v>0.6563</v>
       </c>
       <c r="K10" t="n">
         <v>154</v>
@@ -897,7 +897,7 @@
         <v>132</v>
       </c>
       <c r="M10" t="n">
-        <v>2.3734</v>
+        <v>2.4561</v>
       </c>
       <c r="N10" t="n">
         <v>286</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.0594</v>
+        <v>3.0662</v>
       </c>
       <c r="C11" t="n">
-        <v>0.5642</v>
+        <v>0.5654</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7432</v>
+        <v>0.7716</v>
       </c>
       <c r="E11" t="n">
-        <v>3.0594</v>
+        <v>3.0662</v>
       </c>
       <c r="F11" t="n">
-        <v>3.1247</v>
+        <v>3.0414</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.0653</v>
+        <v>0.0248</v>
       </c>
       <c r="H11" t="n">
-        <v>5.5232</v>
+        <v>5.1404</v>
       </c>
       <c r="I11" t="n">
-        <v>2.8718</v>
+        <v>2.7758</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.0653</v>
+        <v>0.0248</v>
       </c>
       <c r="K11" t="n">
         <v>144</v>
@@ -943,7 +943,7 @@
         <v>136</v>
       </c>
       <c r="M11" t="n">
-        <v>2.8065</v>
+        <v>2.8006</v>
       </c>
       <c r="N11" t="n">
         <v>280</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.0318</v>
+        <v>2.9607</v>
       </c>
       <c r="C12" t="n">
-        <v>0.5591</v>
+        <v>0.546</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7307</v>
+        <v>0.7236</v>
       </c>
       <c r="E12" t="n">
-        <v>3.0318</v>
+        <v>2.9607</v>
       </c>
       <c r="F12" t="n">
-        <v>3.1307</v>
+        <v>3.0582</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.0989</v>
+        <v>-0.0975</v>
       </c>
       <c r="H12" t="n">
-        <v>5.5443</v>
+        <v>5.196</v>
       </c>
       <c r="I12" t="n">
-        <v>2.8828</v>
+        <v>2.8058</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.0989</v>
+        <v>-0.0975</v>
       </c>
       <c r="K12" t="n">
         <v>146</v>
@@ -989,7 +989,7 @@
         <v>77</v>
       </c>
       <c r="M12" t="n">
-        <v>2.7839</v>
+        <v>2.7083</v>
       </c>
       <c r="N12" t="n">
         <v>223</v>
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.8627</v>
+        <v>2.7918</v>
       </c>
       <c r="C13" t="n">
-        <v>0.5279</v>
+        <v>0.5148</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6544</v>
+        <v>0.6467000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>2.8627</v>
+        <v>2.7918</v>
       </c>
       <c r="F13" t="n">
-        <v>3.1058</v>
+        <v>3.001</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.2431</v>
+        <v>-0.2092</v>
       </c>
       <c r="H13" t="n">
-        <v>5.4566</v>
+        <v>5.0073</v>
       </c>
       <c r="I13" t="n">
-        <v>2.8372</v>
+        <v>2.7039</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.2431</v>
+        <v>-0.2092</v>
       </c>
       <c r="K13" t="n">
         <v>197</v>
@@ -1035,7 +1035,7 @@
         <v>81</v>
       </c>
       <c r="M13" t="n">
-        <v>2.5941</v>
+        <v>2.4947</v>
       </c>
       <c r="N13" t="n">
         <v>278</v>
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.5854</v>
+        <v>2.4737</v>
       </c>
       <c r="C14" t="n">
-        <v>0.4768</v>
+        <v>0.4562</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5292</v>
+        <v>0.5019</v>
       </c>
       <c r="E14" t="n">
-        <v>2.5854</v>
+        <v>2.4737</v>
       </c>
       <c r="F14" t="n">
-        <v>2.8464</v>
+        <v>2.7671</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.261</v>
+        <v>-0.2934</v>
       </c>
       <c r="H14" t="n">
-        <v>4.5427</v>
+        <v>4.2354</v>
       </c>
       <c r="I14" t="n">
-        <v>2.362</v>
+        <v>2.2871</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.261</v>
+        <v>-0.2934</v>
       </c>
       <c r="K14" t="n">
         <v>144</v>
@@ -1081,7 +1081,7 @@
         <v>136</v>
       </c>
       <c r="M14" t="n">
-        <v>2.101</v>
+        <v>1.9937</v>
       </c>
       <c r="N14" t="n">
         <v>280</v>
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.0383</v>
+        <v>1.8987</v>
       </c>
       <c r="C15" t="n">
-        <v>0.3759</v>
+        <v>0.3501</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2822</v>
+        <v>0.2401</v>
       </c>
       <c r="E15" t="n">
-        <v>2.0383</v>
+        <v>1.8987</v>
       </c>
       <c r="F15" t="n">
-        <v>2.9507</v>
+        <v>2.8425</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.9124</v>
+        <v>-0.9438</v>
       </c>
       <c r="H15" t="n">
-        <v>4.9102</v>
+        <v>4.4843</v>
       </c>
       <c r="I15" t="n">
-        <v>2.5531</v>
+        <v>2.4215</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.9124</v>
+        <v>-0.9438</v>
       </c>
       <c r="K15" t="n">
         <v>197</v>
@@ -1127,7 +1127,7 @@
         <v>81</v>
       </c>
       <c r="M15" t="n">
-        <v>1.6407</v>
+        <v>1.4777</v>
       </c>
       <c r="N15" t="n">
         <v>278</v>
@@ -1136,47 +1136,47 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>FL1T</t>
+          <t>k0nfig</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.7471</v>
+        <v>1.6799</v>
       </c>
       <c r="C16" t="n">
-        <v>0.3222</v>
+        <v>0.3098</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1507</v>
+        <v>0.1405</v>
       </c>
       <c r="E16" t="n">
-        <v>1.7471</v>
+        <v>1.6799</v>
       </c>
       <c r="F16" t="n">
-        <v>1.7471</v>
+        <v>1.3034</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>0.3765</v>
       </c>
       <c r="H16" t="n">
-        <v>1.7471</v>
+        <v>1.3034</v>
       </c>
       <c r="I16" t="n">
-        <v>1.7471</v>
+        <v>0.7038</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>0.3765</v>
       </c>
       <c r="K16" t="n">
-        <v>218</v>
+        <v>146</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="M16" t="n">
-        <v>1.7471</v>
+        <v>1.0803</v>
       </c>
       <c r="N16" t="n">
-        <v>218</v>
+        <v>223</v>
       </c>
     </row>
     <row r="17">
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.691</v>
+        <v>1.6528</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3118</v>
+        <v>0.3048</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1254</v>
+        <v>0.1282</v>
       </c>
       <c r="E17" t="n">
-        <v>1.691</v>
+        <v>1.6528</v>
       </c>
       <c r="F17" t="n">
-        <v>1.691</v>
+        <v>1.6528</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1.691</v>
+        <v>1.6528</v>
       </c>
       <c r="I17" t="n">
-        <v>1.691</v>
+        <v>1.6528</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.691</v>
+        <v>1.6528</v>
       </c>
       <c r="N17" t="n">
         <v>119</v>
@@ -1228,139 +1228,139 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>mir</t>
+          <t>FL1T</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.6313</v>
+        <v>1.6336</v>
       </c>
       <c r="C18" t="n">
-        <v>0.3008</v>
+        <v>0.3012</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0984</v>
+        <v>0.1194</v>
       </c>
       <c r="E18" t="n">
-        <v>1.6313</v>
+        <v>1.6336</v>
       </c>
       <c r="F18" t="n">
-        <v>1.6313</v>
+        <v>1.6336</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1.6313</v>
+        <v>1.6336</v>
       </c>
       <c r="I18" t="n">
-        <v>1.6313</v>
+        <v>1.6336</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>157</v>
+        <v>218</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1.6313</v>
+        <v>1.6336</v>
       </c>
       <c r="N18" t="n">
-        <v>157</v>
+        <v>218</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CRUC1AL</t>
+          <t>mir</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.6269</v>
+        <v>1.6004</v>
       </c>
       <c r="C19" t="n">
-        <v>0.3</v>
+        <v>0.2951</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0965</v>
+        <v>0.1043</v>
       </c>
       <c r="E19" t="n">
-        <v>1.6269</v>
+        <v>1.6004</v>
       </c>
       <c r="F19" t="n">
-        <v>1.6269</v>
+        <v>1.6004</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.6269</v>
+        <v>1.6004</v>
       </c>
       <c r="I19" t="n">
-        <v>1.6269</v>
+        <v>1.6004</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>207</v>
+        <v>157</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.6269</v>
+        <v>1.6004</v>
       </c>
       <c r="N19" t="n">
-        <v>207</v>
+        <v>157</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>k0nfig</t>
+          <t>CRUC1AL</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.6083</v>
+        <v>1.5515</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2966</v>
+        <v>0.2861</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0881</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>1.6083</v>
+        <v>1.5515</v>
       </c>
       <c r="F20" t="n">
-        <v>1.3057</v>
+        <v>1.5515</v>
       </c>
       <c r="G20" t="n">
-        <v>0.3026</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.3057</v>
+        <v>1.5515</v>
       </c>
       <c r="I20" t="n">
-        <v>0.6788999999999999</v>
+        <v>1.5515</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3026</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>146</v>
+        <v>207</v>
       </c>
       <c r="L20" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.9814999999999999</v>
+        <v>1.5515</v>
       </c>
       <c r="N20" t="n">
-        <v>223</v>
+        <v>207</v>
       </c>
     </row>
     <row r="21">
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.3419</v>
+        <v>1.2987</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2475</v>
+        <v>0.2395</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0322</v>
+        <v>-0.033</v>
       </c>
       <c r="E21" t="n">
-        <v>1.3419</v>
+        <v>1.2987</v>
       </c>
       <c r="F21" t="n">
-        <v>1.3419</v>
+        <v>1.2987</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.3419</v>
+        <v>1.2987</v>
       </c>
       <c r="I21" t="n">
-        <v>1.3419</v>
+        <v>1.2987</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.3419</v>
+        <v>1.2987</v>
       </c>
       <c r="N21" t="n">
         <v>218</v>
@@ -1412,47 +1412,47 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>almazer</t>
+          <t>TeSeS</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.3184</v>
+        <v>1.2824</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2431</v>
+        <v>0.2365</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.0428</v>
+        <v>-0.0404</v>
       </c>
       <c r="E22" t="n">
-        <v>1.3184</v>
+        <v>1.2824</v>
       </c>
       <c r="F22" t="n">
-        <v>1.3184</v>
+        <v>2.3812</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>-1.0988</v>
       </c>
       <c r="H22" t="n">
-        <v>1.3184</v>
+        <v>2.9623</v>
       </c>
       <c r="I22" t="n">
-        <v>1.3184</v>
+        <v>1.5996</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>-1.0988</v>
       </c>
       <c r="K22" t="n">
-        <v>218</v>
+        <v>154</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="M22" t="n">
-        <v>1.3184</v>
+        <v>0.5007999999999999</v>
       </c>
       <c r="N22" t="n">
-        <v>218</v>
+        <v>286</v>
       </c>
     </row>
     <row r="23">
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.3101</v>
+        <v>1.1945</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2416</v>
+        <v>0.2203</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.0466</v>
+        <v>-0.0804</v>
       </c>
       <c r="E23" t="n">
-        <v>1.3101</v>
+        <v>1.1945</v>
       </c>
       <c r="F23" t="n">
-        <v>1.3101</v>
+        <v>1.1945</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1.3101</v>
+        <v>1.1945</v>
       </c>
       <c r="I23" t="n">
-        <v>1.3101</v>
+        <v>1.1945</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1.3101</v>
+        <v>1.1945</v>
       </c>
       <c r="N23" t="n">
         <v>207</v>
@@ -1504,47 +1504,47 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>TeSeS</t>
+          <t>almazer</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.2454</v>
+        <v>1.1848</v>
       </c>
       <c r="C24" t="n">
-        <v>0.2297</v>
+        <v>0.2185</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.07580000000000001</v>
+        <v>-0.0849</v>
       </c>
       <c r="E24" t="n">
-        <v>1.2454</v>
+        <v>1.1848</v>
       </c>
       <c r="F24" t="n">
-        <v>2.4243</v>
+        <v>1.1848</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.1789</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>3.0555</v>
+        <v>1.1848</v>
       </c>
       <c r="I24" t="n">
-        <v>1.5887</v>
+        <v>1.1848</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.1789</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>154</v>
+        <v>218</v>
       </c>
       <c r="L24" t="n">
-        <v>132</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.4097999999999999</v>
+        <v>1.1848</v>
       </c>
       <c r="N24" t="n">
-        <v>286</v>
+        <v>218</v>
       </c>
     </row>
     <row r="25">
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.1252</v>
+        <v>1.0701</v>
       </c>
       <c r="C25" t="n">
-        <v>0.2075</v>
+        <v>0.1973</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.13</v>
+        <v>-0.1371</v>
       </c>
       <c r="E25" t="n">
-        <v>1.1252</v>
+        <v>1.0701</v>
       </c>
       <c r="F25" t="n">
-        <v>1.1252</v>
+        <v>1.0701</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1.1252</v>
+        <v>1.0701</v>
       </c>
       <c r="I25" t="n">
-        <v>1.1252</v>
+        <v>1.0701</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1.1252</v>
+        <v>1.0701</v>
       </c>
       <c r="N25" t="n">
         <v>119</v>
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.9464</v>
+        <v>0.7638</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1745</v>
+        <v>0.1408</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.2108</v>
+        <v>-0.2765</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9464</v>
+        <v>0.7638</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9464</v>
+        <v>0.7638</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.9464</v>
+        <v>0.7638</v>
       </c>
       <c r="I26" t="n">
-        <v>0.9464</v>
+        <v>0.7638</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.9464</v>
+        <v>0.7638</v>
       </c>
       <c r="N26" t="n">
         <v>218</v>
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.4547</v>
+        <v>0.4232</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0838</v>
+        <v>0.078</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4327</v>
+        <v>-0.4316</v>
       </c>
       <c r="E27" t="n">
-        <v>0.4547</v>
+        <v>0.4232</v>
       </c>
       <c r="F27" t="n">
-        <v>0.4547</v>
+        <v>0.4232</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.4547</v>
+        <v>0.4232</v>
       </c>
       <c r="I27" t="n">
-        <v>0.4547</v>
+        <v>0.4232</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.4547</v>
+        <v>0.4232</v>
       </c>
       <c r="N27" t="n">
         <v>119</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.4176</v>
+        <v>0.3556</v>
       </c>
       <c r="C28" t="n">
-        <v>0.077</v>
+        <v>0.06560000000000001</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.4495</v>
+        <v>-0.4623</v>
       </c>
       <c r="E28" t="n">
-        <v>0.4176</v>
+        <v>0.3556</v>
       </c>
       <c r="F28" t="n">
-        <v>0.4176</v>
+        <v>0.3556</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.4176</v>
+        <v>0.3556</v>
       </c>
       <c r="I28" t="n">
-        <v>0.4176</v>
+        <v>0.3556</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.4176</v>
+        <v>0.3556</v>
       </c>
       <c r="N28" t="n">
         <v>157</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.3926</v>
+        <v>0.3161</v>
       </c>
       <c r="C29" t="n">
-        <v>0.07240000000000001</v>
+        <v>0.0583</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.4608</v>
+        <v>-0.4803</v>
       </c>
       <c r="E29" t="n">
-        <v>0.3926</v>
+        <v>0.3161</v>
       </c>
       <c r="F29" t="n">
-        <v>0.3926</v>
+        <v>0.3161</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.3926</v>
+        <v>0.3161</v>
       </c>
       <c r="I29" t="n">
-        <v>0.3926</v>
+        <v>0.3161</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.3926</v>
+        <v>0.3161</v>
       </c>
       <c r="N29" t="n">
         <v>207</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.2354</v>
+        <v>0.1979</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0434</v>
+        <v>0.0365</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.5317</v>
+        <v>-0.5341</v>
       </c>
       <c r="E30" t="n">
-        <v>0.2354</v>
+        <v>0.1979</v>
       </c>
       <c r="F30" t="n">
-        <v>0.2354</v>
+        <v>0.1979</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.2354</v>
+        <v>0.1979</v>
       </c>
       <c r="I30" t="n">
-        <v>0.2354</v>
+        <v>0.1979</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0.2354</v>
+        <v>0.1979</v>
       </c>
       <c r="N30" t="n">
         <v>157</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.1301</v>
+        <v>-0.1489</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.024</v>
+        <v>-0.0275</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6967</v>
+        <v>-0.6919999999999999</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.1301</v>
+        <v>-0.1489</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.1301</v>
+        <v>-0.1489</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.1301</v>
+        <v>-0.1489</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.1301</v>
+        <v>-0.1489</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.1301</v>
+        <v>-0.1489</v>
       </c>
       <c r="N31" t="n">
         <v>119</v>
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.3912</v>
+        <v>-0.4295</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0721</v>
+        <v>-0.07920000000000001</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8146</v>
+        <v>-0.8197</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.3912</v>
+        <v>-0.4295</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.3912</v>
+        <v>-0.4295</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.3912</v>
+        <v>-0.4295</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.3912</v>
+        <v>-0.4295</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.3912</v>
+        <v>-0.4295</v>
       </c>
       <c r="N32" t="n">
         <v>119</v>
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.4363</v>
+        <v>-0.4592</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.0805</v>
+        <v>-0.0847</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.835</v>
+        <v>-0.8332000000000001</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.4363</v>
+        <v>-0.4592</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.4363</v>
+        <v>-0.4592</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.4363</v>
+        <v>-0.4592</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.4363</v>
+        <v>-0.4592</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.4363</v>
+        <v>-0.4592</v>
       </c>
       <c r="N33" t="n">
         <v>157</v>
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.4457</v>
+        <v>-0.504</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.0822</v>
+        <v>-0.0929</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8391999999999999</v>
+        <v>-0.8536</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.4457</v>
+        <v>-0.504</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.4457</v>
+        <v>-0.504</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.4457</v>
+        <v>-0.504</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.4457</v>
+        <v>-0.504</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.4457</v>
+        <v>-0.504</v>
       </c>
       <c r="N34" t="n">
         <v>157</v>
@@ -2014,31 +2014,31 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.5474</v>
+        <v>-0.514</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.1009</v>
+        <v>-0.0948</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8851</v>
+        <v>-0.8582</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.5474</v>
+        <v>-0.514</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.8137</v>
+        <v>-0.7907999999999999</v>
       </c>
       <c r="G35" t="n">
-        <v>0.2663</v>
+        <v>0.2768</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.8137</v>
+        <v>-0.7907999999999999</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.4231</v>
+        <v>-0.427</v>
       </c>
       <c r="J35" t="n">
-        <v>0.2663</v>
+        <v>0.2768</v>
       </c>
       <c r="K35" t="n">
         <v>197</v>
@@ -2047,7 +2047,7 @@
         <v>81</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.1568</v>
+        <v>-0.1502</v>
       </c>
       <c r="N35" t="n">
         <v>278</v>
@@ -2060,31 +2060,31 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.5668</v>
+        <v>-0.6187</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.1045</v>
+        <v>-0.1141</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.8939</v>
+        <v>-0.9058</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.5668</v>
+        <v>-0.6187</v>
       </c>
       <c r="F36" t="n">
-        <v>0.0383</v>
+        <v>0.0202</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.6051</v>
+        <v>-0.6389</v>
       </c>
       <c r="H36" t="n">
-        <v>0.0383</v>
+        <v>0.0202</v>
       </c>
       <c r="I36" t="n">
-        <v>0.0199</v>
+        <v>0.0109</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.6051</v>
+        <v>-0.6389</v>
       </c>
       <c r="K36" t="n">
         <v>154</v>
@@ -2093,7 +2093,7 @@
         <v>132</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.5851999999999999</v>
+        <v>-0.628</v>
       </c>
       <c r="N36" t="n">
         <v>286</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.9302</v>
+        <v>-0.9252</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.1715</v>
+        <v>-0.1706</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.058</v>
+        <v>-1.0454</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.9302</v>
+        <v>-0.9252</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.9302</v>
+        <v>-0.9252</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.9302</v>
+        <v>-0.9252</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.9302</v>
+        <v>-0.9252</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.9302</v>
+        <v>-0.9252</v>
       </c>
       <c r="N37" t="n">
         <v>207</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.2221</v>
+        <v>-1.2644</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.2254</v>
+        <v>-0.2332</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.1897</v>
+        <v>-1.1998</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.2221</v>
+        <v>-1.2644</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.2221</v>
+        <v>-1.2644</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.2221</v>
+        <v>-1.2644</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.2221</v>
+        <v>-1.2644</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.2221</v>
+        <v>-1.2644</v>
       </c>
       <c r="N38" t="n">
         <v>218</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.7578</v>
+        <v>-1.8264</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.3241</v>
+        <v>-0.3368</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.4316</v>
+        <v>-1.4556</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.7578</v>
+        <v>-1.8264</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.7578</v>
+        <v>-1.8264</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.7578</v>
+        <v>-1.8264</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.7578</v>
+        <v>-1.8264</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.7578</v>
+        <v>-1.8264</v>
       </c>
       <c r="N39" t="n">
         <v>207</v>
@@ -2244,31 +2244,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-2.1667</v>
+        <v>-1.9567</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.3996</v>
+        <v>-0.3608</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.6162</v>
+        <v>-1.5149</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.1667</v>
+        <v>-1.9567</v>
       </c>
       <c r="F40" t="n">
-        <v>-2.3191</v>
+        <v>-2.1271</v>
       </c>
       <c r="G40" t="n">
-        <v>0.1524</v>
+        <v>0.1704</v>
       </c>
       <c r="H40" t="n">
-        <v>-2.3191</v>
+        <v>-2.1271</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.2058</v>
+        <v>-1.1486</v>
       </c>
       <c r="J40" t="n">
-        <v>0.1524</v>
+        <v>0.1704</v>
       </c>
       <c r="K40" t="n">
         <v>146</v>
@@ -2277,7 +2277,7 @@
         <v>77</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.0534</v>
+        <v>-0.9782000000000001</v>
       </c>
       <c r="N40" t="n">
         <v>223</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-4.5023</v>
+        <v>-3.7893</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.8302</v>
+        <v>-0.6988</v>
       </c>
       <c r="D41" t="n">
-        <v>-2.6706</v>
+        <v>-2.3492</v>
       </c>
       <c r="E41" t="n">
-        <v>-4.5023</v>
+        <v>-3.7893</v>
       </c>
       <c r="F41" t="n">
-        <v>-6.7441</v>
+        <v>-6.0518</v>
       </c>
       <c r="G41" t="n">
-        <v>2.2418</v>
+        <v>2.2625</v>
       </c>
       <c r="H41" t="n">
-        <v>-6.7441</v>
+        <v>-6.0518</v>
       </c>
       <c r="I41" t="n">
-        <v>-3.5066</v>
+        <v>-3.2679</v>
       </c>
       <c r="J41" t="n">
-        <v>2.2418</v>
+        <v>2.2625</v>
       </c>
       <c r="K41" t="n">
         <v>144</v>
@@ -2323,7 +2323,7 @@
         <v>136</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.2648</v>
+        <v>-1.0054</v>
       </c>
       <c r="N41" t="n">
         <v>280</v>
@@ -2429,10 +2429,10 @@
         <v>1.1</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2516</v>
+        <v>0.2563</v>
       </c>
       <c r="J2" t="n">
-        <v>6.7932</v>
+        <v>6.9201</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.09</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2309</v>
+        <v>0.2363</v>
       </c>
       <c r="J3" t="n">
-        <v>6.2343</v>
+        <v>6.3801</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.04</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1201</v>
+        <v>0.1275</v>
       </c>
       <c r="J4" t="n">
-        <v>3.2427</v>
+        <v>3.4425</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.85</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1856</v>
+        <v>-0.1997</v>
       </c>
       <c r="J5" t="n">
-        <v>-5.0112</v>
+        <v>-5.3919</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.82</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2165</v>
+        <v>-0.2306</v>
       </c>
       <c r="J6" t="n">
-        <v>-5.8455</v>
+        <v>-6.2262</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.44</v>
       </c>
       <c r="I7" t="n">
-        <v>1.0796</v>
+        <v>1.0454</v>
       </c>
       <c r="J7" t="n">
-        <v>29.1492</v>
+        <v>28.2258</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.4</v>
       </c>
       <c r="I8" t="n">
-        <v>1.0231</v>
+        <v>0.9677</v>
       </c>
       <c r="J8" t="n">
-        <v>27.6237</v>
+        <v>26.1279</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0322</v>
+        <v>-0.0222</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.8694</v>
+        <v>-0.5994</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0322</v>
+        <v>-0.0222</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.8694</v>
+        <v>-0.5994</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.84</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5538999999999999</v>
+        <v>-0.5201</v>
       </c>
       <c r="J11" t="n">
-        <v>-14.9553</v>
+        <v>-14.0427</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.13</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3378</v>
+        <v>0.3327</v>
       </c>
       <c r="J12" t="n">
-        <v>9.458399999999999</v>
+        <v>9.3156</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>0.99</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.0106</v>
+        <v>-0.0177</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.2968</v>
+        <v>-0.4956</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.98</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.0266</v>
+        <v>-0.0356</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.7448</v>
+        <v>-0.9968</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.82</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2073</v>
+        <v>-0.2234</v>
       </c>
       <c r="J15" t="n">
-        <v>-5.8044</v>
+        <v>-6.2552</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.6</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4185</v>
+        <v>-0.4287</v>
       </c>
       <c r="J16" t="n">
-        <v>-11.718</v>
+        <v>-12.0036</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.28</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7712</v>
+        <v>0.7288</v>
       </c>
       <c r="J17" t="n">
-        <v>21.5936</v>
+        <v>20.4064</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.16</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4759</v>
+        <v>0.4658</v>
       </c>
       <c r="J18" t="n">
-        <v>13.3252</v>
+        <v>13.0424</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.08</v>
       </c>
       <c r="I19" t="n">
-        <v>0.263</v>
+        <v>0.2692</v>
       </c>
       <c r="J19" t="n">
-        <v>7.364</v>
+        <v>7.5376</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.05</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1715</v>
+        <v>0.1827</v>
       </c>
       <c r="J20" t="n">
-        <v>4.802</v>
+        <v>5.1156</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>1.04</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1386</v>
+        <v>0.1512</v>
       </c>
       <c r="J21" t="n">
-        <v>3.8808</v>
+        <v>4.2336</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.14</v>
       </c>
       <c r="I22" t="n">
-        <v>0.258</v>
+        <v>0.2635</v>
       </c>
       <c r="J22" t="n">
-        <v>6.45</v>
+        <v>6.5875</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.14</v>
       </c>
       <c r="I23" t="n">
-        <v>0.258</v>
+        <v>0.2635</v>
       </c>
       <c r="J23" t="n">
-        <v>6.45</v>
+        <v>6.5875</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.87</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1625</v>
+        <v>-0.1768</v>
       </c>
       <c r="J24" t="n">
-        <v>-4.0625</v>
+        <v>-4.42</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.83</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.2042</v>
+        <v>-0.2187</v>
       </c>
       <c r="J25" t="n">
-        <v>-5.105</v>
+        <v>-5.4675</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.83</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.2042</v>
+        <v>-0.2187</v>
       </c>
       <c r="J26" t="n">
-        <v>-5.105</v>
+        <v>-5.4675</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.64</v>
       </c>
       <c r="I27" t="n">
-        <v>0.5965</v>
+        <v>0.6828</v>
       </c>
       <c r="J27" t="n">
-        <v>14.9125</v>
+        <v>17.07</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.39</v>
       </c>
       <c r="I28" t="n">
-        <v>0.4349</v>
+        <v>0.4939</v>
       </c>
       <c r="J28" t="n">
-        <v>10.8725</v>
+        <v>12.3475</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.19</v>
       </c>
       <c r="I29" t="n">
-        <v>0.2711</v>
+        <v>0.2883</v>
       </c>
       <c r="J29" t="n">
-        <v>6.7775</v>
+        <v>7.2075</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>1.07</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1105</v>
+        <v>0.1273</v>
       </c>
       <c r="J30" t="n">
-        <v>2.7625</v>
+        <v>3.1825</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.61</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.4364</v>
+        <v>-0.4414</v>
       </c>
       <c r="J31" t="n">
-        <v>-10.91</v>
+        <v>-11.035</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.55</v>
       </c>
       <c r="I32" t="n">
-        <v>0.9324</v>
+        <v>1.026</v>
       </c>
       <c r="J32" t="n">
-        <v>24.2424</v>
+        <v>26.676</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.34</v>
       </c>
       <c r="I33" t="n">
-        <v>0.6593</v>
+        <v>0.7309</v>
       </c>
       <c r="J33" t="n">
-        <v>17.1418</v>
+        <v>19.0034</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.2</v>
       </c>
       <c r="I34" t="n">
-        <v>0.4675</v>
+        <v>0.5175999999999999</v>
       </c>
       <c r="J34" t="n">
-        <v>12.155</v>
+        <v>13.4576</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.12</v>
       </c>
       <c r="I35" t="n">
-        <v>0.3483</v>
+        <v>0.3618</v>
       </c>
       <c r="J35" t="n">
-        <v>9.0558</v>
+        <v>9.4068</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.77</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.7507</v>
+        <v>-0.6925</v>
       </c>
       <c r="J36" t="n">
-        <v>-19.5182</v>
+        <v>-18.005</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.05</v>
       </c>
       <c r="I37" t="n">
-        <v>0.1788</v>
+        <v>0.1766</v>
       </c>
       <c r="J37" t="n">
-        <v>4.6488</v>
+        <v>4.5916</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>0.96</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.0487</v>
+        <v>-0.0614</v>
       </c>
       <c r="J38" t="n">
-        <v>-1.2662</v>
+        <v>-1.5964</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.96</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.0487</v>
+        <v>-0.0614</v>
       </c>
       <c r="J39" t="n">
-        <v>-1.2662</v>
+        <v>-1.5964</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.68</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.3384</v>
+        <v>-0.3529</v>
       </c>
       <c r="J40" t="n">
-        <v>-8.798400000000001</v>
+        <v>-9.1754</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.67</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.3479</v>
+        <v>-0.362</v>
       </c>
       <c r="J41" t="n">
-        <v>-9.045400000000001</v>
+        <v>-9.412000000000001</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.21</v>
       </c>
       <c r="I42" t="n">
-        <v>0.5083</v>
+        <v>0.5567</v>
       </c>
       <c r="J42" t="n">
-        <v>15.249</v>
+        <v>16.701</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.13</v>
       </c>
       <c r="I43" t="n">
-        <v>0.3844</v>
+        <v>0.4091</v>
       </c>
       <c r="J43" t="n">
-        <v>11.532</v>
+        <v>12.273</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.02</v>
       </c>
       <c r="I44" t="n">
-        <v>0.0867</v>
+        <v>0.0948</v>
       </c>
       <c r="J44" t="n">
-        <v>2.601</v>
+        <v>2.844</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.007900000000000001</v>
+        <v>-0.0053</v>
       </c>
       <c r="J45" t="n">
-        <v>-0.237</v>
+        <v>-0.159</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.84</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.5273</v>
+        <v>-0.5014</v>
       </c>
       <c r="J46" t="n">
-        <v>-15.819</v>
+        <v>-15.042</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.56</v>
       </c>
       <c r="I47" t="n">
-        <v>0.7471</v>
+        <v>0.8339</v>
       </c>
       <c r="J47" t="n">
-        <v>22.413</v>
+        <v>25.017</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>0.99</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.023</v>
+        <v>-0.0271</v>
       </c>
       <c r="J48" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.8129999999999999</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.99</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.023</v>
+        <v>-0.0271</v>
       </c>
       <c r="J49" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.8129999999999999</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.9</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.1376</v>
+        <v>-0.1495</v>
       </c>
       <c r="J50" t="n">
-        <v>-4.128</v>
+        <v>-4.485</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.71</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.3301</v>
+        <v>-0.3411</v>
       </c>
       <c r="J51" t="n">
-        <v>-9.903</v>
+        <v>-10.233</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.74</v>
       </c>
       <c r="I52" t="n">
-        <v>0.6329</v>
+        <v>0.7295</v>
       </c>
       <c r="J52" t="n">
-        <v>12.658</v>
+        <v>14.59</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.42</v>
       </c>
       <c r="I53" t="n">
-        <v>0.4388</v>
+        <v>0.5022</v>
       </c>
       <c r="J53" t="n">
-        <v>8.776</v>
+        <v>10.044</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.3</v>
       </c>
       <c r="I54" t="n">
-        <v>0.3632</v>
+        <v>0.4013</v>
       </c>
       <c r="J54" t="n">
-        <v>7.264</v>
+        <v>8.026</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1.2</v>
       </c>
       <c r="I55" t="n">
-        <v>0.2652</v>
+        <v>0.2867</v>
       </c>
       <c r="J55" t="n">
-        <v>5.304</v>
+        <v>5.734</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>1.17</v>
       </c>
       <c r="I56" t="n">
-        <v>0.2273</v>
+        <v>0.2496</v>
       </c>
       <c r="J56" t="n">
-        <v>4.546</v>
+        <v>4.992</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.1872</v>
+        <v>-0.2102</v>
       </c>
       <c r="J57" t="n">
-        <v>-3.744</v>
+        <v>-4.204</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>0.79</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.2084</v>
+        <v>-0.2309</v>
       </c>
       <c r="J58" t="n">
-        <v>-4.168</v>
+        <v>-4.618</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.72</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.2781</v>
+        <v>-0.2988</v>
       </c>
       <c r="J59" t="n">
-        <v>-5.562</v>
+        <v>-5.976</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.3053</v>
+        <v>-0.3254</v>
       </c>
       <c r="J60" t="n">
-        <v>-6.106</v>
+        <v>-6.508</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.44</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.5373</v>
+        <v>-0.5452</v>
       </c>
       <c r="J61" t="n">
-        <v>-10.746</v>
+        <v>-10.904</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.43</v>
       </c>
       <c r="I62" t="n">
-        <v>0.6423</v>
+        <v>0.7136</v>
       </c>
       <c r="J62" t="n">
-        <v>14.7729</v>
+        <v>16.4128</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>0.99</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.0176</v>
+        <v>-0.023</v>
       </c>
       <c r="J63" t="n">
-        <v>-0.4048</v>
+        <v>-0.529</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>0.97</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.0472</v>
+        <v>-0.0561</v>
       </c>
       <c r="J64" t="n">
-        <v>-1.0856</v>
+        <v>-1.2903</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.74</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.2933</v>
+        <v>-0.3067</v>
       </c>
       <c r="J65" t="n">
-        <v>-6.7459</v>
+        <v>-7.0541</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.67</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.36</v>
+        <v>-0.3715</v>
       </c>
       <c r="J66" t="n">
-        <v>-8.279999999999999</v>
+        <v>-8.544499999999999</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.63</v>
       </c>
       <c r="I67" t="n">
-        <v>1.0297</v>
+        <v>1.1301</v>
       </c>
       <c r="J67" t="n">
-        <v>23.6831</v>
+        <v>25.9923</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.25</v>
       </c>
       <c r="I68" t="n">
-        <v>0.5353</v>
+        <v>0.5943000000000001</v>
       </c>
       <c r="J68" t="n">
-        <v>12.3119</v>
+        <v>13.6689</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.16</v>
       </c>
       <c r="I69" t="n">
-        <v>0.4089</v>
+        <v>0.4502</v>
       </c>
       <c r="J69" t="n">
-        <v>9.4047</v>
+        <v>10.3546</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>1.02</v>
       </c>
       <c r="I70" t="n">
-        <v>0.0454</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="J70" t="n">
-        <v>1.0442</v>
+        <v>1.5226</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.98</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.1467</v>
+        <v>-0.1363</v>
       </c>
       <c r="J71" t="n">
-        <v>-3.3741</v>
+        <v>-3.1349</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.19</v>
       </c>
       <c r="I72" t="n">
-        <v>0.3937</v>
+        <v>0.426</v>
       </c>
       <c r="J72" t="n">
-        <v>13.3858</v>
+        <v>14.484</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.02</v>
       </c>
       <c r="I73" t="n">
-        <v>0.0746</v>
+        <v>0.0795</v>
       </c>
       <c r="J73" t="n">
-        <v>2.5364</v>
+        <v>2.703</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.98</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.0329</v>
+        <v>-0.0404</v>
       </c>
       <c r="J74" t="n">
-        <v>-1.1186</v>
+        <v>-1.3736</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.84</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.1932</v>
+        <v>-0.2079</v>
       </c>
       <c r="J75" t="n">
-        <v>-6.5688</v>
+        <v>-7.0686</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.75</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.2831</v>
+        <v>-0.2969</v>
       </c>
       <c r="J76" t="n">
-        <v>-9.625400000000001</v>
+        <v>-10.0946</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.23</v>
       </c>
       <c r="I77" t="n">
-        <v>0.5293</v>
+        <v>0.5821</v>
       </c>
       <c r="J77" t="n">
-        <v>17.9962</v>
+        <v>19.7914</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.2</v>
       </c>
       <c r="I78" t="n">
-        <v>0.485</v>
+        <v>0.5327</v>
       </c>
       <c r="J78" t="n">
-        <v>16.49</v>
+        <v>18.1118</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.19</v>
       </c>
       <c r="I79" t="n">
-        <v>0.47</v>
+        <v>0.5159</v>
       </c>
       <c r="J79" t="n">
-        <v>15.98</v>
+        <v>17.5406</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1.06</v>
       </c>
       <c r="I80" t="n">
-        <v>0.2126</v>
+        <v>0.2193</v>
       </c>
       <c r="J80" t="n">
-        <v>7.2284</v>
+        <v>7.4562</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.71</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.8708</v>
+        <v>-0.8028999999999999</v>
       </c>
       <c r="J81" t="n">
-        <v>-29.6072</v>
+        <v>-27.2986</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.17</v>
       </c>
       <c r="I82" t="n">
-        <v>0.3994</v>
+        <v>0.3938</v>
       </c>
       <c r="J82" t="n">
-        <v>11.982</v>
+        <v>11.814</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>0.99</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.0166</v>
+        <v>-0.0222</v>
       </c>
       <c r="J83" t="n">
-        <v>-0.498</v>
+        <v>-0.666</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.96</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.0594</v>
+        <v>-0.0697</v>
       </c>
       <c r="J84" t="n">
-        <v>-1.782</v>
+        <v>-2.091</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.84</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.1925</v>
+        <v>-0.2073</v>
       </c>
       <c r="J85" t="n">
-        <v>-5.775</v>
+        <v>-6.219</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.79</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.243</v>
+        <v>-0.2576</v>
       </c>
       <c r="J86" t="n">
-        <v>-7.29</v>
+        <v>-7.728</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.53</v>
       </c>
       <c r="I87" t="n">
-        <v>1.1792</v>
+        <v>1.1448</v>
       </c>
       <c r="J87" t="n">
-        <v>35.376</v>
+        <v>34.344</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.36</v>
       </c>
       <c r="I88" t="n">
-        <v>0.9284</v>
+        <v>0.872</v>
       </c>
       <c r="J88" t="n">
-        <v>27.852</v>
+        <v>26.16</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.15</v>
       </c>
       <c r="I89" t="n">
-        <v>0.4367</v>
+        <v>0.4333</v>
       </c>
       <c r="J89" t="n">
-        <v>13.101</v>
+        <v>12.999</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>1.13</v>
       </c>
       <c r="I90" t="n">
-        <v>0.3843</v>
+        <v>0.3855</v>
       </c>
       <c r="J90" t="n">
-        <v>11.529</v>
+        <v>11.565</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.84</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.5705</v>
+        <v>-0.5318000000000001</v>
       </c>
       <c r="J91" t="n">
-        <v>-17.115</v>
+        <v>-15.954</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.08</v>
       </c>
       <c r="I92" t="n">
-        <v>0.218</v>
+        <v>0.2219</v>
       </c>
       <c r="J92" t="n">
-        <v>5.668</v>
+        <v>5.7694</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.04</v>
       </c>
       <c r="I93" t="n">
-        <v>0.1273</v>
+        <v>0.1327</v>
       </c>
       <c r="J93" t="n">
-        <v>3.3098</v>
+        <v>3.4502</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.98</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.0323</v>
+        <v>-0.0399</v>
       </c>
       <c r="J94" t="n">
-        <v>-0.8398</v>
+        <v>-1.0374</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.9</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.1288</v>
+        <v>-0.1427</v>
       </c>
       <c r="J95" t="n">
-        <v>-3.3488</v>
+        <v>-3.7102</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.75</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.2824</v>
+        <v>-0.2963</v>
       </c>
       <c r="J96" t="n">
-        <v>-7.3424</v>
+        <v>-7.7038</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.34</v>
       </c>
       <c r="I97" t="n">
-        <v>0.89</v>
+        <v>0.8366</v>
       </c>
       <c r="J97" t="n">
-        <v>23.14</v>
+        <v>21.7516</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.24</v>
       </c>
       <c r="I98" t="n">
-        <v>0.6576</v>
+        <v>0.632</v>
       </c>
       <c r="J98" t="n">
-        <v>17.0976</v>
+        <v>16.432</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.17</v>
       </c>
       <c r="I99" t="n">
-        <v>0.4905</v>
+        <v>0.4815</v>
       </c>
       <c r="J99" t="n">
-        <v>12.753</v>
+        <v>12.519</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>1.14</v>
       </c>
       <c r="I100" t="n">
-        <v>0.4145</v>
+        <v>0.4122</v>
       </c>
       <c r="J100" t="n">
-        <v>10.777</v>
+        <v>10.7172</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>1.03</v>
       </c>
       <c r="I101" t="n">
-        <v>0.0885</v>
+        <v>0.1069</v>
       </c>
       <c r="J101" t="n">
-        <v>2.301</v>
+        <v>2.7794</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>0.74</v>
       </c>
       <c r="I102" t="n">
-        <v>-0.2255</v>
+        <v>-0.2541</v>
       </c>
       <c r="J102" t="n">
-        <v>-4.2845</v>
+        <v>-4.8279</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>0.62</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.3495</v>
+        <v>-0.3719</v>
       </c>
       <c r="J103" t="n">
-        <v>-6.6405</v>
+        <v>-7.0661</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.53</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.4305</v>
+        <v>-0.4488</v>
       </c>
       <c r="J104" t="n">
-        <v>-8.179500000000001</v>
+        <v>-8.527200000000001</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.52</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.4397</v>
+        <v>-0.4575</v>
       </c>
       <c r="J105" t="n">
-        <v>-8.3543</v>
+        <v>-8.692500000000001</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.42</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.5342</v>
+        <v>-0.5454</v>
       </c>
       <c r="J106" t="n">
-        <v>-10.1498</v>
+        <v>-10.3626</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.79</v>
       </c>
       <c r="I107" t="n">
-        <v>1.4242</v>
+        <v>1.4176</v>
       </c>
       <c r="J107" t="n">
-        <v>27.0598</v>
+        <v>26.9344</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.73</v>
       </c>
       <c r="I108" t="n">
-        <v>1.3562</v>
+        <v>1.3454</v>
       </c>
       <c r="J108" t="n">
-        <v>25.7678</v>
+        <v>25.5626</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.63</v>
       </c>
       <c r="I109" t="n">
-        <v>1.2418</v>
+        <v>1.2232</v>
       </c>
       <c r="J109" t="n">
-        <v>23.5942</v>
+        <v>23.2408</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>1.4</v>
       </c>
       <c r="I110" t="n">
-        <v>0.9492</v>
+        <v>0.9035</v>
       </c>
       <c r="J110" t="n">
-        <v>18.0348</v>
+        <v>17.1665</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>1.05</v>
       </c>
       <c r="I111" t="n">
-        <v>0.08160000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="J111" t="n">
-        <v>1.5504</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.35</v>
       </c>
       <c r="I112" t="n">
-        <v>0.7074</v>
+        <v>0.6784</v>
       </c>
       <c r="J112" t="n">
-        <v>21.222</v>
+        <v>20.352</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.01</v>
       </c>
       <c r="I113" t="n">
-        <v>0.0392</v>
+        <v>0.0444</v>
       </c>
       <c r="J113" t="n">
-        <v>1.176</v>
+        <v>1.332</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.99</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.02</v>
+        <v>-0.0248</v>
       </c>
       <c r="J114" t="n">
-        <v>-0.6</v>
+        <v>-0.744</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.85</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.1868</v>
+        <v>-0.2006</v>
       </c>
       <c r="J115" t="n">
-        <v>-5.604</v>
+        <v>-6.018</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.75</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.2871</v>
+        <v>-0.3</v>
       </c>
       <c r="J116" t="n">
-        <v>-8.613</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.1</v>
       </c>
       <c r="I117" t="n">
-        <v>0.3496</v>
+        <v>0.3424</v>
       </c>
       <c r="J117" t="n">
-        <v>10.488</v>
+        <v>10.272</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.01</v>
       </c>
       <c r="I118" t="n">
-        <v>0.0538</v>
+        <v>0.059</v>
       </c>
       <c r="J118" t="n">
-        <v>1.614</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>0.97</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.1295</v>
+        <v>-0.1351</v>
       </c>
       <c r="J119" t="n">
-        <v>-3.885</v>
+        <v>-4.053</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.96</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.1638</v>
+        <v>-0.1684</v>
       </c>
       <c r="J120" t="n">
-        <v>-4.914</v>
+        <v>-5.052</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.95</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.1967</v>
+        <v>-0.1999</v>
       </c>
       <c r="J121" t="n">
-        <v>-5.901</v>
+        <v>-5.997</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.63</v>
       </c>
       <c r="I122" t="n">
-        <v>1.3394</v>
+        <v>1.3093</v>
       </c>
       <c r="J122" t="n">
-        <v>40.182</v>
+        <v>39.279</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.03</v>
       </c>
       <c r="I123" t="n">
-        <v>0.11</v>
+        <v>0.1218</v>
       </c>
       <c r="J123" t="n">
-        <v>3.3</v>
+        <v>3.654</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.01</v>
       </c>
       <c r="I124" t="n">
-        <v>0.0323</v>
+        <v>0.0443</v>
       </c>
       <c r="J124" t="n">
-        <v>0.969</v>
+        <v>1.329</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.92</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.3176</v>
+        <v>-0.3068</v>
       </c>
       <c r="J125" t="n">
-        <v>-9.528</v>
+        <v>-9.204000000000001</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.9</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.3767</v>
+        <v>-0.3613</v>
       </c>
       <c r="J126" t="n">
-        <v>-11.301</v>
+        <v>-10.839</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.36</v>
       </c>
       <c r="I127" t="n">
-        <v>0.7194</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="J127" t="n">
-        <v>21.582</v>
+        <v>20.7</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.18</v>
       </c>
       <c r="I128" t="n">
-        <v>0.4011</v>
+        <v>0.3988</v>
       </c>
       <c r="J128" t="n">
-        <v>12.033</v>
+        <v>11.964</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.03</v>
       </c>
       <c r="I129" t="n">
-        <v>0.0915</v>
+        <v>0.0997</v>
       </c>
       <c r="J129" t="n">
-        <v>2.745</v>
+        <v>2.991</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1.01</v>
       </c>
       <c r="I130" t="n">
-        <v>0.0375</v>
+        <v>0.0432</v>
       </c>
       <c r="J130" t="n">
-        <v>1.125</v>
+        <v>1.296</v>
       </c>
     </row>
     <row r="131">
@@ -7629,10 +7629,10 @@
         <v>1.3</v>
       </c>
       <c r="I132" t="n">
-        <v>0.8088</v>
+        <v>0.7635999999999999</v>
       </c>
       <c r="J132" t="n">
-        <v>23.4552</v>
+        <v>22.1444</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.16</v>
       </c>
       <c r="I133" t="n">
-        <v>0.4705</v>
+        <v>0.4621</v>
       </c>
       <c r="J133" t="n">
-        <v>13.6445</v>
+        <v>13.4009</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.16</v>
       </c>
       <c r="I134" t="n">
-        <v>0.4705</v>
+        <v>0.4621</v>
       </c>
       <c r="J134" t="n">
-        <v>13.6445</v>
+        <v>13.4009</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.08</v>
       </c>
       <c r="I135" t="n">
-        <v>0.2567</v>
+        <v>0.2649</v>
       </c>
       <c r="J135" t="n">
-        <v>7.4443</v>
+        <v>7.6821</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>1.05</v>
       </c>
       <c r="I136" t="n">
-        <v>0.1646</v>
+        <v>0.178</v>
       </c>
       <c r="J136" t="n">
-        <v>4.7734</v>
+        <v>5.162</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>0.9</v>
       </c>
       <c r="I137" t="n">
-        <v>-0.1134</v>
+        <v>-0.1309</v>
       </c>
       <c r="J137" t="n">
-        <v>-3.2886</v>
+        <v>-3.7961</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>0.83</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.1879</v>
+        <v>-0.2063</v>
       </c>
       <c r="J138" t="n">
-        <v>-5.4491</v>
+        <v>-5.9827</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.82</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.1977</v>
+        <v>-0.2161</v>
       </c>
       <c r="J139" t="n">
-        <v>-5.7333</v>
+        <v>-6.2669</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.8</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.2165</v>
+        <v>-0.235</v>
       </c>
       <c r="J140" t="n">
-        <v>-6.2785</v>
+        <v>-6.815</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.71</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.3027</v>
+        <v>-0.3197</v>
       </c>
       <c r="J141" t="n">
-        <v>-8.7783</v>
+        <v>-9.2713</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.22</v>
       </c>
       <c r="I142" t="n">
-        <v>0.6442</v>
+        <v>0.6131</v>
       </c>
       <c r="J142" t="n">
-        <v>19.326</v>
+        <v>18.393</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.21</v>
       </c>
       <c r="I143" t="n">
-        <v>0.619</v>
+        <v>0.5908</v>
       </c>
       <c r="J143" t="n">
-        <v>18.57</v>
+        <v>17.724</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.18</v>
       </c>
       <c r="I144" t="n">
-        <v>0.5426</v>
+        <v>0.5226</v>
       </c>
       <c r="J144" t="n">
-        <v>16.278</v>
+        <v>15.678</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1.16</v>
       </c>
       <c r="I145" t="n">
-        <v>0.4906</v>
+        <v>0.4759</v>
       </c>
       <c r="J145" t="n">
-        <v>14.718</v>
+        <v>14.277</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.57</v>
       </c>
       <c r="I146" t="n">
-        <v>-1.2031</v>
+        <v>-1.0899</v>
       </c>
       <c r="J146" t="n">
-        <v>-36.093</v>
+        <v>-32.697</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.19</v>
       </c>
       <c r="I147" t="n">
-        <v>0.4178</v>
+        <v>0.4148</v>
       </c>
       <c r="J147" t="n">
-        <v>12.534</v>
+        <v>12.444</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.04</v>
       </c>
       <c r="I148" t="n">
-        <v>0.1146</v>
+        <v>0.1236</v>
       </c>
       <c r="J148" t="n">
-        <v>3.438</v>
+        <v>3.708</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.04</v>
       </c>
       <c r="I149" t="n">
-        <v>0.1146</v>
+        <v>0.1236</v>
       </c>
       <c r="J149" t="n">
-        <v>3.438</v>
+        <v>3.708</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.89</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.1462</v>
+        <v>-0.1589</v>
       </c>
       <c r="J150" t="n">
-        <v>-4.386</v>
+        <v>-4.767</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.88</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.157</v>
+        <v>-0.17</v>
       </c>
       <c r="J151" t="n">
-        <v>-4.71</v>
+        <v>-5.1</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.71</v>
       </c>
       <c r="I152" t="n">
-        <v>1.3855</v>
+        <v>1.3671</v>
       </c>
       <c r="J152" t="n">
-        <v>36.023</v>
+        <v>35.5446</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.65</v>
       </c>
       <c r="I153" t="n">
-        <v>1.3125</v>
+        <v>1.2898</v>
       </c>
       <c r="J153" t="n">
-        <v>34.125</v>
+        <v>33.5348</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.16</v>
       </c>
       <c r="I154" t="n">
-        <v>0.4485</v>
+        <v>0.4471</v>
       </c>
       <c r="J154" t="n">
-        <v>11.661</v>
+        <v>11.6246</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.93</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.33</v>
+        <v>-0.3084</v>
       </c>
       <c r="J155" t="n">
-        <v>-8.58</v>
+        <v>-8.0184</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.88</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.4763</v>
+        <v>-0.4434</v>
       </c>
       <c r="J156" t="n">
-        <v>-12.3838</v>
+        <v>-11.5284</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.17</v>
       </c>
       <c r="I157" t="n">
-        <v>0.4296</v>
+        <v>0.4161</v>
       </c>
       <c r="J157" t="n">
-        <v>11.1696</v>
+        <v>10.8186</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>0.97</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.037</v>
+        <v>-0.0482</v>
       </c>
       <c r="J158" t="n">
-        <v>-0.962</v>
+        <v>-1.2532</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>0.85</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.1737</v>
+        <v>-0.1905</v>
       </c>
       <c r="J159" t="n">
-        <v>-4.5162</v>
+        <v>-4.953</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.72</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.3019</v>
+        <v>-0.3172</v>
       </c>
       <c r="J160" t="n">
-        <v>-7.8494</v>
+        <v>-8.247199999999999</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.67</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.3495</v>
+        <v>-0.3632</v>
       </c>
       <c r="J161" t="n">
-        <v>-9.087</v>
+        <v>-9.443199999999999</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.54</v>
       </c>
       <c r="I162" t="n">
-        <v>1.1904</v>
+        <v>1.157</v>
       </c>
       <c r="J162" t="n">
-        <v>34.5216</v>
+        <v>33.553</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.33</v>
       </c>
       <c r="I163" t="n">
-        <v>0.8598</v>
+        <v>0.8115</v>
       </c>
       <c r="J163" t="n">
-        <v>24.9342</v>
+        <v>23.5335</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.3</v>
       </c>
       <c r="I164" t="n">
-        <v>0.7913</v>
+        <v>0.7514999999999999</v>
       </c>
       <c r="J164" t="n">
-        <v>22.9477</v>
+        <v>21.7935</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1.04</v>
       </c>
       <c r="I165" t="n">
-        <v>0.1172</v>
+        <v>0.1364</v>
       </c>
       <c r="J165" t="n">
-        <v>3.3988</v>
+        <v>3.9556</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.83</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.5986</v>
+        <v>-0.5567</v>
       </c>
       <c r="J166" t="n">
-        <v>-17.3594</v>
+        <v>-16.1443</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.12</v>
       </c>
       <c r="I167" t="n">
-        <v>0.3108</v>
+        <v>0.3086</v>
       </c>
       <c r="J167" t="n">
-        <v>9.013199999999999</v>
+        <v>8.949400000000001</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>0.98</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.0291</v>
+        <v>-0.0375</v>
       </c>
       <c r="J168" t="n">
-        <v>-0.8439</v>
+        <v>-1.0875</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.9</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.126</v>
+        <v>-0.1406</v>
       </c>
       <c r="J169" t="n">
-        <v>-3.654</v>
+        <v>-4.0774</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.84</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.1891</v>
+        <v>-0.2048</v>
       </c>
       <c r="J170" t="n">
-        <v>-5.4839</v>
+        <v>-5.9392</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.77</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.2593</v>
+        <v>-0.2744</v>
       </c>
       <c r="J171" t="n">
-        <v>-7.5197</v>
+        <v>-7.9576</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.22</v>
       </c>
       <c r="I172" t="n">
-        <v>0.4523</v>
+        <v>0.4333</v>
       </c>
       <c r="J172" t="n">
-        <v>9.4983</v>
+        <v>9.099299999999999</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>0.8</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.2122</v>
+        <v>-0.2318</v>
       </c>
       <c r="J173" t="n">
-        <v>-4.4562</v>
+        <v>-4.8678</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.74</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.2683</v>
+        <v>-0.2874</v>
       </c>
       <c r="J174" t="n">
-        <v>-5.6343</v>
+        <v>-6.0354</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.72</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.2871</v>
+        <v>-0.3057</v>
       </c>
       <c r="J175" t="n">
-        <v>-6.0291</v>
+        <v>-6.4197</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.36</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.6217</v>
+        <v>-0.6221</v>
       </c>
       <c r="J176" t="n">
-        <v>-13.0557</v>
+        <v>-13.0641</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.6</v>
       </c>
       <c r="I177" t="n">
-        <v>0.7145</v>
+        <v>0.7122000000000001</v>
       </c>
       <c r="J177" t="n">
-        <v>15.0045</v>
+        <v>14.9562</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.44</v>
       </c>
       <c r="I178" t="n">
-        <v>0.544</v>
+        <v>0.553</v>
       </c>
       <c r="J178" t="n">
-        <v>11.424</v>
+        <v>11.613</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.34</v>
       </c>
       <c r="I179" t="n">
-        <v>0.4344</v>
+        <v>0.449</v>
       </c>
       <c r="J179" t="n">
-        <v>9.122400000000001</v>
+        <v>9.429</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.04</v>
       </c>
       <c r="I180" t="n">
-        <v>0.0502</v>
+        <v>0.0682</v>
       </c>
       <c r="J180" t="n">
-        <v>1.0542</v>
+        <v>1.4322</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.98</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.06320000000000001</v>
+        <v>-0.0638</v>
       </c>
       <c r="J181" t="n">
-        <v>-1.3272</v>
+        <v>-1.3398</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.43</v>
       </c>
       <c r="I182" t="n">
-        <v>1.0351</v>
+        <v>0.9862</v>
       </c>
       <c r="J182" t="n">
-        <v>25.8775</v>
+        <v>24.655</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.26</v>
       </c>
       <c r="I183" t="n">
-        <v>0.6886</v>
+        <v>0.6627999999999999</v>
       </c>
       <c r="J183" t="n">
-        <v>17.215</v>
+        <v>16.57</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.24</v>
       </c>
       <c r="I184" t="n">
-        <v>0.6428</v>
+        <v>0.622</v>
       </c>
       <c r="J184" t="n">
-        <v>16.07</v>
+        <v>15.55</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>1.24</v>
       </c>
       <c r="I185" t="n">
-        <v>0.6428</v>
+        <v>0.622</v>
       </c>
       <c r="J185" t="n">
-        <v>16.07</v>
+        <v>15.55</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>1.19</v>
       </c>
       <c r="I186" t="n">
-        <v>0.5229</v>
+        <v>0.5145</v>
       </c>
       <c r="J186" t="n">
-        <v>13.0725</v>
+        <v>12.8625</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.23</v>
       </c>
       <c r="I187" t="n">
-        <v>0.5316</v>
+        <v>0.5123</v>
       </c>
       <c r="J187" t="n">
-        <v>13.29</v>
+        <v>12.8075</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>0.99</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.0106</v>
+        <v>-0.0177</v>
       </c>
       <c r="J188" t="n">
-        <v>-0.265</v>
+        <v>-0.4425</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.86</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.1665</v>
+        <v>-0.1824</v>
       </c>
       <c r="J189" t="n">
-        <v>-4.1625</v>
+        <v>-4.56</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.74</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.2863</v>
+        <v>-0.3013</v>
       </c>
       <c r="J190" t="n">
-        <v>-7.1575</v>
+        <v>-7.5325</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.7</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.3247</v>
+        <v>-0.3386</v>
       </c>
       <c r="J191" t="n">
-        <v>-8.1175</v>
+        <v>-8.465</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>0.65</v>
       </c>
       <c r="I192" t="n">
-        <v>-0.2957</v>
+        <v>-0.3249</v>
       </c>
       <c r="J192" t="n">
-        <v>-4.7312</v>
+        <v>-5.1984</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>0.63</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.3173</v>
+        <v>-0.3451</v>
       </c>
       <c r="J193" t="n">
-        <v>-5.0768</v>
+        <v>-5.5216</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>0.43</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.5093</v>
+        <v>-0.5246</v>
       </c>
       <c r="J194" t="n">
-        <v>-8.1488</v>
+        <v>-8.393599999999999</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.39</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.548</v>
+        <v>-0.5602</v>
       </c>
       <c r="J195" t="n">
-        <v>-8.768000000000001</v>
+        <v>-8.963200000000001</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.38</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.5578</v>
+        <v>-0.5692</v>
       </c>
       <c r="J196" t="n">
-        <v>-8.924799999999999</v>
+        <v>-9.107200000000001</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>2.11</v>
       </c>
       <c r="I197" t="n">
-        <v>1.0858</v>
+        <v>1.0872</v>
       </c>
       <c r="J197" t="n">
-        <v>17.3728</v>
+        <v>17.3952</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.65</v>
       </c>
       <c r="I198" t="n">
-        <v>0.7184</v>
+        <v>0.7238</v>
       </c>
       <c r="J198" t="n">
-        <v>11.4944</v>
+        <v>11.5808</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.54</v>
       </c>
       <c r="I199" t="n">
-        <v>0.6124000000000001</v>
+        <v>0.6242</v>
       </c>
       <c r="J199" t="n">
-        <v>9.798400000000001</v>
+        <v>9.9872</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>1.52</v>
       </c>
       <c r="I200" t="n">
-        <v>0.5923</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="J200" t="n">
-        <v>9.476800000000001</v>
+        <v>9.684799999999999</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>1.41</v>
       </c>
       <c r="I201" t="n">
-        <v>0.4779</v>
+        <v>0.4971</v>
       </c>
       <c r="J201" t="n">
-        <v>7.6464</v>
+        <v>7.9536</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.7</v>
       </c>
       <c r="I202" t="n">
-        <v>1.3702</v>
+        <v>1.3514</v>
       </c>
       <c r="J202" t="n">
-        <v>32.8848</v>
+        <v>32.4336</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.54</v>
       </c>
       <c r="I203" t="n">
-        <v>1.1742</v>
+        <v>1.1427</v>
       </c>
       <c r="J203" t="n">
-        <v>28.1808</v>
+        <v>27.4248</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.2</v>
       </c>
       <c r="I204" t="n">
-        <v>0.5462</v>
+        <v>0.5357</v>
       </c>
       <c r="J204" t="n">
-        <v>13.1088</v>
+        <v>12.8568</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>1.07</v>
       </c>
       <c r="I205" t="n">
-        <v>0.1962</v>
+        <v>0.2156</v>
       </c>
       <c r="J205" t="n">
-        <v>4.7088</v>
+        <v>5.1744</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.88</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.479</v>
+        <v>-0.4453</v>
       </c>
       <c r="J206" t="n">
-        <v>-11.496</v>
+        <v>-10.6872</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>0.98</v>
       </c>
       <c r="I207" t="n">
-        <v>-0.0167</v>
+        <v>-0.0279</v>
       </c>
       <c r="J207" t="n">
-        <v>-0.4008</v>
+        <v>-0.6696</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I208" t="n">
-        <v>-0.0712</v>
+        <v>-0.0861</v>
       </c>
       <c r="J208" t="n">
-        <v>-1.7088</v>
+        <v>-2.0664</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>0.85</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.1712</v>
+        <v>-0.1886</v>
       </c>
       <c r="J209" t="n">
-        <v>-4.1088</v>
+        <v>-4.5264</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.79</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.2298</v>
+        <v>-0.2474</v>
       </c>
       <c r="J210" t="n">
-        <v>-5.5152</v>
+        <v>-5.9376</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.66</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.3546</v>
+        <v>-0.3689</v>
       </c>
       <c r="J211" t="n">
-        <v>-8.510400000000001</v>
+        <v>-8.8536</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.3</v>
       </c>
       <c r="I212" t="n">
-        <v>0.8738</v>
+        <v>0.8091</v>
       </c>
       <c r="J212" t="n">
-        <v>26.214</v>
+        <v>24.273</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.05</v>
       </c>
       <c r="I213" t="n">
-        <v>0.1972</v>
+        <v>0.2003</v>
       </c>
       <c r="J213" t="n">
-        <v>5.916</v>
+        <v>6.009</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.93</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.2599</v>
+        <v>-0.2595</v>
       </c>
       <c r="J214" t="n">
-        <v>-7.797</v>
+        <v>-7.785</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.88</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.4057</v>
+        <v>-0.394</v>
       </c>
       <c r="J215" t="n">
-        <v>-12.171</v>
+        <v>-11.82</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.84</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.5154</v>
+        <v>-0.4931</v>
       </c>
       <c r="J216" t="n">
-        <v>-15.462</v>
+        <v>-14.793</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.46</v>
       </c>
       <c r="I217" t="n">
-        <v>0.8604000000000001</v>
+        <v>0.8202</v>
       </c>
       <c r="J217" t="n">
-        <v>25.812</v>
+        <v>24.606</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.11</v>
       </c>
       <c r="I218" t="n">
-        <v>0.2529</v>
+        <v>0.262</v>
       </c>
       <c r="J218" t="n">
-        <v>7.587</v>
+        <v>7.86</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.02</v>
       </c>
       <c r="I219" t="n">
-        <v>0.0578</v>
+        <v>0.06759999999999999</v>
       </c>
       <c r="J219" t="n">
-        <v>1.734</v>
+        <v>2.028</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.99</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.0261</v>
+        <v>-0.0295</v>
       </c>
       <c r="J220" t="n">
-        <v>-0.783</v>
+        <v>-0.885</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.73</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.3144</v>
+        <v>-0.3252</v>
       </c>
       <c r="J221" t="n">
-        <v>-9.432</v>
+        <v>-9.756</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.34</v>
       </c>
       <c r="I222" t="n">
-        <v>0.8868</v>
+        <v>0.8343</v>
       </c>
       <c r="J222" t="n">
-        <v>23.9436</v>
+        <v>22.5261</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.29</v>
       </c>
       <c r="I223" t="n">
-        <v>0.7721</v>
+        <v>0.7338</v>
       </c>
       <c r="J223" t="n">
-        <v>20.8467</v>
+        <v>19.8126</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.27</v>
       </c>
       <c r="I224" t="n">
-        <v>0.7256</v>
+        <v>0.6928</v>
       </c>
       <c r="J224" t="n">
-        <v>19.5912</v>
+        <v>18.7056</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>1.15</v>
       </c>
       <c r="I225" t="n">
-        <v>0.4383</v>
+        <v>0.4344</v>
       </c>
       <c r="J225" t="n">
-        <v>11.8341</v>
+        <v>11.7288</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.92</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.3429</v>
+        <v>-0.3245</v>
       </c>
       <c r="J226" t="n">
-        <v>-9.2583</v>
+        <v>-8.7615</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>0.97</v>
       </c>
       <c r="I227" t="n">
-        <v>-0.0426</v>
+        <v>-0.0526</v>
       </c>
       <c r="J227" t="n">
-        <v>-1.1502</v>
+        <v>-1.4202</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>0.96</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.0561</v>
+        <v>-0.06710000000000001</v>
       </c>
       <c r="J228" t="n">
-        <v>-1.5147</v>
+        <v>-1.8117</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.91</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.1147</v>
+        <v>-0.129</v>
       </c>
       <c r="J229" t="n">
-        <v>-3.0969</v>
+        <v>-3.483</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.88</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.1468</v>
+        <v>-0.1621</v>
       </c>
       <c r="J230" t="n">
-        <v>-3.9636</v>
+        <v>-4.3767</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.86</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.1678</v>
+        <v>-0.1834</v>
       </c>
       <c r="J231" t="n">
-        <v>-4.5306</v>
+        <v>-4.9518</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.13</v>
       </c>
       <c r="I232" t="n">
-        <v>0.2539</v>
+        <v>0.2571</v>
       </c>
       <c r="J232" t="n">
-        <v>6.8553</v>
+        <v>6.9417</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>0.97</v>
       </c>
       <c r="I233" t="n">
-        <v>-0.0431</v>
+        <v>-0.053</v>
       </c>
       <c r="J233" t="n">
-        <v>-1.1637</v>
+        <v>-1.431</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>0.88</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.1472</v>
+        <v>-0.1624</v>
       </c>
       <c r="J234" t="n">
-        <v>-3.9744</v>
+        <v>-4.3848</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.88</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.1472</v>
+        <v>-0.1624</v>
       </c>
       <c r="J235" t="n">
-        <v>-3.9744</v>
+        <v>-4.3848</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.74</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.2883</v>
+        <v>-0.3029</v>
       </c>
       <c r="J236" t="n">
-        <v>-7.7841</v>
+        <v>-8.1783</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.67</v>
       </c>
       <c r="I237" t="n">
-        <v>0.8084</v>
+        <v>0.7958</v>
       </c>
       <c r="J237" t="n">
-        <v>21.8268</v>
+        <v>21.4866</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.49</v>
       </c>
       <c r="I238" t="n">
-        <v>0.6143</v>
+        <v>0.6162</v>
       </c>
       <c r="J238" t="n">
-        <v>16.5861</v>
+        <v>16.6374</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>1.11</v>
       </c>
       <c r="I239" t="n">
-        <v>0.1671</v>
+        <v>0.185</v>
       </c>
       <c r="J239" t="n">
-        <v>4.5117</v>
+        <v>4.995</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.98</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.0549</v>
+        <v>-0.0573</v>
       </c>
       <c r="J240" t="n">
-        <v>-1.4823</v>
+        <v>-1.5471</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.71</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.3457</v>
+        <v>-0.3534</v>
       </c>
       <c r="J241" t="n">
-        <v>-9.3339</v>
+        <v>-9.5418</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.3</v>
       </c>
       <c r="I242" t="n">
-        <v>0.8017</v>
+        <v>0.7586000000000001</v>
       </c>
       <c r="J242" t="n">
-        <v>22.4476</v>
+        <v>21.2408</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.23</v>
       </c>
       <c r="I243" t="n">
-        <v>0.6367</v>
+        <v>0.6128</v>
       </c>
       <c r="J243" t="n">
-        <v>17.8276</v>
+        <v>17.1584</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.17</v>
       </c>
       <c r="I244" t="n">
-        <v>0.4922</v>
+        <v>0.4826</v>
       </c>
       <c r="J244" t="n">
-        <v>13.7816</v>
+        <v>13.5128</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>1.12</v>
       </c>
       <c r="I245" t="n">
-        <v>0.364</v>
+        <v>0.3654</v>
       </c>
       <c r="J245" t="n">
-        <v>10.192</v>
+        <v>10.2312</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>1.04</v>
       </c>
       <c r="I246" t="n">
-        <v>0.1262</v>
+        <v>0.1426</v>
       </c>
       <c r="J246" t="n">
-        <v>3.5336</v>
+        <v>3.9928</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.09</v>
       </c>
       <c r="I247" t="n">
-        <v>0.2699</v>
+        <v>0.2649</v>
       </c>
       <c r="J247" t="n">
-        <v>7.5572</v>
+        <v>7.4172</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.08</v>
       </c>
       <c r="I248" t="n">
-        <v>0.2479</v>
+        <v>0.2438</v>
       </c>
       <c r="J248" t="n">
-        <v>6.9412</v>
+        <v>6.8264</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>0.79</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.2323</v>
+        <v>-0.2493</v>
       </c>
       <c r="J249" t="n">
-        <v>-6.5044</v>
+        <v>-6.9804</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.76</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.2616</v>
+        <v>-0.2782</v>
       </c>
       <c r="J250" t="n">
-        <v>-7.3248</v>
+        <v>-7.7896</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.6</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.4135</v>
+        <v>-0.4248</v>
       </c>
       <c r="J251" t="n">
-        <v>-11.578</v>
+        <v>-11.8944</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.53</v>
       </c>
       <c r="I252" t="n">
-        <v>1.1866</v>
+        <v>1.1513</v>
       </c>
       <c r="J252" t="n">
-        <v>32.0382</v>
+        <v>31.0851</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.44</v>
       </c>
       <c r="I253" t="n">
-        <v>1.0701</v>
+        <v>1.0231</v>
       </c>
       <c r="J253" t="n">
-        <v>28.8927</v>
+        <v>27.6237</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>1.16</v>
       </c>
       <c r="I254" t="n">
-        <v>0.4674</v>
+        <v>0.46</v>
       </c>
       <c r="J254" t="n">
-        <v>12.6198</v>
+        <v>12.42</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.276</v>
+        <v>-0.2631</v>
       </c>
       <c r="J255" t="n">
-        <v>-7.452</v>
+        <v>-7.1037</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.8</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.6688</v>
+        <v>-0.6209</v>
       </c>
       <c r="J256" t="n">
-        <v>-18.0576</v>
+        <v>-16.7643</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>0.98</v>
       </c>
       <c r="I257" t="n">
-        <v>-0.0189</v>
+        <v>-0.0296</v>
       </c>
       <c r="J257" t="n">
-        <v>-0.5103</v>
+        <v>-0.7992</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>0.91</v>
       </c>
       <c r="I258" t="n">
-        <v>-0.1087</v>
+        <v>-0.1245</v>
       </c>
       <c r="J258" t="n">
-        <v>-2.9349</v>
+        <v>-3.3615</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>0.85</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.1719</v>
+        <v>-0.1891</v>
       </c>
       <c r="J259" t="n">
-        <v>-4.6413</v>
+        <v>-5.1057</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.85</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.1719</v>
+        <v>-0.1891</v>
       </c>
       <c r="J260" t="n">
-        <v>-4.6413</v>
+        <v>-5.1057</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.3279</v>
+        <v>-0.3429</v>
       </c>
       <c r="J261" t="n">
-        <v>-8.853300000000001</v>
+        <v>-9.2583</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.26</v>
       </c>
       <c r="I262" t="n">
-        <v>0.4106</v>
+        <v>0.4119</v>
       </c>
       <c r="J262" t="n">
-        <v>14.7816</v>
+        <v>14.8284</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.21</v>
       </c>
       <c r="I263" t="n">
-        <v>0.3426</v>
+        <v>0.3477</v>
       </c>
       <c r="J263" t="n">
-        <v>12.3336</v>
+        <v>12.5172</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>1.13</v>
       </c>
       <c r="I264" t="n">
-        <v>0.2285</v>
+        <v>0.2381</v>
       </c>
       <c r="J264" t="n">
-        <v>8.226000000000001</v>
+        <v>8.5716</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>0.89</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.1486</v>
+        <v>-0.1608</v>
       </c>
       <c r="J265" t="n">
-        <v>-5.3496</v>
+        <v>-5.7888</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.66</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.377</v>
+        <v>-0.3866</v>
       </c>
       <c r="J266" t="n">
-        <v>-13.572</v>
+        <v>-13.9176</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.35</v>
       </c>
       <c r="I267" t="n">
-        <v>0.4802</v>
+        <v>0.486</v>
       </c>
       <c r="J267" t="n">
-        <v>17.2872</v>
+        <v>17.496</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>1.27</v>
       </c>
       <c r="I268" t="n">
-        <v>0.3841</v>
+        <v>0.3946</v>
       </c>
       <c r="J268" t="n">
-        <v>13.8276</v>
+        <v>14.2056</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>1</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.0066</v>
+        <v>-0.0051</v>
       </c>
       <c r="J269" t="n">
-        <v>-0.2376</v>
+        <v>-0.1836</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.92</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.1201</v>
+        <v>-0.1302</v>
       </c>
       <c r="J270" t="n">
-        <v>-4.3236</v>
+        <v>-4.6872</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.85</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.1967</v>
+        <v>-0.2083</v>
       </c>
       <c r="J271" t="n">
-        <v>-7.0812</v>
+        <v>-7.4988</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.4</v>
       </c>
       <c r="I272" t="n">
-        <v>1.0063</v>
+        <v>0.9498</v>
       </c>
       <c r="J272" t="n">
-        <v>24.1512</v>
+        <v>22.7952</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.35</v>
       </c>
       <c r="I273" t="n">
-        <v>0.9085</v>
+        <v>0.8537</v>
       </c>
       <c r="J273" t="n">
-        <v>21.804</v>
+        <v>20.4888</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.27</v>
       </c>
       <c r="I274" t="n">
-        <v>0.7251</v>
+        <v>0.6925</v>
       </c>
       <c r="J274" t="n">
-        <v>17.4024</v>
+        <v>16.62</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>1.03</v>
       </c>
       <c r="I275" t="n">
-        <v>0.08550000000000001</v>
+        <v>0.1048</v>
       </c>
       <c r="J275" t="n">
-        <v>2.052</v>
+        <v>2.5152</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.93</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.3129</v>
+        <v>-0.2964</v>
       </c>
       <c r="J276" t="n">
-        <v>-7.5096</v>
+        <v>-7.1136</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.28</v>
       </c>
       <c r="I277" t="n">
-        <v>0.6383</v>
+        <v>0.607</v>
       </c>
       <c r="J277" t="n">
-        <v>15.3192</v>
+        <v>14.568</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>0.83</v>
       </c>
       <c r="I278" t="n">
-        <v>-0.1939</v>
+        <v>-0.2108</v>
       </c>
       <c r="J278" t="n">
-        <v>-4.6536</v>
+        <v>-5.0592</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>0.76</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.2632</v>
+        <v>-0.2794</v>
       </c>
       <c r="J279" t="n">
-        <v>-6.3168</v>
+        <v>-6.7056</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.76</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.2632</v>
+        <v>-0.2794</v>
       </c>
       <c r="J280" t="n">
-        <v>-6.3168</v>
+        <v>-6.7056</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.75</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.2729</v>
+        <v>-0.2889</v>
       </c>
       <c r="J281" t="n">
-        <v>-6.5496</v>
+        <v>-6.9336</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.61</v>
       </c>
       <c r="I282" t="n">
-        <v>1.2945</v>
+        <v>1.2651</v>
       </c>
       <c r="J282" t="n">
-        <v>31.068</v>
+        <v>30.3624</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>1.48</v>
       </c>
       <c r="I283" t="n">
-        <v>1.1274</v>
+        <v>1.0869</v>
       </c>
       <c r="J283" t="n">
-        <v>27.0576</v>
+        <v>26.0856</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>1.06</v>
       </c>
       <c r="I284" t="n">
-        <v>0.1954</v>
+        <v>0.2075</v>
       </c>
       <c r="J284" t="n">
-        <v>4.6896</v>
+        <v>4.98</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>0.86</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.5043</v>
+        <v>-0.4745</v>
       </c>
       <c r="J285" t="n">
-        <v>-12.1032</v>
+        <v>-11.388</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.76</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.7658</v>
+        <v>-0.7077</v>
       </c>
       <c r="J286" t="n">
-        <v>-18.3792</v>
+        <v>-16.9848</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.26</v>
       </c>
       <c r="I287" t="n">
-        <v>0.5862000000000001</v>
+        <v>0.5623</v>
       </c>
       <c r="J287" t="n">
-        <v>14.0688</v>
+        <v>13.4952</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>0.96</v>
       </c>
       <c r="I288" t="n">
-        <v>-0.0548</v>
+        <v>-0.06610000000000001</v>
       </c>
       <c r="J288" t="n">
-        <v>-1.3152</v>
+        <v>-1.5864</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.0799</v>
+        <v>-0.09279999999999999</v>
       </c>
       <c r="J289" t="n">
-        <v>-1.9176</v>
+        <v>-2.2272</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.79</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.2376</v>
+        <v>-0.2534</v>
       </c>
       <c r="J290" t="n">
-        <v>-5.7024</v>
+        <v>-6.0816</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.58</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.4372</v>
+        <v>-0.4465</v>
       </c>
       <c r="J291" t="n">
-        <v>-10.4928</v>
+        <v>-10.716</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.65</v>
       </c>
       <c r="I292" t="n">
-        <v>1.3226</v>
+        <v>1.2987</v>
       </c>
       <c r="J292" t="n">
-        <v>33.065</v>
+        <v>32.4675</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.4</v>
       </c>
       <c r="I293" t="n">
-        <v>0.9981</v>
+        <v>0.9426</v>
       </c>
       <c r="J293" t="n">
-        <v>24.9525</v>
+        <v>23.565</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>1.13</v>
       </c>
       <c r="I294" t="n">
-        <v>0.3784</v>
+        <v>0.3815</v>
       </c>
       <c r="J294" t="n">
-        <v>9.460000000000001</v>
+        <v>9.5375</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>1.01</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.0007</v>
+        <v>0.0214</v>
       </c>
       <c r="J295" t="n">
-        <v>-0.0175</v>
+        <v>0.535</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>0.95</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.2574</v>
+        <v>-0.2422</v>
       </c>
       <c r="J296" t="n">
-        <v>-6.435</v>
+        <v>-6.055</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>1.01</v>
       </c>
       <c r="I297" t="n">
-        <v>0.0618</v>
+        <v>0.0607</v>
       </c>
       <c r="J297" t="n">
-        <v>1.545</v>
+        <v>1.5175</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>1.01</v>
       </c>
       <c r="I298" t="n">
-        <v>0.0618</v>
+        <v>0.0607</v>
       </c>
       <c r="J298" t="n">
-        <v>1.545</v>
+        <v>1.5175</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>0.91</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.1132</v>
+        <v>-0.1279</v>
       </c>
       <c r="J299" t="n">
-        <v>-2.83</v>
+        <v>-3.1975</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.78</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.2459</v>
+        <v>-0.2619</v>
       </c>
       <c r="J300" t="n">
-        <v>-6.1475</v>
+        <v>-6.5475</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.76</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.2655</v>
+        <v>-0.2812</v>
       </c>
       <c r="J301" t="n">
-        <v>-6.6375</v>
+        <v>-7.03</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>1.27</v>
       </c>
       <c r="I302" t="n">
-        <v>0.4408</v>
+        <v>0.437</v>
       </c>
       <c r="J302" t="n">
-        <v>12.7832</v>
+        <v>12.673</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>1.07</v>
       </c>
       <c r="I303" t="n">
-        <v>0.146</v>
+        <v>0.1542</v>
       </c>
       <c r="J303" t="n">
-        <v>4.234</v>
+        <v>4.4718</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>1.03</v>
       </c>
       <c r="I304" t="n">
-        <v>0.07480000000000001</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="J304" t="n">
-        <v>2.1692</v>
+        <v>2.3664</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>0.96</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.0606</v>
+        <v>-0.0706</v>
       </c>
       <c r="J305" t="n">
-        <v>-1.7574</v>
+        <v>-2.0474</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>0.52</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.4987</v>
+        <v>-0.5038</v>
       </c>
       <c r="J306" t="n">
-        <v>-14.4623</v>
+        <v>-14.6102</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>1.47</v>
       </c>
       <c r="I307" t="n">
-        <v>0.5895</v>
+        <v>0.5935</v>
       </c>
       <c r="J307" t="n">
-        <v>17.0955</v>
+        <v>17.2115</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>1.46</v>
       </c>
       <c r="I308" t="n">
-        <v>0.5785</v>
+        <v>0.5832000000000001</v>
       </c>
       <c r="J308" t="n">
-        <v>16.7765</v>
+        <v>16.9128</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>1.27</v>
       </c>
       <c r="I309" t="n">
-        <v>0.3634</v>
+        <v>0.379</v>
       </c>
       <c r="J309" t="n">
-        <v>10.5386</v>
+        <v>10.991</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>1.13</v>
       </c>
       <c r="I310" t="n">
-        <v>0.1928</v>
+        <v>0.2111</v>
       </c>
       <c r="J310" t="n">
-        <v>5.5912</v>
+        <v>6.1219</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.7</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.3563</v>
+        <v>-0.3635</v>
       </c>
       <c r="J311" t="n">
-        <v>-10.3327</v>
+        <v>-10.5415</v>
       </c>
     </row>
     <row r="312">
@@ -14829,10 +14829,10 @@
         <v>1.56</v>
       </c>
       <c r="I312" t="n">
-        <v>1.2786</v>
+        <v>1.2399</v>
       </c>
       <c r="J312" t="n">
-        <v>51.144</v>
+        <v>49.596</v>
       </c>
     </row>
     <row r="313">
@@ -14869,10 +14869,10 @@
         <v>0.96</v>
       </c>
       <c r="I313" t="n">
-        <v>-0.1694</v>
+        <v>-0.1722</v>
       </c>
       <c r="J313" t="n">
-        <v>-6.776</v>
+        <v>-6.888</v>
       </c>
     </row>
     <row r="314">
@@ -14909,10 +14909,10 @@
         <v>0.92</v>
       </c>
       <c r="I314" t="n">
-        <v>-0.2958</v>
+        <v>-0.2916</v>
       </c>
       <c r="J314" t="n">
-        <v>-11.832</v>
+        <v>-11.664</v>
       </c>
     </row>
     <row r="315">
@@ -14949,10 +14949,10 @@
         <v>0.86</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.4671</v>
+        <v>-0.4484</v>
       </c>
       <c r="J315" t="n">
-        <v>-18.684</v>
+        <v>-17.936</v>
       </c>
     </row>
     <row r="316">
@@ -14989,10 +14989,10 @@
         <v>0.8</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.6271</v>
+        <v>-0.5916</v>
       </c>
       <c r="J316" t="n">
-        <v>-25.084</v>
+        <v>-23.664</v>
       </c>
     </row>
     <row r="317">
@@ -15069,10 +15069,10 @@
         <v>1.15</v>
       </c>
       <c r="I318" t="n">
-        <v>0.3213</v>
+        <v>0.3291</v>
       </c>
       <c r="J318" t="n">
-        <v>12.852</v>
+        <v>13.164</v>
       </c>
     </row>
     <row r="319">
@@ -15109,10 +15109,10 @@
         <v>1.14</v>
       </c>
       <c r="I319" t="n">
-        <v>0.3029</v>
+        <v>0.3116</v>
       </c>
       <c r="J319" t="n">
-        <v>12.116</v>
+        <v>12.464</v>
       </c>
     </row>
     <row r="320">
@@ -15149,10 +15149,10 @@
         <v>1.11</v>
       </c>
       <c r="I320" t="n">
-        <v>0.2468</v>
+        <v>0.2577</v>
       </c>
       <c r="J320" t="n">
-        <v>9.872</v>
+        <v>10.308</v>
       </c>
     </row>
     <row r="321">
@@ -15189,10 +15189,10 @@
         <v>0.89</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.1564</v>
+        <v>-0.1669</v>
       </c>
       <c r="J321" t="n">
-        <v>-6.256</v>
+        <v>-6.676</v>
       </c>
     </row>
     <row r="322">
@@ -15229,10 +15229,10 @@
         <v>2.51</v>
       </c>
       <c r="I322" t="n">
-        <v>1.8338</v>
+        <v>1.9372</v>
       </c>
       <c r="J322" t="n">
-        <v>34.8422</v>
+        <v>36.8068</v>
       </c>
     </row>
     <row r="323">
@@ -15269,10 +15269,10 @@
         <v>1.43</v>
       </c>
       <c r="I323" t="n">
-        <v>1.0097</v>
+        <v>0.9635</v>
       </c>
       <c r="J323" t="n">
-        <v>19.1843</v>
+        <v>18.3065</v>
       </c>
     </row>
     <row r="324">
@@ -15309,10 +15309,10 @@
         <v>1.32</v>
       </c>
       <c r="I324" t="n">
-        <v>0.7903</v>
+        <v>0.7596000000000001</v>
       </c>
       <c r="J324" t="n">
-        <v>15.0157</v>
+        <v>14.4324</v>
       </c>
     </row>
     <row r="325">
@@ -15349,10 +15349,10 @@
         <v>1.2</v>
       </c>
       <c r="I325" t="n">
-        <v>0.5086000000000001</v>
+        <v>0.5096000000000001</v>
       </c>
       <c r="J325" t="n">
-        <v>9.663399999999999</v>
+        <v>9.682399999999999</v>
       </c>
     </row>
     <row r="326">
@@ -15389,10 +15389,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.7014</v>
+        <v>-0.6392</v>
       </c>
       <c r="J326" t="n">
-        <v>-13.3266</v>
+        <v>-12.1448</v>
       </c>
     </row>
     <row r="327">
@@ -15429,10 +15429,10 @@
         <v>1.34</v>
       </c>
       <c r="I327" t="n">
-        <v>0.8351</v>
+        <v>0.7705</v>
       </c>
       <c r="J327" t="n">
-        <v>15.8669</v>
+        <v>14.6395</v>
       </c>
     </row>
     <row r="328">
@@ -15469,10 +15469,10 @@
         <v>0.75</v>
       </c>
       <c r="I328" t="n">
-        <v>-0.2576</v>
+        <v>-0.2771</v>
       </c>
       <c r="J328" t="n">
-        <v>-4.8944</v>
+        <v>-5.2649</v>
       </c>
     </row>
     <row r="329">
@@ -15509,10 +15509,10 @@
         <v>0.67</v>
       </c>
       <c r="I329" t="n">
-        <v>-0.3322</v>
+        <v>-0.3497</v>
       </c>
       <c r="J329" t="n">
-        <v>-6.3118</v>
+        <v>-6.6443</v>
       </c>
     </row>
     <row r="330">
@@ -15549,10 +15549,10 @@
         <v>0.61</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.3885</v>
+        <v>-0.4036</v>
       </c>
       <c r="J330" t="n">
-        <v>-7.3815</v>
+        <v>-7.6684</v>
       </c>
     </row>
     <row r="331">
@@ -15589,10 +15589,10 @@
         <v>0.4</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.5834</v>
+        <v>-0.5868</v>
       </c>
       <c r="J331" t="n">
-        <v>-11.0846</v>
+        <v>-11.1492</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/5257/event_5257_evp_summary.xlsx
+++ b/database/event/5257/event_5257_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.6309</v>
+        <v>5.5821</v>
       </c>
       <c r="C2" t="n">
-        <v>1.0384</v>
+        <v>1.0294</v>
       </c>
       <c r="D2" t="n">
-        <v>1.9391</v>
+        <v>1.9371</v>
       </c>
       <c r="E2" t="n">
-        <v>5.6309</v>
+        <v>5.5821</v>
       </c>
       <c r="F2" t="n">
-        <v>2.9881</v>
+        <v>2.9874</v>
       </c>
       <c r="G2" t="n">
-        <v>2.6428</v>
+        <v>2.5947</v>
       </c>
       <c r="H2" t="n">
-        <v>4.9647</v>
+        <v>4.7734</v>
       </c>
       <c r="I2" t="n">
-        <v>2.6809</v>
+        <v>2.6801</v>
       </c>
       <c r="J2" t="n">
-        <v>2.6428</v>
+        <v>2.5947</v>
       </c>
       <c r="K2" t="n">
         <v>144</v>
@@ -529,7 +529,7 @@
         <v>136</v>
       </c>
       <c r="M2" t="n">
-        <v>5.3237</v>
+        <v>5.2748</v>
       </c>
       <c r="N2" t="n">
         <v>280</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.4187</v>
+        <v>4.4354</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8148</v>
+        <v>0.8179</v>
       </c>
       <c r="D3" t="n">
-        <v>1.3873</v>
+        <v>1.4147</v>
       </c>
       <c r="E3" t="n">
-        <v>4.4187</v>
+        <v>4.4354</v>
       </c>
       <c r="F3" t="n">
-        <v>2.3277</v>
+        <v>2.447</v>
       </c>
       <c r="G3" t="n">
-        <v>2.091</v>
+        <v>1.9884</v>
       </c>
       <c r="H3" t="n">
-        <v>2.7856</v>
+        <v>2.7444</v>
       </c>
       <c r="I3" t="n">
-        <v>1.5042</v>
+        <v>1.5409</v>
       </c>
       <c r="J3" t="n">
-        <v>2.091</v>
+        <v>1.9884</v>
       </c>
       <c r="K3" t="n">
         <v>154</v>
@@ -575,7 +575,7 @@
         <v>132</v>
       </c>
       <c r="M3" t="n">
-        <v>3.5952</v>
+        <v>3.5293</v>
       </c>
       <c r="N3" t="n">
         <v>286</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.2373</v>
+        <v>4.2026</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7814</v>
+        <v>0.775</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3047</v>
+        <v>1.3087</v>
       </c>
       <c r="E4" t="n">
-        <v>4.2373</v>
+        <v>4.2026</v>
       </c>
       <c r="F4" t="n">
-        <v>2.8046</v>
+        <v>2.8302</v>
       </c>
       <c r="G4" t="n">
-        <v>1.4327</v>
+        <v>1.3724</v>
       </c>
       <c r="H4" t="n">
-        <v>4.3593</v>
+        <v>4.1833</v>
       </c>
       <c r="I4" t="n">
-        <v>2.354</v>
+        <v>2.3488</v>
       </c>
       <c r="J4" t="n">
-        <v>1.4327</v>
+        <v>1.3724</v>
       </c>
       <c r="K4" t="n">
         <v>144</v>
@@ -621,7 +621,7 @@
         <v>136</v>
       </c>
       <c r="M4" t="n">
-        <v>3.7867</v>
+        <v>3.721200000000001</v>
       </c>
       <c r="N4" t="n">
         <v>280</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.2321</v>
+        <v>4.1109</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7804</v>
+        <v>0.7581</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3023</v>
+        <v>1.2669</v>
       </c>
       <c r="E5" t="n">
-        <v>4.2321</v>
+        <v>4.1109</v>
       </c>
       <c r="F5" t="n">
-        <v>2.8058</v>
+        <v>2.8193</v>
       </c>
       <c r="G5" t="n">
-        <v>1.4263</v>
+        <v>1.2916</v>
       </c>
       <c r="H5" t="n">
-        <v>4.363</v>
+        <v>4.1422</v>
       </c>
       <c r="I5" t="n">
-        <v>2.356</v>
+        <v>2.3257</v>
       </c>
       <c r="J5" t="n">
-        <v>1.4263</v>
+        <v>1.2916</v>
       </c>
       <c r="K5" t="n">
         <v>146</v>
@@ -667,7 +667,7 @@
         <v>77</v>
       </c>
       <c r="M5" t="n">
-        <v>3.7823</v>
+        <v>3.6173</v>
       </c>
       <c r="N5" t="n">
         <v>223</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.854</v>
+        <v>3.7438</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7107</v>
+        <v>0.6904</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1302</v>
+        <v>1.0997</v>
       </c>
       <c r="E6" t="n">
-        <v>3.854</v>
+        <v>3.7438</v>
       </c>
       <c r="F6" t="n">
-        <v>3.5054</v>
+        <v>3.4365</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3486</v>
+        <v>0.3073</v>
       </c>
       <c r="H6" t="n">
-        <v>6.6716</v>
+        <v>6.4593</v>
       </c>
       <c r="I6" t="n">
-        <v>3.6026</v>
+        <v>3.6267</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3486</v>
+        <v>0.3073</v>
       </c>
       <c r="K6" t="n">
         <v>154</v>
@@ -713,7 +713,7 @@
         <v>132</v>
       </c>
       <c r="M6" t="n">
-        <v>3.9512</v>
+        <v>3.934</v>
       </c>
       <c r="N6" t="n">
         <v>286</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.6197</v>
+        <v>3.5248</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6675</v>
+        <v>0.65</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0236</v>
+        <v>0.9999</v>
       </c>
       <c r="E7" t="n">
-        <v>3.6197</v>
+        <v>3.5248</v>
       </c>
       <c r="F7" t="n">
-        <v>3.0254</v>
+        <v>2.9553</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5943000000000001</v>
+        <v>0.5695</v>
       </c>
       <c r="H7" t="n">
-        <v>5.0879</v>
+        <v>4.6528</v>
       </c>
       <c r="I7" t="n">
-        <v>2.7474</v>
+        <v>2.6124</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5943000000000001</v>
+        <v>0.5695</v>
       </c>
       <c r="K7" t="n">
         <v>197</v>
@@ -759,7 +759,7 @@
         <v>81</v>
       </c>
       <c r="M7" t="n">
-        <v>3.3417</v>
+        <v>3.1819</v>
       </c>
       <c r="N7" t="n">
         <v>278</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.2237</v>
+        <v>3.1411</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5945</v>
+        <v>0.5792</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8433</v>
+        <v>0.8250999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>3.2237</v>
+        <v>3.1411</v>
       </c>
       <c r="F8" t="n">
-        <v>3.0135</v>
+        <v>2.9842</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2102</v>
+        <v>0.1569</v>
       </c>
       <c r="H8" t="n">
-        <v>5.0484</v>
+        <v>4.7613</v>
       </c>
       <c r="I8" t="n">
-        <v>2.7261</v>
+        <v>2.6733</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2102</v>
+        <v>0.1569</v>
       </c>
       <c r="K8" t="n">
         <v>146</v>
@@ -805,7 +805,7 @@
         <v>77</v>
       </c>
       <c r="M8" t="n">
-        <v>2.9363</v>
+        <v>2.8302</v>
       </c>
       <c r="N8" t="n">
         <v>223</v>
@@ -814,139 +814,139 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>mantuu</t>
+          <t>stavn</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.2058</v>
+        <v>3.1086</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5911999999999999</v>
+        <v>0.5732</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8351</v>
+        <v>0.8103</v>
       </c>
       <c r="E9" t="n">
-        <v>3.2058</v>
+        <v>3.1086</v>
       </c>
       <c r="F9" t="n">
-        <v>2.145</v>
+        <v>2.5377</v>
       </c>
       <c r="G9" t="n">
-        <v>1.0608</v>
+        <v>0.5709</v>
       </c>
       <c r="H9" t="n">
-        <v>2.1828</v>
+        <v>3.0849</v>
       </c>
       <c r="I9" t="n">
-        <v>1.1787</v>
+        <v>1.7321</v>
       </c>
       <c r="J9" t="n">
-        <v>1.0608</v>
+        <v>0.5709</v>
       </c>
       <c r="K9" t="n">
-        <v>197</v>
+        <v>154</v>
       </c>
       <c r="L9" t="n">
-        <v>81</v>
+        <v>132</v>
       </c>
       <c r="M9" t="n">
-        <v>2.2395</v>
+        <v>2.303</v>
       </c>
       <c r="N9" t="n">
-        <v>278</v>
+        <v>286</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>stavn</t>
+          <t>k1to</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.1499</v>
+        <v>3.0631</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5809</v>
+        <v>0.5649</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8097</v>
+        <v>0.7896</v>
       </c>
       <c r="E10" t="n">
-        <v>3.1499</v>
+        <v>3.0631</v>
       </c>
       <c r="F10" t="n">
-        <v>2.4936</v>
+        <v>3.033</v>
       </c>
       <c r="G10" t="n">
-        <v>0.6563</v>
+        <v>0.0301</v>
       </c>
       <c r="H10" t="n">
-        <v>3.333</v>
+        <v>4.9445</v>
       </c>
       <c r="I10" t="n">
-        <v>1.7998</v>
+        <v>2.7762</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6563</v>
+        <v>0.0301</v>
       </c>
       <c r="K10" t="n">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="L10" t="n">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="M10" t="n">
-        <v>2.4561</v>
+        <v>2.8063</v>
       </c>
       <c r="N10" t="n">
-        <v>286</v>
+        <v>280</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>k1to</t>
+          <t>mantuu</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.0662</v>
+        <v>2.9419</v>
       </c>
       <c r="C11" t="n">
-        <v>0.5654</v>
+        <v>0.5425</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7716</v>
+        <v>0.7344000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>3.0662</v>
+        <v>2.9419</v>
       </c>
       <c r="F11" t="n">
-        <v>3.0414</v>
+        <v>1.9577</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0248</v>
+        <v>0.9842</v>
       </c>
       <c r="H11" t="n">
-        <v>5.1404</v>
+        <v>1.9577</v>
       </c>
       <c r="I11" t="n">
-        <v>2.7758</v>
+        <v>1.0992</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0248</v>
+        <v>0.9842</v>
       </c>
       <c r="K11" t="n">
-        <v>144</v>
+        <v>197</v>
       </c>
       <c r="L11" t="n">
-        <v>136</v>
+        <v>81</v>
       </c>
       <c r="M11" t="n">
-        <v>2.8006</v>
+        <v>2.0834</v>
       </c>
       <c r="N11" t="n">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="12">
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.9607</v>
+        <v>2.9345</v>
       </c>
       <c r="C12" t="n">
-        <v>0.546</v>
+        <v>0.5411</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7236</v>
+        <v>0.731</v>
       </c>
       <c r="E12" t="n">
-        <v>2.9607</v>
+        <v>2.9345</v>
       </c>
       <c r="F12" t="n">
-        <v>3.0582</v>
+        <v>3.0501</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.0975</v>
+        <v>-0.1156</v>
       </c>
       <c r="H12" t="n">
-        <v>5.196</v>
+        <v>5.0086</v>
       </c>
       <c r="I12" t="n">
-        <v>2.8058</v>
+        <v>2.8122</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.0975</v>
+        <v>-0.1156</v>
       </c>
       <c r="K12" t="n">
         <v>146</v>
@@ -989,7 +989,7 @@
         <v>77</v>
       </c>
       <c r="M12" t="n">
-        <v>2.7083</v>
+        <v>2.6966</v>
       </c>
       <c r="N12" t="n">
         <v>223</v>
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.7918</v>
+        <v>2.748</v>
       </c>
       <c r="C13" t="n">
-        <v>0.5148</v>
+        <v>0.5067</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6467000000000001</v>
+        <v>0.6461</v>
       </c>
       <c r="E13" t="n">
-        <v>2.7918</v>
+        <v>2.748</v>
       </c>
       <c r="F13" t="n">
-        <v>3.001</v>
+        <v>2.9769</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.2092</v>
+        <v>-0.2289</v>
       </c>
       <c r="H13" t="n">
-        <v>5.0073</v>
+        <v>4.7338</v>
       </c>
       <c r="I13" t="n">
-        <v>2.7039</v>
+        <v>2.6579</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.2092</v>
+        <v>-0.2289</v>
       </c>
       <c r="K13" t="n">
         <v>197</v>
@@ -1035,7 +1035,7 @@
         <v>81</v>
       </c>
       <c r="M13" t="n">
-        <v>2.4947</v>
+        <v>2.429</v>
       </c>
       <c r="N13" t="n">
         <v>278</v>
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.4737</v>
+        <v>2.4922</v>
       </c>
       <c r="C14" t="n">
-        <v>0.4562</v>
+        <v>0.4596</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5019</v>
+        <v>0.5295</v>
       </c>
       <c r="E14" t="n">
-        <v>2.4737</v>
+        <v>2.4922</v>
       </c>
       <c r="F14" t="n">
-        <v>2.7671</v>
+        <v>2.8113</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.2934</v>
+        <v>-0.3191</v>
       </c>
       <c r="H14" t="n">
-        <v>4.2354</v>
+        <v>4.1121</v>
       </c>
       <c r="I14" t="n">
-        <v>2.2871</v>
+        <v>2.3088</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.2934</v>
+        <v>-0.3191</v>
       </c>
       <c r="K14" t="n">
         <v>144</v>
@@ -1081,7 +1081,7 @@
         <v>136</v>
       </c>
       <c r="M14" t="n">
-        <v>1.9937</v>
+        <v>1.9897</v>
       </c>
       <c r="N14" t="n">
         <v>280</v>
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.8987</v>
+        <v>1.8867</v>
       </c>
       <c r="C15" t="n">
-        <v>0.3501</v>
+        <v>0.3479</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2401</v>
+        <v>0.2537</v>
       </c>
       <c r="E15" t="n">
-        <v>1.8987</v>
+        <v>1.8867</v>
       </c>
       <c r="F15" t="n">
-        <v>2.8425</v>
+        <v>2.792</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.9438</v>
+        <v>-0.9053</v>
       </c>
       <c r="H15" t="n">
-        <v>4.4843</v>
+        <v>4.0396</v>
       </c>
       <c r="I15" t="n">
-        <v>2.4215</v>
+        <v>2.2681</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.9438</v>
+        <v>-0.9053</v>
       </c>
       <c r="K15" t="n">
         <v>197</v>
@@ -1127,7 +1127,7 @@
         <v>81</v>
       </c>
       <c r="M15" t="n">
-        <v>1.4777</v>
+        <v>1.3628</v>
       </c>
       <c r="N15" t="n">
         <v>278</v>
@@ -1136,415 +1136,415 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>k0nfig</t>
+          <t>acoR</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.6799</v>
+        <v>1.543</v>
       </c>
       <c r="C16" t="n">
-        <v>0.3098</v>
+        <v>0.2845</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1405</v>
+        <v>0.09710000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>1.6799</v>
+        <v>1.543</v>
       </c>
       <c r="F16" t="n">
-        <v>1.3034</v>
+        <v>1.543</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3765</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>1.3034</v>
+        <v>1.543</v>
       </c>
       <c r="I16" t="n">
-        <v>0.7038</v>
+        <v>1.543</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3765</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>146</v>
+        <v>119</v>
       </c>
       <c r="L16" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1.0803</v>
+        <v>1.543</v>
       </c>
       <c r="N16" t="n">
-        <v>223</v>
+        <v>119</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>acoR</t>
+          <t>FL1T</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.6528</v>
+        <v>1.4642</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3048</v>
+        <v>0.27</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1282</v>
+        <v>0.0612</v>
       </c>
       <c r="E17" t="n">
-        <v>1.6528</v>
+        <v>1.4642</v>
       </c>
       <c r="F17" t="n">
-        <v>1.6528</v>
+        <v>1.4642</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1.6528</v>
+        <v>1.4642</v>
       </c>
       <c r="I17" t="n">
-        <v>1.6528</v>
+        <v>1.4642</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>119</v>
+        <v>218</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.6528</v>
+        <v>1.4642</v>
       </c>
       <c r="N17" t="n">
-        <v>119</v>
+        <v>218</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>FL1T</t>
+          <t>k0nfig</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.6336</v>
+        <v>1.4595</v>
       </c>
       <c r="C18" t="n">
-        <v>0.3012</v>
+        <v>0.2691</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1194</v>
+        <v>0.0591</v>
       </c>
       <c r="E18" t="n">
-        <v>1.6336</v>
+        <v>1.4595</v>
       </c>
       <c r="F18" t="n">
-        <v>1.6336</v>
+        <v>1.1009</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>0.3586</v>
       </c>
       <c r="H18" t="n">
-        <v>1.6336</v>
+        <v>1.1009</v>
       </c>
       <c r="I18" t="n">
-        <v>1.6336</v>
+        <v>0.6181</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>0.3586</v>
       </c>
       <c r="K18" t="n">
-        <v>218</v>
+        <v>146</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="M18" t="n">
-        <v>1.6336</v>
+        <v>0.9766999999999999</v>
       </c>
       <c r="N18" t="n">
-        <v>218</v>
+        <v>223</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>mir</t>
+          <t>CRUC1AL</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.6004</v>
+        <v>1.4185</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2951</v>
+        <v>0.2616</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1043</v>
+        <v>0.0404</v>
       </c>
       <c r="E19" t="n">
-        <v>1.6004</v>
+        <v>1.4185</v>
       </c>
       <c r="F19" t="n">
-        <v>1.6004</v>
+        <v>1.4185</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.6004</v>
+        <v>1.4185</v>
       </c>
       <c r="I19" t="n">
-        <v>1.6004</v>
+        <v>1.4185</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>157</v>
+        <v>207</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.6004</v>
+        <v>1.4185</v>
       </c>
       <c r="N19" t="n">
-        <v>157</v>
+        <v>207</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CRUC1AL</t>
+          <t>TeSeS</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.5515</v>
+        <v>1.3943</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2861</v>
+        <v>0.2571</v>
       </c>
       <c r="D20" t="n">
-        <v>0.08210000000000001</v>
+        <v>0.0294</v>
       </c>
       <c r="E20" t="n">
-        <v>1.5515</v>
+        <v>1.3943</v>
       </c>
       <c r="F20" t="n">
-        <v>1.5515</v>
+        <v>2.4357</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>-1.0414</v>
       </c>
       <c r="H20" t="n">
-        <v>1.5515</v>
+        <v>2.7022</v>
       </c>
       <c r="I20" t="n">
-        <v>1.5515</v>
+        <v>1.5172</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>-1.0414</v>
       </c>
       <c r="K20" t="n">
-        <v>207</v>
+        <v>154</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="M20" t="n">
-        <v>1.5515</v>
+        <v>0.4758</v>
       </c>
       <c r="N20" t="n">
-        <v>207</v>
+        <v>286</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>xsepower</t>
+          <t>mir</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.2987</v>
+        <v>1.3831</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2395</v>
+        <v>0.2551</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.033</v>
+        <v>0.0243</v>
       </c>
       <c r="E21" t="n">
-        <v>1.2987</v>
+        <v>1.3831</v>
       </c>
       <c r="F21" t="n">
-        <v>1.2987</v>
+        <v>1.3831</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.2987</v>
+        <v>1.3831</v>
       </c>
       <c r="I21" t="n">
-        <v>1.2987</v>
+        <v>1.3831</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>218</v>
+        <v>157</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.2987</v>
+        <v>1.3831</v>
       </c>
       <c r="N21" t="n">
-        <v>218</v>
+        <v>157</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>TeSeS</t>
+          <t>almazer</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.2824</v>
+        <v>1.2621</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2365</v>
+        <v>0.2327</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.0404</v>
+        <v>-0.0308</v>
       </c>
       <c r="E22" t="n">
-        <v>1.2824</v>
+        <v>1.2621</v>
       </c>
       <c r="F22" t="n">
-        <v>2.3812</v>
+        <v>1.2621</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.0988</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>2.9623</v>
+        <v>1.2621</v>
       </c>
       <c r="I22" t="n">
-        <v>1.5996</v>
+        <v>1.2621</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.0988</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>154</v>
+        <v>218</v>
       </c>
       <c r="L22" t="n">
-        <v>132</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.5007999999999999</v>
+        <v>1.2621</v>
       </c>
       <c r="N22" t="n">
-        <v>286</v>
+        <v>218</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>robiin</t>
+          <t>xsepower</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.1945</v>
+        <v>1.1288</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2203</v>
+        <v>0.2082</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.0804</v>
+        <v>-0.0916</v>
       </c>
       <c r="E23" t="n">
-        <v>1.1945</v>
+        <v>1.1288</v>
       </c>
       <c r="F23" t="n">
-        <v>1.1945</v>
+        <v>1.1288</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1.1945</v>
+        <v>1.1288</v>
       </c>
       <c r="I23" t="n">
-        <v>1.1945</v>
+        <v>1.1288</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>207</v>
+        <v>218</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1.1945</v>
+        <v>1.1288</v>
       </c>
       <c r="N23" t="n">
-        <v>207</v>
+        <v>218</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>almazer</t>
+          <t>robiin</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.1848</v>
+        <v>1.0427</v>
       </c>
       <c r="C24" t="n">
-        <v>0.2185</v>
+        <v>0.1923</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.0849</v>
+        <v>-0.1308</v>
       </c>
       <c r="E24" t="n">
-        <v>1.1848</v>
+        <v>1.0427</v>
       </c>
       <c r="F24" t="n">
-        <v>1.1848</v>
+        <v>1.0427</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.1848</v>
+        <v>1.0427</v>
       </c>
       <c r="I24" t="n">
-        <v>1.1848</v>
+        <v>1.0427</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1.1848</v>
+        <v>1.0427</v>
       </c>
       <c r="N24" t="n">
-        <v>218</v>
+        <v>207</v>
       </c>
     </row>
     <row r="25">
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.0701</v>
+        <v>0.9535</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1973</v>
+        <v>0.1758</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.1371</v>
+        <v>-0.1714</v>
       </c>
       <c r="E25" t="n">
-        <v>1.0701</v>
+        <v>0.9535</v>
       </c>
       <c r="F25" t="n">
-        <v>1.0701</v>
+        <v>0.9535</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1.0701</v>
+        <v>0.9535</v>
       </c>
       <c r="I25" t="n">
-        <v>1.0701</v>
+        <v>0.9535</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1.0701</v>
+        <v>0.9535</v>
       </c>
       <c r="N25" t="n">
         <v>119</v>
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.7638</v>
+        <v>0.8386</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1408</v>
+        <v>0.1546</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.2765</v>
+        <v>-0.2238</v>
       </c>
       <c r="E26" t="n">
-        <v>0.7638</v>
+        <v>0.8386</v>
       </c>
       <c r="F26" t="n">
-        <v>0.7638</v>
+        <v>0.8386</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.7638</v>
+        <v>0.8386</v>
       </c>
       <c r="I26" t="n">
-        <v>0.7638</v>
+        <v>0.8386</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.7638</v>
+        <v>0.8386</v>
       </c>
       <c r="N26" t="n">
         <v>218</v>
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.4232</v>
+        <v>0.3568</v>
       </c>
       <c r="C27" t="n">
-        <v>0.078</v>
+        <v>0.0658</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4316</v>
+        <v>-0.4432</v>
       </c>
       <c r="E27" t="n">
-        <v>0.4232</v>
+        <v>0.3568</v>
       </c>
       <c r="F27" t="n">
-        <v>0.4232</v>
+        <v>0.3568</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.4232</v>
+        <v>0.3568</v>
       </c>
       <c r="I27" t="n">
-        <v>0.4232</v>
+        <v>0.3568</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.4232</v>
+        <v>0.3568</v>
       </c>
       <c r="N27" t="n">
         <v>119</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.3556</v>
+        <v>0.2986</v>
       </c>
       <c r="C28" t="n">
-        <v>0.06560000000000001</v>
+        <v>0.0551</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.4623</v>
+        <v>-0.4698</v>
       </c>
       <c r="E28" t="n">
-        <v>0.3556</v>
+        <v>0.2986</v>
       </c>
       <c r="F28" t="n">
-        <v>0.3556</v>
+        <v>0.2986</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.3556</v>
+        <v>0.2986</v>
       </c>
       <c r="I28" t="n">
-        <v>0.3556</v>
+        <v>0.2986</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.3556</v>
+        <v>0.2986</v>
       </c>
       <c r="N28" t="n">
         <v>157</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.3161</v>
+        <v>0.2824</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0583</v>
+        <v>0.0521</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.4803</v>
+        <v>-0.4771</v>
       </c>
       <c r="E29" t="n">
-        <v>0.3161</v>
+        <v>0.2824</v>
       </c>
       <c r="F29" t="n">
-        <v>0.3161</v>
+        <v>0.2824</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.3161</v>
+        <v>0.2824</v>
       </c>
       <c r="I29" t="n">
-        <v>0.3161</v>
+        <v>0.2824</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.3161</v>
+        <v>0.2824</v>
       </c>
       <c r="N29" t="n">
         <v>207</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.1979</v>
+        <v>0.1444</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0365</v>
+        <v>0.0266</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.5341</v>
+        <v>-0.54</v>
       </c>
       <c r="E30" t="n">
-        <v>0.1979</v>
+        <v>0.1444</v>
       </c>
       <c r="F30" t="n">
-        <v>0.1979</v>
+        <v>0.1444</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.1979</v>
+        <v>0.1444</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1979</v>
+        <v>0.1444</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0.1979</v>
+        <v>0.1444</v>
       </c>
       <c r="N30" t="n">
         <v>157</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.1489</v>
+        <v>-0.1911</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0275</v>
+        <v>-0.0352</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6919999999999999</v>
+        <v>-0.6928</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.1489</v>
+        <v>-0.1911</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.1489</v>
+        <v>-0.1911</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.1489</v>
+        <v>-0.1911</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.1489</v>
+        <v>-0.1911</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.1489</v>
+        <v>-0.1911</v>
       </c>
       <c r="N31" t="n">
         <v>119</v>
@@ -1872,124 +1872,124 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>roeJ</t>
+          <t>b0RUP</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.4295</v>
+        <v>-0.2781</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.07920000000000001</v>
+        <v>-0.0513</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8197</v>
+        <v>-0.7325</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.4295</v>
+        <v>-0.2781</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.4295</v>
+        <v>0.312</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>-0.5901</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.4295</v>
+        <v>0.312</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.4295</v>
+        <v>0.1752</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>-0.5901</v>
       </c>
       <c r="K32" t="n">
-        <v>119</v>
+        <v>154</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.4295</v>
+        <v>-0.4148999999999999</v>
       </c>
       <c r="N32" t="n">
-        <v>119</v>
+        <v>286</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>magixx</t>
+          <t>roeJ</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.4592</v>
+        <v>-0.4218</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.0847</v>
+        <v>-0.07779999999999999</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8332000000000001</v>
+        <v>-0.7979000000000001</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.4592</v>
+        <v>-0.4218</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.4592</v>
+        <v>-0.4218</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.4592</v>
+        <v>-0.4218</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.4592</v>
+        <v>-0.4218</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>157</v>
+        <v>119</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.4592</v>
+        <v>-0.4218</v>
       </c>
       <c r="N33" t="n">
-        <v>157</v>
+        <v>119</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>chopper</t>
+          <t>magixx</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.504</v>
+        <v>-0.4804</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.0929</v>
+        <v>-0.0886</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8536</v>
+        <v>-0.8246</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.504</v>
+        <v>-0.4804</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.504</v>
+        <v>-0.4804</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.504</v>
+        <v>-0.4804</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.504</v>
+        <v>-0.4804</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.504</v>
+        <v>-0.4804</v>
       </c>
       <c r="N34" t="n">
         <v>157</v>
@@ -2010,93 +2010,93 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>NBK-</t>
+          <t>chopper</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.514</v>
+        <v>-0.4911</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.0948</v>
+        <v>-0.0906</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8582</v>
+        <v>-0.8295</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.514</v>
+        <v>-0.4911</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.7907999999999999</v>
+        <v>-0.4911</v>
       </c>
       <c r="G35" t="n">
-        <v>0.2768</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.7907999999999999</v>
+        <v>-0.4911</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.427</v>
+        <v>-0.4911</v>
       </c>
       <c r="J35" t="n">
-        <v>0.2768</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>197</v>
+        <v>157</v>
       </c>
       <c r="L35" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.1502</v>
+        <v>-0.4911</v>
       </c>
       <c r="N35" t="n">
-        <v>278</v>
+        <v>157</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>b0RUP</t>
+          <t>NBK-</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.6187</v>
+        <v>-0.6</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.1141</v>
+        <v>-0.1106</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9058</v>
+        <v>-0.8791</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.6187</v>
+        <v>-0.6</v>
       </c>
       <c r="F36" t="n">
-        <v>0.0202</v>
+        <v>-0.8173</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.6389</v>
+        <v>0.2173</v>
       </c>
       <c r="H36" t="n">
-        <v>0.0202</v>
+        <v>-0.8173</v>
       </c>
       <c r="I36" t="n">
-        <v>0.0109</v>
+        <v>-0.4589</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.6389</v>
+        <v>0.2173</v>
       </c>
       <c r="K36" t="n">
-        <v>154</v>
+        <v>197</v>
       </c>
       <c r="L36" t="n">
-        <v>132</v>
+        <v>81</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.628</v>
+        <v>-0.2416</v>
       </c>
       <c r="N36" t="n">
-        <v>286</v>
+        <v>278</v>
       </c>
     </row>
     <row r="37">
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.9252</v>
+        <v>-1.0046</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.1706</v>
+        <v>-0.1853</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0454</v>
+        <v>-1.0634</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.9252</v>
+        <v>-1.0046</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.9252</v>
+        <v>-1.0046</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.9252</v>
+        <v>-1.0046</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.9252</v>
+        <v>-1.0046</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.9252</v>
+        <v>-1.0046</v>
       </c>
       <c r="N37" t="n">
         <v>207</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.2644</v>
+        <v>-1.2007</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.2332</v>
+        <v>-0.2214</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.1998</v>
+        <v>-1.1528</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.2644</v>
+        <v>-1.2007</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.2644</v>
+        <v>-1.2007</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.2644</v>
+        <v>-1.2007</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.2644</v>
+        <v>-1.2007</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.2644</v>
+        <v>-1.2007</v>
       </c>
       <c r="N38" t="n">
         <v>218</v>
@@ -2194,93 +2194,93 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>MiGHTYMAX</t>
+          <t>RUSH</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.8264</v>
+        <v>-1.7471</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.3368</v>
+        <v>-0.3222</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.4556</v>
+        <v>-1.4017</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.8264</v>
+        <v>-1.7471</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.8264</v>
+        <v>-1.8861</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>0.139</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.8264</v>
+        <v>-1.8861</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.8264</v>
+        <v>-1.059</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>0.139</v>
       </c>
       <c r="K39" t="n">
-        <v>207</v>
+        <v>146</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.8264</v>
+        <v>-0.9199999999999999</v>
       </c>
       <c r="N39" t="n">
-        <v>207</v>
+        <v>223</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>RUSH</t>
+          <t>MiGHTYMAX</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.9567</v>
+        <v>-1.7881</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.3608</v>
+        <v>-0.3297</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.5149</v>
+        <v>-1.4204</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.9567</v>
+        <v>-1.7881</v>
       </c>
       <c r="F40" t="n">
-        <v>-2.1271</v>
+        <v>-1.7881</v>
       </c>
       <c r="G40" t="n">
-        <v>0.1704</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-2.1271</v>
+        <v>-1.7881</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.1486</v>
+        <v>-1.7881</v>
       </c>
       <c r="J40" t="n">
-        <v>0.1704</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>146</v>
+        <v>207</v>
       </c>
       <c r="L40" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-0.9782000000000001</v>
+        <v>-1.7881</v>
       </c>
       <c r="N40" t="n">
-        <v>223</v>
+        <v>207</v>
       </c>
     </row>
     <row r="41">
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-3.7893</v>
+        <v>-3.5155</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.6988</v>
+        <v>-0.6483</v>
       </c>
       <c r="D41" t="n">
-        <v>-2.3492</v>
+        <v>-2.2073</v>
       </c>
       <c r="E41" t="n">
-        <v>-3.7893</v>
+        <v>-3.5155</v>
       </c>
       <c r="F41" t="n">
-        <v>-6.0518</v>
+        <v>-5.6569</v>
       </c>
       <c r="G41" t="n">
-        <v>2.2625</v>
+        <v>2.1414</v>
       </c>
       <c r="H41" t="n">
-        <v>-6.0518</v>
+        <v>-5.6569</v>
       </c>
       <c r="I41" t="n">
-        <v>-3.2679</v>
+        <v>-3.1762</v>
       </c>
       <c r="J41" t="n">
-        <v>2.2625</v>
+        <v>2.1414</v>
       </c>
       <c r="K41" t="n">
         <v>144</v>
@@ -2323,7 +2323,7 @@
         <v>136</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.0054</v>
+        <v>-1.0348</v>
       </c>
       <c r="N41" t="n">
         <v>280</v>
@@ -2429,10 +2429,10 @@
         <v>1.1</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2563</v>
+        <v>0.2091</v>
       </c>
       <c r="J2" t="n">
-        <v>6.9201</v>
+        <v>5.6457</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.09</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2363</v>
+        <v>0.1911</v>
       </c>
       <c r="J3" t="n">
-        <v>6.3801</v>
+        <v>5.1597</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.04</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1275</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>3.4425</v>
+        <v>2.5974</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.85</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1997</v>
+        <v>-0.1791</v>
       </c>
       <c r="J5" t="n">
-        <v>-5.3919</v>
+        <v>-4.8357</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.82</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2306</v>
+        <v>-0.2102</v>
       </c>
       <c r="J6" t="n">
-        <v>-6.2262</v>
+        <v>-5.6754</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.44</v>
       </c>
       <c r="I7" t="n">
-        <v>1.0454</v>
+        <v>1.0422</v>
       </c>
       <c r="J7" t="n">
-        <v>28.2258</v>
+        <v>28.1394</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.4</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9677</v>
+        <v>0.956</v>
       </c>
       <c r="J8" t="n">
-        <v>26.1279</v>
+        <v>25.812</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0222</v>
+        <v>-0.0169</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.5994</v>
+        <v>-0.4563</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0222</v>
+        <v>-0.0169</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.5994</v>
+        <v>-0.4563</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.84</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5201</v>
+        <v>-0.4798</v>
       </c>
       <c r="J11" t="n">
-        <v>-14.0427</v>
+        <v>-12.9546</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.13</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3327</v>
+        <v>0.2808</v>
       </c>
       <c r="J12" t="n">
-        <v>9.3156</v>
+        <v>7.8624</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>0.99</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.0177</v>
+        <v>-0.0129</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.4956</v>
+        <v>-0.3612</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.98</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.0356</v>
+        <v>-0.0278</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.9968</v>
+        <v>-0.7784</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.82</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2234</v>
+        <v>-0.2035</v>
       </c>
       <c r="J15" t="n">
-        <v>-6.2552</v>
+        <v>-5.698</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.6</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4287</v>
+        <v>-0.4205</v>
       </c>
       <c r="J16" t="n">
-        <v>-12.0036</v>
+        <v>-11.774</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.28</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7288</v>
+        <v>0.6978</v>
       </c>
       <c r="J17" t="n">
-        <v>20.4064</v>
+        <v>19.5384</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.16</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4658</v>
+        <v>0.427</v>
       </c>
       <c r="J18" t="n">
-        <v>13.0424</v>
+        <v>11.956</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.08</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2692</v>
+        <v>0.2357</v>
       </c>
       <c r="J19" t="n">
-        <v>7.5376</v>
+        <v>6.5996</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.05</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1827</v>
+        <v>0.1548</v>
       </c>
       <c r="J20" t="n">
-        <v>5.1156</v>
+        <v>4.3344</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>1.04</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1512</v>
+        <v>0.1261</v>
       </c>
       <c r="J21" t="n">
-        <v>4.2336</v>
+        <v>3.5308</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.14</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2635</v>
+        <v>0.2491</v>
       </c>
       <c r="J22" t="n">
-        <v>6.5875</v>
+        <v>6.2275</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.14</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2635</v>
+        <v>0.2491</v>
       </c>
       <c r="J23" t="n">
-        <v>6.5875</v>
+        <v>6.2275</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.87</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1768</v>
+        <v>-0.1567</v>
       </c>
       <c r="J24" t="n">
-        <v>-4.42</v>
+        <v>-3.9175</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.83</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.2187</v>
+        <v>-0.1983</v>
       </c>
       <c r="J25" t="n">
-        <v>-5.4675</v>
+        <v>-4.9575</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.83</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.2187</v>
+        <v>-0.1983</v>
       </c>
       <c r="J26" t="n">
-        <v>-5.4675</v>
+        <v>-4.9575</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.64</v>
       </c>
       <c r="I27" t="n">
-        <v>0.6828</v>
+        <v>0.6393</v>
       </c>
       <c r="J27" t="n">
-        <v>17.07</v>
+        <v>15.9825</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.39</v>
       </c>
       <c r="I28" t="n">
-        <v>0.4939</v>
+        <v>0.4447</v>
       </c>
       <c r="J28" t="n">
-        <v>12.3475</v>
+        <v>11.1175</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.19</v>
       </c>
       <c r="I29" t="n">
-        <v>0.2883</v>
+        <v>0.2365</v>
       </c>
       <c r="J29" t="n">
-        <v>7.2075</v>
+        <v>5.9125</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>1.07</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1273</v>
+        <v>0.0975</v>
       </c>
       <c r="J30" t="n">
-        <v>3.1825</v>
+        <v>2.4375</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.61</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.4414</v>
+        <v>-0.4379</v>
       </c>
       <c r="J31" t="n">
-        <v>-11.035</v>
+        <v>-10.9475</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.55</v>
       </c>
       <c r="I32" t="n">
-        <v>1.026</v>
+        <v>1.0145</v>
       </c>
       <c r="J32" t="n">
-        <v>26.676</v>
+        <v>26.377</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.34</v>
       </c>
       <c r="I33" t="n">
-        <v>0.7309</v>
+        <v>0.7161999999999999</v>
       </c>
       <c r="J33" t="n">
-        <v>19.0034</v>
+        <v>18.6212</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.2</v>
       </c>
       <c r="I34" t="n">
-        <v>0.5175999999999999</v>
+        <v>0.5078</v>
       </c>
       <c r="J34" t="n">
-        <v>13.4576</v>
+        <v>13.2028</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.12</v>
       </c>
       <c r="I35" t="n">
-        <v>0.3618</v>
+        <v>0.3278</v>
       </c>
       <c r="J35" t="n">
-        <v>9.4068</v>
+        <v>8.5228</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.77</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.6925</v>
+        <v>-0.6631</v>
       </c>
       <c r="J36" t="n">
-        <v>-18.005</v>
+        <v>-17.2406</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.05</v>
       </c>
       <c r="I37" t="n">
-        <v>0.1766</v>
+        <v>0.1391</v>
       </c>
       <c r="J37" t="n">
-        <v>4.5916</v>
+        <v>3.6166</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>0.96</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.0614</v>
+        <v>-0.0505</v>
       </c>
       <c r="J38" t="n">
-        <v>-1.5964</v>
+        <v>-1.313</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.96</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.0614</v>
+        <v>-0.0505</v>
       </c>
       <c r="J39" t="n">
-        <v>-1.5964</v>
+        <v>-1.313</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.68</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.3529</v>
+        <v>-0.3378</v>
       </c>
       <c r="J40" t="n">
-        <v>-9.1754</v>
+        <v>-8.7828</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.67</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.362</v>
+        <v>-0.3476</v>
       </c>
       <c r="J41" t="n">
-        <v>-9.412000000000001</v>
+        <v>-9.037599999999999</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.21</v>
       </c>
       <c r="I42" t="n">
-        <v>0.5567</v>
+        <v>0.5452</v>
       </c>
       <c r="J42" t="n">
-        <v>16.701</v>
+        <v>16.356</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.13</v>
       </c>
       <c r="I43" t="n">
-        <v>0.4091</v>
+        <v>0.3675</v>
       </c>
       <c r="J43" t="n">
-        <v>12.273</v>
+        <v>11.025</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.02</v>
       </c>
       <c r="I44" t="n">
-        <v>0.0948</v>
+        <v>0.0743</v>
       </c>
       <c r="J44" t="n">
-        <v>2.844</v>
+        <v>2.229</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.0053</v>
+        <v>-0.003</v>
       </c>
       <c r="J45" t="n">
-        <v>-0.159</v>
+        <v>-0.09</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.84</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.5014</v>
+        <v>-0.4594</v>
       </c>
       <c r="J46" t="n">
-        <v>-15.042</v>
+        <v>-13.782</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.56</v>
       </c>
       <c r="I47" t="n">
-        <v>0.8339</v>
+        <v>0.7982</v>
       </c>
       <c r="J47" t="n">
-        <v>25.017</v>
+        <v>23.946</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>0.99</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.0271</v>
+        <v>-0.0193</v>
       </c>
       <c r="J48" t="n">
-        <v>-0.8129999999999999</v>
+        <v>-0.579</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.99</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.0271</v>
+        <v>-0.0193</v>
       </c>
       <c r="J49" t="n">
-        <v>-0.8129999999999999</v>
+        <v>-0.579</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.9</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.1495</v>
+        <v>-0.1296</v>
       </c>
       <c r="J50" t="n">
-        <v>-4.485</v>
+        <v>-3.888</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.71</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.3411</v>
+        <v>-0.326</v>
       </c>
       <c r="J51" t="n">
-        <v>-10.233</v>
+        <v>-9.779999999999999</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.74</v>
       </c>
       <c r="I52" t="n">
-        <v>0.7295</v>
+        <v>0.6818</v>
       </c>
       <c r="J52" t="n">
-        <v>14.59</v>
+        <v>13.636</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.42</v>
       </c>
       <c r="I53" t="n">
-        <v>0.5022</v>
+        <v>0.4586</v>
       </c>
       <c r="J53" t="n">
-        <v>10.044</v>
+        <v>9.172000000000001</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.3</v>
       </c>
       <c r="I54" t="n">
-        <v>0.4013</v>
+        <v>0.3435</v>
       </c>
       <c r="J54" t="n">
-        <v>8.026</v>
+        <v>6.87</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1.2</v>
       </c>
       <c r="I55" t="n">
-        <v>0.2867</v>
+        <v>0.2383</v>
       </c>
       <c r="J55" t="n">
-        <v>5.734</v>
+        <v>4.766</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>1.17</v>
       </c>
       <c r="I56" t="n">
-        <v>0.2496</v>
+        <v>0.2047</v>
       </c>
       <c r="J56" t="n">
-        <v>4.992</v>
+        <v>4.094</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.2102</v>
+        <v>-0.1951</v>
       </c>
       <c r="J57" t="n">
-        <v>-4.204</v>
+        <v>-3.902</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>0.79</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.2309</v>
+        <v>-0.2162</v>
       </c>
       <c r="J58" t="n">
-        <v>-4.618</v>
+        <v>-4.324</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.72</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.2988</v>
+        <v>-0.2853</v>
       </c>
       <c r="J59" t="n">
-        <v>-5.976</v>
+        <v>-5.706</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.3254</v>
+        <v>-0.3122</v>
       </c>
       <c r="J60" t="n">
-        <v>-6.508</v>
+        <v>-6.244</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.44</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.5452</v>
+        <v>-0.5493</v>
       </c>
       <c r="J61" t="n">
-        <v>-10.904</v>
+        <v>-10.986</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.43</v>
       </c>
       <c r="I62" t="n">
-        <v>0.7136</v>
+        <v>0.6826</v>
       </c>
       <c r="J62" t="n">
-        <v>16.4128</v>
+        <v>15.6998</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>0.99</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.023</v>
+        <v>-0.017</v>
       </c>
       <c r="J63" t="n">
-        <v>-0.529</v>
+        <v>-0.391</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>0.97</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.0561</v>
+        <v>-0.0446</v>
       </c>
       <c r="J64" t="n">
-        <v>-1.2903</v>
+        <v>-1.0258</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.74</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.3067</v>
+        <v>-0.289</v>
       </c>
       <c r="J65" t="n">
-        <v>-7.0541</v>
+        <v>-6.647</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.67</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.3715</v>
+        <v>-0.3582</v>
       </c>
       <c r="J66" t="n">
-        <v>-8.544499999999999</v>
+        <v>-8.2386</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.63</v>
       </c>
       <c r="I67" t="n">
-        <v>1.1301</v>
+        <v>1.1235</v>
       </c>
       <c r="J67" t="n">
-        <v>25.9923</v>
+        <v>25.8405</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.25</v>
       </c>
       <c r="I68" t="n">
-        <v>0.5943000000000001</v>
+        <v>0.585</v>
       </c>
       <c r="J68" t="n">
-        <v>13.6689</v>
+        <v>13.455</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.16</v>
       </c>
       <c r="I69" t="n">
-        <v>0.4502</v>
+        <v>0.4214</v>
       </c>
       <c r="J69" t="n">
-        <v>10.3546</v>
+        <v>9.6922</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>1.02</v>
       </c>
       <c r="I70" t="n">
-        <v>0.06619999999999999</v>
+        <v>0.0501</v>
       </c>
       <c r="J70" t="n">
-        <v>1.5226</v>
+        <v>1.1523</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.98</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.1363</v>
+        <v>-0.1092</v>
       </c>
       <c r="J71" t="n">
-        <v>-3.1349</v>
+        <v>-2.5116</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.19</v>
       </c>
       <c r="I72" t="n">
-        <v>0.426</v>
+        <v>0.3707</v>
       </c>
       <c r="J72" t="n">
-        <v>14.484</v>
+        <v>12.6038</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.02</v>
       </c>
       <c r="I73" t="n">
-        <v>0.0795</v>
+        <v>0.0565</v>
       </c>
       <c r="J73" t="n">
-        <v>2.703</v>
+        <v>1.921</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.98</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.0404</v>
+        <v>-0.0313</v>
       </c>
       <c r="J74" t="n">
-        <v>-1.3736</v>
+        <v>-1.0642</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.84</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.2079</v>
+        <v>-0.1875</v>
       </c>
       <c r="J75" t="n">
-        <v>-7.0686</v>
+        <v>-6.375</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.75</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.2969</v>
+        <v>-0.2786</v>
       </c>
       <c r="J76" t="n">
-        <v>-10.0946</v>
+        <v>-9.4724</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.23</v>
       </c>
       <c r="I77" t="n">
-        <v>0.5821</v>
+        <v>0.5701000000000001</v>
       </c>
       <c r="J77" t="n">
-        <v>19.7914</v>
+        <v>19.3834</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.2</v>
       </c>
       <c r="I78" t="n">
-        <v>0.5327</v>
+        <v>0.5206</v>
       </c>
       <c r="J78" t="n">
-        <v>18.1118</v>
+        <v>17.7004</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.19</v>
       </c>
       <c r="I79" t="n">
-        <v>0.5159</v>
+        <v>0.501</v>
       </c>
       <c r="J79" t="n">
-        <v>17.5406</v>
+        <v>17.034</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1.06</v>
       </c>
       <c r="I80" t="n">
-        <v>0.2193</v>
+        <v>0.187</v>
       </c>
       <c r="J80" t="n">
-        <v>7.4562</v>
+        <v>6.358</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.71</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.8028999999999999</v>
+        <v>-0.7795</v>
       </c>
       <c r="J81" t="n">
-        <v>-27.2986</v>
+        <v>-26.503</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.17</v>
       </c>
       <c r="I82" t="n">
-        <v>0.3938</v>
+        <v>0.3382</v>
       </c>
       <c r="J82" t="n">
-        <v>11.814</v>
+        <v>10.146</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>0.99</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.0222</v>
+        <v>-0.0165</v>
       </c>
       <c r="J83" t="n">
-        <v>-0.666</v>
+        <v>-0.495</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.96</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.0697</v>
+        <v>-0.0567</v>
       </c>
       <c r="J84" t="n">
-        <v>-2.091</v>
+        <v>-1.701</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.84</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.2073</v>
+        <v>-0.187</v>
       </c>
       <c r="J85" t="n">
-        <v>-6.219</v>
+        <v>-5.61</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.79</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.2576</v>
+        <v>-0.2379</v>
       </c>
       <c r="J86" t="n">
-        <v>-7.728</v>
+        <v>-7.137</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.53</v>
       </c>
       <c r="I87" t="n">
-        <v>1.1448</v>
+        <v>1.1578</v>
       </c>
       <c r="J87" t="n">
-        <v>34.344</v>
+        <v>34.734</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.36</v>
       </c>
       <c r="I88" t="n">
-        <v>0.872</v>
+        <v>0.8528</v>
       </c>
       <c r="J88" t="n">
-        <v>26.16</v>
+        <v>25.584</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.15</v>
       </c>
       <c r="I89" t="n">
-        <v>0.4333</v>
+        <v>0.3988</v>
       </c>
       <c r="J89" t="n">
-        <v>12.999</v>
+        <v>11.964</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>1.13</v>
       </c>
       <c r="I90" t="n">
-        <v>0.3855</v>
+        <v>0.3513</v>
       </c>
       <c r="J90" t="n">
-        <v>11.565</v>
+        <v>10.539</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.84</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.5318000000000001</v>
+        <v>-0.4935</v>
       </c>
       <c r="J91" t="n">
-        <v>-15.954</v>
+        <v>-14.805</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.08</v>
       </c>
       <c r="I92" t="n">
-        <v>0.2219</v>
+        <v>0.178</v>
       </c>
       <c r="J92" t="n">
-        <v>5.7694</v>
+        <v>4.628</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.04</v>
       </c>
       <c r="I93" t="n">
-        <v>0.1327</v>
+        <v>0.1001</v>
       </c>
       <c r="J93" t="n">
-        <v>3.4502</v>
+        <v>2.6026</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.98</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.0399</v>
+        <v>-0.031</v>
       </c>
       <c r="J94" t="n">
-        <v>-1.0374</v>
+        <v>-0.806</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.9</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.1427</v>
+        <v>-0.1239</v>
       </c>
       <c r="J95" t="n">
-        <v>-3.7102</v>
+        <v>-3.2214</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.75</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.2963</v>
+        <v>-0.278</v>
       </c>
       <c r="J96" t="n">
-        <v>-7.7038</v>
+        <v>-7.228</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.34</v>
       </c>
       <c r="I97" t="n">
-        <v>0.8366</v>
+        <v>0.8142</v>
       </c>
       <c r="J97" t="n">
-        <v>21.7516</v>
+        <v>21.1692</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.24</v>
       </c>
       <c r="I98" t="n">
-        <v>0.632</v>
+        <v>0.5989</v>
       </c>
       <c r="J98" t="n">
-        <v>16.432</v>
+        <v>15.5714</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.17</v>
       </c>
       <c r="I99" t="n">
-        <v>0.4815</v>
+        <v>0.446</v>
       </c>
       <c r="J99" t="n">
-        <v>12.519</v>
+        <v>11.596</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>1.14</v>
       </c>
       <c r="I100" t="n">
-        <v>0.4122</v>
+        <v>0.3771</v>
       </c>
       <c r="J100" t="n">
-        <v>10.7172</v>
+        <v>9.804600000000001</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>1.03</v>
       </c>
       <c r="I101" t="n">
-        <v>0.1069</v>
+        <v>0.0863</v>
       </c>
       <c r="J101" t="n">
-        <v>2.7794</v>
+        <v>2.2438</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>0.74</v>
       </c>
       <c r="I102" t="n">
-        <v>-0.2541</v>
+        <v>-0.2396</v>
       </c>
       <c r="J102" t="n">
-        <v>-4.8279</v>
+        <v>-4.5524</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>0.62</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.3719</v>
+        <v>-0.3647</v>
       </c>
       <c r="J103" t="n">
-        <v>-7.0661</v>
+        <v>-6.9293</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.53</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.4488</v>
+        <v>-0.444</v>
       </c>
       <c r="J104" t="n">
-        <v>-8.527200000000001</v>
+        <v>-8.436</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.52</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.4575</v>
+        <v>-0.4531</v>
       </c>
       <c r="J105" t="n">
-        <v>-8.692500000000001</v>
+        <v>-8.6089</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.42</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.5454</v>
+        <v>-0.5487</v>
       </c>
       <c r="J106" t="n">
-        <v>-10.3626</v>
+        <v>-10.4253</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.79</v>
       </c>
       <c r="I107" t="n">
-        <v>1.4176</v>
+        <v>1.4447</v>
       </c>
       <c r="J107" t="n">
-        <v>26.9344</v>
+        <v>27.4493</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.73</v>
       </c>
       <c r="I108" t="n">
-        <v>1.3454</v>
+        <v>1.3692</v>
       </c>
       <c r="J108" t="n">
-        <v>25.5626</v>
+        <v>26.0148</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.63</v>
       </c>
       <c r="I109" t="n">
-        <v>1.2232</v>
+        <v>1.2432</v>
       </c>
       <c r="J109" t="n">
-        <v>23.2408</v>
+        <v>23.6208</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>1.4</v>
       </c>
       <c r="I110" t="n">
-        <v>0.9035</v>
+        <v>0.9006</v>
       </c>
       <c r="J110" t="n">
-        <v>17.1665</v>
+        <v>17.1114</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>1.05</v>
       </c>
       <c r="I111" t="n">
-        <v>0.12</v>
+        <v>0.0897</v>
       </c>
       <c r="J111" t="n">
-        <v>2.28</v>
+        <v>1.7043</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.35</v>
       </c>
       <c r="I112" t="n">
-        <v>0.6784</v>
+        <v>0.6217</v>
       </c>
       <c r="J112" t="n">
-        <v>20.352</v>
+        <v>18.651</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.01</v>
       </c>
       <c r="I113" t="n">
-        <v>0.0444</v>
+        <v>0.0298</v>
       </c>
       <c r="J113" t="n">
-        <v>1.332</v>
+        <v>0.894</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.99</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.0248</v>
+        <v>-0.018</v>
       </c>
       <c r="J114" t="n">
-        <v>-0.744</v>
+        <v>-0.54</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.85</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.2006</v>
+        <v>-0.18</v>
       </c>
       <c r="J115" t="n">
-        <v>-6.018</v>
+        <v>-5.4</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.75</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.3</v>
+        <v>-0.2821</v>
       </c>
       <c r="J116" t="n">
-        <v>-9</v>
+        <v>-8.462999999999999</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.1</v>
       </c>
       <c r="I117" t="n">
-        <v>0.3424</v>
+        <v>0.3005</v>
       </c>
       <c r="J117" t="n">
-        <v>10.272</v>
+        <v>9.015000000000001</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.01</v>
       </c>
       <c r="I118" t="n">
-        <v>0.059</v>
+        <v>0.0428</v>
       </c>
       <c r="J118" t="n">
-        <v>1.77</v>
+        <v>1.284</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>0.97</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.1351</v>
+        <v>-0.1074</v>
       </c>
       <c r="J119" t="n">
-        <v>-4.053</v>
+        <v>-3.222</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.96</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.1684</v>
+        <v>-0.137</v>
       </c>
       <c r="J120" t="n">
-        <v>-5.052</v>
+        <v>-4.11</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.95</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.1999</v>
+        <v>-0.1656</v>
       </c>
       <c r="J121" t="n">
-        <v>-5.997</v>
+        <v>-4.968</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.63</v>
       </c>
       <c r="I122" t="n">
-        <v>1.3093</v>
+        <v>1.3341</v>
       </c>
       <c r="J122" t="n">
-        <v>39.279</v>
+        <v>40.023</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.03</v>
       </c>
       <c r="I123" t="n">
-        <v>0.1218</v>
+        <v>0.0993</v>
       </c>
       <c r="J123" t="n">
-        <v>3.654</v>
+        <v>2.979</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.01</v>
       </c>
       <c r="I124" t="n">
-        <v>0.0443</v>
+        <v>0.0331</v>
       </c>
       <c r="J124" t="n">
-        <v>1.329</v>
+        <v>0.993</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.92</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.3068</v>
+        <v>-0.2654</v>
       </c>
       <c r="J125" t="n">
-        <v>-9.204000000000001</v>
+        <v>-7.962</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.9</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.3613</v>
+        <v>-0.3188</v>
       </c>
       <c r="J126" t="n">
-        <v>-10.839</v>
+        <v>-9.564</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.36</v>
       </c>
       <c r="I127" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.6333</v>
       </c>
       <c r="J127" t="n">
-        <v>20.7</v>
+        <v>18.999</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.18</v>
       </c>
       <c r="I128" t="n">
-        <v>0.3988</v>
+        <v>0.3426</v>
       </c>
       <c r="J128" t="n">
-        <v>11.964</v>
+        <v>10.278</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.03</v>
       </c>
       <c r="I129" t="n">
-        <v>0.0997</v>
+        <v>0.0737</v>
       </c>
       <c r="J129" t="n">
-        <v>2.991</v>
+        <v>2.211</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1.01</v>
       </c>
       <c r="I130" t="n">
-        <v>0.0432</v>
+        <v>0.0292</v>
       </c>
       <c r="J130" t="n">
-        <v>1.296</v>
+        <v>0.876</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.43</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.5814</v>
+        <v>-0.5955</v>
       </c>
       <c r="J131" t="n">
-        <v>-17.442</v>
+        <v>-17.865</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.3</v>
       </c>
       <c r="I132" t="n">
-        <v>0.7635999999999999</v>
+        <v>0.7353</v>
       </c>
       <c r="J132" t="n">
-        <v>22.1444</v>
+        <v>21.3237</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.16</v>
       </c>
       <c r="I133" t="n">
-        <v>0.4621</v>
+        <v>0.4249</v>
       </c>
       <c r="J133" t="n">
-        <v>13.4009</v>
+        <v>12.3221</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.16</v>
       </c>
       <c r="I134" t="n">
-        <v>0.4621</v>
+        <v>0.4249</v>
       </c>
       <c r="J134" t="n">
-        <v>13.4009</v>
+        <v>12.3221</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.08</v>
       </c>
       <c r="I135" t="n">
-        <v>0.2649</v>
+        <v>0.2325</v>
       </c>
       <c r="J135" t="n">
-        <v>7.6821</v>
+        <v>6.7425</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>1.05</v>
       </c>
       <c r="I136" t="n">
-        <v>0.178</v>
+        <v>0.151</v>
       </c>
       <c r="J136" t="n">
-        <v>5.162</v>
+        <v>4.379</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>0.9</v>
       </c>
       <c r="I137" t="n">
-        <v>-0.1309</v>
+        <v>-0.1157</v>
       </c>
       <c r="J137" t="n">
-        <v>-3.7961</v>
+        <v>-3.3553</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>0.83</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.2063</v>
+        <v>-0.1889</v>
       </c>
       <c r="J138" t="n">
-        <v>-5.9827</v>
+        <v>-5.4781</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.82</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.2161</v>
+        <v>-0.1985</v>
       </c>
       <c r="J139" t="n">
-        <v>-6.2669</v>
+        <v>-5.7565</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.8</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.235</v>
+        <v>-0.2172</v>
       </c>
       <c r="J140" t="n">
-        <v>-6.815</v>
+        <v>-6.2988</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.71</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.3197</v>
+        <v>-0.3031</v>
       </c>
       <c r="J141" t="n">
-        <v>-9.2713</v>
+        <v>-8.789899999999999</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.22</v>
       </c>
       <c r="I142" t="n">
-        <v>0.6131</v>
+        <v>0.5753</v>
       </c>
       <c r="J142" t="n">
-        <v>18.393</v>
+        <v>17.259</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.21</v>
       </c>
       <c r="I143" t="n">
-        <v>0.5908</v>
+        <v>0.5521</v>
       </c>
       <c r="J143" t="n">
-        <v>17.724</v>
+        <v>16.563</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.18</v>
       </c>
       <c r="I144" t="n">
-        <v>0.5226</v>
+        <v>0.4821</v>
       </c>
       <c r="J144" t="n">
-        <v>15.678</v>
+        <v>14.463</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1.16</v>
       </c>
       <c r="I145" t="n">
-        <v>0.4759</v>
+        <v>0.4348</v>
       </c>
       <c r="J145" t="n">
-        <v>14.277</v>
+        <v>13.044</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.57</v>
       </c>
       <c r="I146" t="n">
-        <v>-1.0899</v>
+        <v>-1.1</v>
       </c>
       <c r="J146" t="n">
-        <v>-32.697</v>
+        <v>-33</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.19</v>
       </c>
       <c r="I147" t="n">
-        <v>0.4148</v>
+        <v>0.3579</v>
       </c>
       <c r="J147" t="n">
-        <v>12.444</v>
+        <v>10.737</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.04</v>
       </c>
       <c r="I148" t="n">
-        <v>0.1236</v>
+        <v>0.0936</v>
       </c>
       <c r="J148" t="n">
-        <v>3.708</v>
+        <v>2.808</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.04</v>
       </c>
       <c r="I149" t="n">
-        <v>0.1236</v>
+        <v>0.0936</v>
       </c>
       <c r="J149" t="n">
-        <v>3.708</v>
+        <v>2.808</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.89</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.1589</v>
+        <v>-0.1388</v>
       </c>
       <c r="J150" t="n">
-        <v>-4.767</v>
+        <v>-4.164</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.88</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.17</v>
+        <v>-0.1497</v>
       </c>
       <c r="J151" t="n">
-        <v>-5.1</v>
+        <v>-4.491</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.71</v>
       </c>
       <c r="I152" t="n">
-        <v>1.3671</v>
+        <v>1.3906</v>
       </c>
       <c r="J152" t="n">
-        <v>35.5446</v>
+        <v>36.1556</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.65</v>
       </c>
       <c r="I153" t="n">
-        <v>1.2898</v>
+        <v>1.3087</v>
       </c>
       <c r="J153" t="n">
-        <v>33.5348</v>
+        <v>34.0262</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.16</v>
       </c>
       <c r="I154" t="n">
-        <v>0.4471</v>
+        <v>0.4147</v>
       </c>
       <c r="J154" t="n">
-        <v>11.6246</v>
+        <v>10.7822</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.93</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.3084</v>
+        <v>-0.2703</v>
       </c>
       <c r="J155" t="n">
-        <v>-8.0184</v>
+        <v>-7.0278</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.88</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.4434</v>
+        <v>-0.4044</v>
       </c>
       <c r="J156" t="n">
-        <v>-11.5284</v>
+        <v>-10.5144</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.17</v>
       </c>
       <c r="I157" t="n">
-        <v>0.4161</v>
+        <v>0.3622</v>
       </c>
       <c r="J157" t="n">
-        <v>10.8186</v>
+        <v>9.417199999999999</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>0.97</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.0482</v>
+        <v>-0.0387</v>
       </c>
       <c r="J158" t="n">
-        <v>-1.2532</v>
+        <v>-1.0062</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>0.85</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.1905</v>
+        <v>-0.1716</v>
       </c>
       <c r="J159" t="n">
-        <v>-4.953</v>
+        <v>-4.4616</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.72</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.3172</v>
+        <v>-0.3</v>
       </c>
       <c r="J160" t="n">
-        <v>-8.247199999999999</v>
+        <v>-7.8</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.67</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.3632</v>
+        <v>-0.3489</v>
       </c>
       <c r="J161" t="n">
-        <v>-9.443199999999999</v>
+        <v>-9.071400000000001</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.54</v>
       </c>
       <c r="I162" t="n">
-        <v>1.157</v>
+        <v>1.1704</v>
       </c>
       <c r="J162" t="n">
-        <v>33.553</v>
+        <v>33.9416</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.33</v>
       </c>
       <c r="I163" t="n">
-        <v>0.8115</v>
+        <v>0.7882</v>
       </c>
       <c r="J163" t="n">
-        <v>23.5335</v>
+        <v>22.8578</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.3</v>
       </c>
       <c r="I164" t="n">
-        <v>0.7514999999999999</v>
+        <v>0.7245</v>
       </c>
       <c r="J164" t="n">
-        <v>21.7935</v>
+        <v>21.0105</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1.04</v>
       </c>
       <c r="I165" t="n">
-        <v>0.1364</v>
+        <v>0.1128</v>
       </c>
       <c r="J165" t="n">
-        <v>3.9556</v>
+        <v>3.2712</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.83</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.5567</v>
+        <v>-0.5195</v>
       </c>
       <c r="J166" t="n">
-        <v>-16.1443</v>
+        <v>-15.0655</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.12</v>
       </c>
       <c r="I167" t="n">
-        <v>0.3086</v>
+        <v>0.2577</v>
       </c>
       <c r="J167" t="n">
-        <v>8.949400000000001</v>
+        <v>7.4733</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>0.98</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.0375</v>
+        <v>-0.0293</v>
       </c>
       <c r="J168" t="n">
-        <v>-1.0875</v>
+        <v>-0.8497</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.9</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.1406</v>
+        <v>-0.1225</v>
       </c>
       <c r="J169" t="n">
-        <v>-4.0774</v>
+        <v>-3.5525</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.84</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.2048</v>
+        <v>-0.1847</v>
       </c>
       <c r="J170" t="n">
-        <v>-5.9392</v>
+        <v>-5.3563</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.77</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.2744</v>
+        <v>-0.2553</v>
       </c>
       <c r="J171" t="n">
-        <v>-7.9576</v>
+        <v>-7.4037</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.22</v>
       </c>
       <c r="I172" t="n">
-        <v>0.4333</v>
+        <v>0.4492</v>
       </c>
       <c r="J172" t="n">
-        <v>9.099299999999999</v>
+        <v>9.433199999999999</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>0.8</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.2318</v>
+        <v>-0.2154</v>
       </c>
       <c r="J173" t="n">
-        <v>-4.8678</v>
+        <v>-4.5234</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.74</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.2874</v>
+        <v>-0.2709</v>
       </c>
       <c r="J174" t="n">
-        <v>-6.0354</v>
+        <v>-5.6889</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.72</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.3057</v>
+        <v>-0.2895</v>
       </c>
       <c r="J175" t="n">
-        <v>-6.4197</v>
+        <v>-6.0795</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.36</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.6221</v>
+        <v>-0.6399</v>
       </c>
       <c r="J176" t="n">
-        <v>-13.0641</v>
+        <v>-13.4379</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.6</v>
       </c>
       <c r="I177" t="n">
-        <v>0.7122000000000001</v>
+        <v>0.64</v>
       </c>
       <c r="J177" t="n">
-        <v>14.9562</v>
+        <v>13.44</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.44</v>
       </c>
       <c r="I178" t="n">
-        <v>0.553</v>
+        <v>0.4839</v>
       </c>
       <c r="J178" t="n">
-        <v>11.613</v>
+        <v>10.1619</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.34</v>
       </c>
       <c r="I179" t="n">
-        <v>0.449</v>
+        <v>0.3854</v>
       </c>
       <c r="J179" t="n">
-        <v>9.429</v>
+        <v>8.093400000000001</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.04</v>
       </c>
       <c r="I180" t="n">
-        <v>0.0682</v>
+        <v>0.0485</v>
       </c>
       <c r="J180" t="n">
-        <v>1.4322</v>
+        <v>1.0185</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.98</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.0638</v>
+        <v>-0.0519</v>
       </c>
       <c r="J181" t="n">
-        <v>-1.3398</v>
+        <v>-1.0899</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.43</v>
       </c>
       <c r="I182" t="n">
-        <v>0.9862</v>
+        <v>0.9825</v>
       </c>
       <c r="J182" t="n">
-        <v>24.655</v>
+        <v>24.5625</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.26</v>
       </c>
       <c r="I183" t="n">
-        <v>0.6627999999999999</v>
+        <v>0.6354</v>
       </c>
       <c r="J183" t="n">
-        <v>16.57</v>
+        <v>15.885</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.24</v>
       </c>
       <c r="I184" t="n">
-        <v>0.622</v>
+        <v>0.5931999999999999</v>
       </c>
       <c r="J184" t="n">
-        <v>15.55</v>
+        <v>14.83</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>1.24</v>
       </c>
       <c r="I185" t="n">
-        <v>0.622</v>
+        <v>0.5931999999999999</v>
       </c>
       <c r="J185" t="n">
-        <v>15.55</v>
+        <v>14.83</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>1.19</v>
       </c>
       <c r="I186" t="n">
-        <v>0.5145</v>
+        <v>0.4832</v>
       </c>
       <c r="J186" t="n">
-        <v>12.8625</v>
+        <v>12.08</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.23</v>
       </c>
       <c r="I187" t="n">
-        <v>0.5123</v>
+        <v>0.4563</v>
       </c>
       <c r="J187" t="n">
-        <v>12.8075</v>
+        <v>11.4075</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>0.99</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.0177</v>
+        <v>-0.0129</v>
       </c>
       <c r="J188" t="n">
-        <v>-0.4425</v>
+        <v>-0.3225</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.86</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.1824</v>
+        <v>-0.163</v>
       </c>
       <c r="J189" t="n">
-        <v>-4.56</v>
+        <v>-4.075</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.74</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.3013</v>
+        <v>-0.2832</v>
       </c>
       <c r="J190" t="n">
-        <v>-7.5325</v>
+        <v>-7.08</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.7</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.3386</v>
+        <v>-0.3227</v>
       </c>
       <c r="J191" t="n">
-        <v>-8.465</v>
+        <v>-8.067500000000001</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>0.65</v>
       </c>
       <c r="I192" t="n">
-        <v>-0.3249</v>
+        <v>-0.3147</v>
       </c>
       <c r="J192" t="n">
-        <v>-5.1984</v>
+        <v>-5.0352</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>0.63</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.3451</v>
+        <v>-0.3369</v>
       </c>
       <c r="J193" t="n">
-        <v>-5.5216</v>
+        <v>-5.3904</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>0.43</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.5246</v>
+        <v>-0.5265</v>
       </c>
       <c r="J194" t="n">
-        <v>-8.393599999999999</v>
+        <v>-8.423999999999999</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.39</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.5602</v>
+        <v>-0.5655</v>
       </c>
       <c r="J195" t="n">
-        <v>-8.963200000000001</v>
+        <v>-9.048</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.38</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.5692</v>
+        <v>-0.5755</v>
       </c>
       <c r="J196" t="n">
-        <v>-9.107200000000001</v>
+        <v>-9.208</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>2.11</v>
       </c>
       <c r="I197" t="n">
-        <v>1.0872</v>
+        <v>1.0466</v>
       </c>
       <c r="J197" t="n">
-        <v>17.3952</v>
+        <v>16.7456</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.65</v>
       </c>
       <c r="I198" t="n">
-        <v>0.7238</v>
+        <v>0.6573</v>
       </c>
       <c r="J198" t="n">
-        <v>11.5808</v>
+        <v>10.5168</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.54</v>
       </c>
       <c r="I199" t="n">
-        <v>0.6242</v>
+        <v>0.5602</v>
       </c>
       <c r="J199" t="n">
-        <v>9.9872</v>
+        <v>8.963200000000001</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>1.52</v>
       </c>
       <c r="I200" t="n">
-        <v>0.6052999999999999</v>
+        <v>0.5417999999999999</v>
       </c>
       <c r="J200" t="n">
-        <v>9.684799999999999</v>
+        <v>8.668799999999999</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>1.41</v>
       </c>
       <c r="I201" t="n">
-        <v>0.4971</v>
+        <v>0.4373</v>
       </c>
       <c r="J201" t="n">
-        <v>7.9536</v>
+        <v>6.9968</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.7</v>
       </c>
       <c r="I202" t="n">
-        <v>1.3514</v>
+        <v>1.3738</v>
       </c>
       <c r="J202" t="n">
-        <v>32.4336</v>
+        <v>32.9712</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.54</v>
       </c>
       <c r="I203" t="n">
-        <v>1.1427</v>
+        <v>1.1558</v>
       </c>
       <c r="J203" t="n">
-        <v>27.4248</v>
+        <v>27.7392</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.2</v>
       </c>
       <c r="I204" t="n">
-        <v>0.5357</v>
+        <v>0.505</v>
       </c>
       <c r="J204" t="n">
-        <v>12.8568</v>
+        <v>12.12</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>1.07</v>
       </c>
       <c r="I205" t="n">
-        <v>0.2156</v>
+        <v>0.1865</v>
       </c>
       <c r="J205" t="n">
-        <v>5.1744</v>
+        <v>4.476</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.88</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.4453</v>
+        <v>-0.4067</v>
       </c>
       <c r="J206" t="n">
-        <v>-10.6872</v>
+        <v>-9.7608</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>0.98</v>
       </c>
       <c r="I207" t="n">
-        <v>-0.0279</v>
+        <v>-0.0207</v>
       </c>
       <c r="J207" t="n">
-        <v>-0.6696</v>
+        <v>-0.4968</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I208" t="n">
-        <v>-0.0861</v>
+        <v>-0.073</v>
       </c>
       <c r="J208" t="n">
-        <v>-2.0664</v>
+        <v>-1.752</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>0.85</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.1886</v>
+        <v>-0.1706</v>
       </c>
       <c r="J209" t="n">
-        <v>-4.5264</v>
+        <v>-4.0944</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.79</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.2474</v>
+        <v>-0.2286</v>
       </c>
       <c r="J210" t="n">
-        <v>-5.9376</v>
+        <v>-5.4864</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.66</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.3689</v>
+        <v>-0.355</v>
       </c>
       <c r="J211" t="n">
-        <v>-8.8536</v>
+        <v>-8.52</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.3</v>
       </c>
       <c r="I212" t="n">
-        <v>0.8091</v>
+        <v>0.7846</v>
       </c>
       <c r="J212" t="n">
-        <v>24.273</v>
+        <v>23.538</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.05</v>
       </c>
       <c r="I213" t="n">
-        <v>0.2003</v>
+        <v>0.1659</v>
       </c>
       <c r="J213" t="n">
-        <v>6.009</v>
+        <v>4.977</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.93</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.2595</v>
+        <v>-0.221</v>
       </c>
       <c r="J214" t="n">
-        <v>-7.785</v>
+        <v>-6.63</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.88</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.394</v>
+        <v>-0.3512</v>
       </c>
       <c r="J215" t="n">
-        <v>-11.82</v>
+        <v>-10.536</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.84</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.4931</v>
+        <v>-0.4509</v>
       </c>
       <c r="J216" t="n">
-        <v>-14.793</v>
+        <v>-13.527</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.46</v>
       </c>
       <c r="I217" t="n">
-        <v>0.8202</v>
+        <v>0.7672</v>
       </c>
       <c r="J217" t="n">
-        <v>24.606</v>
+        <v>23.016</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.11</v>
       </c>
       <c r="I218" t="n">
-        <v>0.262</v>
+        <v>0.216</v>
       </c>
       <c r="J218" t="n">
-        <v>7.86</v>
+        <v>6.48</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.02</v>
       </c>
       <c r="I219" t="n">
-        <v>0.06759999999999999</v>
+        <v>0.0496</v>
       </c>
       <c r="J219" t="n">
-        <v>2.028</v>
+        <v>1.488</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.99</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.0295</v>
+        <v>-0.021</v>
       </c>
       <c r="J220" t="n">
-        <v>-0.885</v>
+        <v>-0.63</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.73</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.3252</v>
+        <v>-0.3093</v>
       </c>
       <c r="J221" t="n">
-        <v>-9.756</v>
+        <v>-9.279</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.34</v>
       </c>
       <c r="I222" t="n">
-        <v>0.8343</v>
+        <v>0.8121</v>
       </c>
       <c r="J222" t="n">
-        <v>22.5261</v>
+        <v>21.9267</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.29</v>
       </c>
       <c r="I223" t="n">
-        <v>0.7338</v>
+        <v>0.7054</v>
       </c>
       <c r="J223" t="n">
-        <v>19.8126</v>
+        <v>19.0458</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.27</v>
       </c>
       <c r="I224" t="n">
-        <v>0.6928</v>
+        <v>0.6625</v>
       </c>
       <c r="J224" t="n">
-        <v>18.7056</v>
+        <v>17.8875</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>1.15</v>
       </c>
       <c r="I225" t="n">
-        <v>0.4344</v>
+        <v>0.3996</v>
       </c>
       <c r="J225" t="n">
-        <v>11.7288</v>
+        <v>10.7892</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.92</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.3245</v>
+        <v>-0.2841</v>
       </c>
       <c r="J226" t="n">
-        <v>-8.7615</v>
+        <v>-7.6707</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>0.97</v>
       </c>
       <c r="I227" t="n">
-        <v>-0.0526</v>
+        <v>-0.0423</v>
       </c>
       <c r="J227" t="n">
-        <v>-1.4202</v>
+        <v>-1.1421</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>0.96</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.06710000000000001</v>
+        <v>-0.0551</v>
       </c>
       <c r="J228" t="n">
-        <v>-1.8117</v>
+        <v>-1.4877</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.91</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.129</v>
+        <v>-0.1117</v>
       </c>
       <c r="J229" t="n">
-        <v>-3.483</v>
+        <v>-3.0159</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.88</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.1621</v>
+        <v>-0.1431</v>
       </c>
       <c r="J230" t="n">
-        <v>-4.3767</v>
+        <v>-3.8637</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.86</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.1834</v>
+        <v>-0.1638</v>
       </c>
       <c r="J231" t="n">
-        <v>-4.9518</v>
+        <v>-4.4226</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.13</v>
       </c>
       <c r="I232" t="n">
-        <v>0.2571</v>
+        <v>0.2428</v>
       </c>
       <c r="J232" t="n">
-        <v>6.9417</v>
+        <v>6.5556</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>0.97</v>
       </c>
       <c r="I233" t="n">
-        <v>-0.053</v>
+        <v>-0.0426</v>
       </c>
       <c r="J233" t="n">
-        <v>-1.431</v>
+        <v>-1.1502</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>0.88</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.1624</v>
+        <v>-0.1433</v>
       </c>
       <c r="J234" t="n">
-        <v>-4.3848</v>
+        <v>-3.8691</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.88</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.1624</v>
+        <v>-0.1433</v>
       </c>
       <c r="J235" t="n">
-        <v>-4.3848</v>
+        <v>-3.8691</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.74</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.3029</v>
+        <v>-0.2849</v>
       </c>
       <c r="J236" t="n">
-        <v>-8.1783</v>
+        <v>-7.6923</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.67</v>
       </c>
       <c r="I237" t="n">
-        <v>0.7958</v>
+        <v>0.7255</v>
       </c>
       <c r="J237" t="n">
-        <v>21.4866</v>
+        <v>19.5885</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.49</v>
       </c>
       <c r="I238" t="n">
-        <v>0.6162</v>
+        <v>0.5447</v>
       </c>
       <c r="J238" t="n">
-        <v>16.6374</v>
+        <v>14.7069</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>1.11</v>
       </c>
       <c r="I239" t="n">
-        <v>0.185</v>
+        <v>0.1465</v>
       </c>
       <c r="J239" t="n">
-        <v>4.995</v>
+        <v>3.9555</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.98</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.0573</v>
+        <v>-0.0451</v>
       </c>
       <c r="J240" t="n">
-        <v>-1.5471</v>
+        <v>-1.2177</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.71</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.3534</v>
+        <v>-0.3412</v>
       </c>
       <c r="J241" t="n">
-        <v>-9.5418</v>
+        <v>-9.212400000000001</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.3</v>
       </c>
       <c r="I242" t="n">
-        <v>0.7586000000000001</v>
+        <v>0.7308</v>
       </c>
       <c r="J242" t="n">
-        <v>21.2408</v>
+        <v>20.4624</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.23</v>
       </c>
       <c r="I243" t="n">
-        <v>0.6128</v>
+        <v>0.5785</v>
       </c>
       <c r="J243" t="n">
-        <v>17.1584</v>
+        <v>16.198</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.17</v>
       </c>
       <c r="I244" t="n">
-        <v>0.4826</v>
+        <v>0.4465</v>
       </c>
       <c r="J244" t="n">
-        <v>13.5128</v>
+        <v>12.502</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>1.12</v>
       </c>
       <c r="I245" t="n">
-        <v>0.3654</v>
+        <v>0.3305</v>
       </c>
       <c r="J245" t="n">
-        <v>10.2312</v>
+        <v>9.254</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>1.04</v>
       </c>
       <c r="I246" t="n">
-        <v>0.1426</v>
+        <v>0.1186</v>
       </c>
       <c r="J246" t="n">
-        <v>3.9928</v>
+        <v>3.3208</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.09</v>
       </c>
       <c r="I247" t="n">
-        <v>0.2649</v>
+        <v>0.2188</v>
       </c>
       <c r="J247" t="n">
-        <v>7.4172</v>
+        <v>6.1264</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.08</v>
       </c>
       <c r="I248" t="n">
-        <v>0.2438</v>
+        <v>0.1994</v>
       </c>
       <c r="J248" t="n">
-        <v>6.8264</v>
+        <v>5.5832</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>0.79</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.2493</v>
+        <v>-0.2301</v>
       </c>
       <c r="J249" t="n">
-        <v>-6.9804</v>
+        <v>-6.4428</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.76</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.2782</v>
+        <v>-0.2596</v>
       </c>
       <c r="J250" t="n">
-        <v>-7.7896</v>
+        <v>-7.2688</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.6</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.4248</v>
+        <v>-0.4158</v>
       </c>
       <c r="J251" t="n">
-        <v>-11.8944</v>
+        <v>-11.6424</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.53</v>
       </c>
       <c r="I252" t="n">
-        <v>1.1513</v>
+        <v>1.1648</v>
       </c>
       <c r="J252" t="n">
-        <v>31.0851</v>
+        <v>31.4496</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.44</v>
       </c>
       <c r="I253" t="n">
-        <v>1.0231</v>
+        <v>1.024</v>
       </c>
       <c r="J253" t="n">
-        <v>27.6237</v>
+        <v>27.648</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>1.16</v>
       </c>
       <c r="I254" t="n">
-        <v>0.46</v>
+        <v>0.424</v>
       </c>
       <c r="J254" t="n">
-        <v>12.42</v>
+        <v>11.448</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.2631</v>
+        <v>-0.2246</v>
       </c>
       <c r="J255" t="n">
-        <v>-7.1037</v>
+        <v>-6.0642</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.8</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.6209</v>
+        <v>-0.5862000000000001</v>
       </c>
       <c r="J256" t="n">
-        <v>-16.7643</v>
+        <v>-15.8274</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>0.98</v>
       </c>
       <c r="I257" t="n">
-        <v>-0.0296</v>
+        <v>-0.0224</v>
       </c>
       <c r="J257" t="n">
-        <v>-0.7992</v>
+        <v>-0.6048</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>0.91</v>
       </c>
       <c r="I258" t="n">
-        <v>-0.1245</v>
+        <v>-0.1089</v>
       </c>
       <c r="J258" t="n">
-        <v>-3.3615</v>
+        <v>-2.9403</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>0.85</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.1891</v>
+        <v>-0.1708</v>
       </c>
       <c r="J259" t="n">
-        <v>-5.1057</v>
+        <v>-4.6116</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.85</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.1891</v>
+        <v>-0.1708</v>
       </c>
       <c r="J260" t="n">
-        <v>-5.1057</v>
+        <v>-4.6116</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.3429</v>
+        <v>-0.3272</v>
       </c>
       <c r="J261" t="n">
-        <v>-9.2583</v>
+        <v>-8.8344</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.26</v>
       </c>
       <c r="I262" t="n">
-        <v>0.4119</v>
+        <v>0.41</v>
       </c>
       <c r="J262" t="n">
-        <v>14.8284</v>
+        <v>14.76</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.21</v>
       </c>
       <c r="I263" t="n">
-        <v>0.3477</v>
+        <v>0.3393</v>
       </c>
       <c r="J263" t="n">
-        <v>12.5172</v>
+        <v>12.2148</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>1.13</v>
       </c>
       <c r="I264" t="n">
-        <v>0.2381</v>
+        <v>0.223</v>
       </c>
       <c r="J264" t="n">
-        <v>8.5716</v>
+        <v>8.028</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>0.89</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.1608</v>
+        <v>-0.1406</v>
       </c>
       <c r="J265" t="n">
-        <v>-5.7888</v>
+        <v>-5.0616</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.66</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.3866</v>
+        <v>-0.3754</v>
       </c>
       <c r="J266" t="n">
-        <v>-13.9176</v>
+        <v>-13.5144</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.35</v>
       </c>
       <c r="I267" t="n">
-        <v>0.486</v>
+        <v>0.4182</v>
       </c>
       <c r="J267" t="n">
-        <v>17.496</v>
+        <v>15.0552</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>1.27</v>
       </c>
       <c r="I268" t="n">
-        <v>0.3946</v>
+        <v>0.3315</v>
       </c>
       <c r="J268" t="n">
-        <v>14.2056</v>
+        <v>11.934</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>1</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.0051</v>
+        <v>-0.0033</v>
       </c>
       <c r="J269" t="n">
-        <v>-0.1836</v>
+        <v>-0.1188</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.92</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.1302</v>
+        <v>-0.111</v>
       </c>
       <c r="J270" t="n">
-        <v>-4.6872</v>
+        <v>-3.996</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.85</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.2083</v>
+        <v>-0.1878</v>
       </c>
       <c r="J271" t="n">
-        <v>-7.4988</v>
+        <v>-6.7608</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.4</v>
       </c>
       <c r="I272" t="n">
-        <v>0.9498</v>
+        <v>0.9385</v>
       </c>
       <c r="J272" t="n">
-        <v>22.7952</v>
+        <v>22.524</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.35</v>
       </c>
       <c r="I273" t="n">
-        <v>0.8537</v>
+        <v>0.8329</v>
       </c>
       <c r="J273" t="n">
-        <v>20.4888</v>
+        <v>19.9896</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.27</v>
       </c>
       <c r="I274" t="n">
-        <v>0.6925</v>
+        <v>0.6622</v>
       </c>
       <c r="J274" t="n">
-        <v>16.62</v>
+        <v>15.8928</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>1.03</v>
       </c>
       <c r="I275" t="n">
-        <v>0.1048</v>
+        <v>0.0844</v>
       </c>
       <c r="J275" t="n">
-        <v>2.5152</v>
+        <v>2.0256</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.93</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.2964</v>
+        <v>-0.2569</v>
       </c>
       <c r="J276" t="n">
-        <v>-7.1136</v>
+        <v>-6.1656</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.28</v>
       </c>
       <c r="I277" t="n">
-        <v>0.607</v>
+        <v>0.5546</v>
       </c>
       <c r="J277" t="n">
-        <v>14.568</v>
+        <v>13.3104</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>0.83</v>
       </c>
       <c r="I278" t="n">
-        <v>-0.2108</v>
+        <v>-0.1915</v>
       </c>
       <c r="J278" t="n">
-        <v>-5.0592</v>
+        <v>-4.596</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>0.76</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.2794</v>
+        <v>-0.2607</v>
       </c>
       <c r="J279" t="n">
-        <v>-6.7056</v>
+        <v>-6.2568</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.76</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.2794</v>
+        <v>-0.2607</v>
       </c>
       <c r="J280" t="n">
-        <v>-6.7056</v>
+        <v>-6.2568</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.75</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.2889</v>
+        <v>-0.2706</v>
       </c>
       <c r="J281" t="n">
-        <v>-6.9336</v>
+        <v>-6.4944</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.61</v>
       </c>
       <c r="I282" t="n">
-        <v>1.2651</v>
+        <v>1.2846</v>
       </c>
       <c r="J282" t="n">
-        <v>30.3624</v>
+        <v>30.8304</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>1.48</v>
       </c>
       <c r="I283" t="n">
-        <v>1.0869</v>
+        <v>1.0972</v>
       </c>
       <c r="J283" t="n">
-        <v>26.0856</v>
+        <v>26.3328</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>1.06</v>
       </c>
       <c r="I284" t="n">
-        <v>0.2075</v>
+        <v>0.1784</v>
       </c>
       <c r="J284" t="n">
-        <v>4.98</v>
+        <v>4.2816</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>0.86</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.4745</v>
+        <v>-0.4333</v>
       </c>
       <c r="J285" t="n">
-        <v>-11.388</v>
+        <v>-10.3992</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.76</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.7077</v>
+        <v>-0.6782</v>
       </c>
       <c r="J286" t="n">
-        <v>-16.9848</v>
+        <v>-16.2768</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.26</v>
       </c>
       <c r="I287" t="n">
-        <v>0.5623</v>
+        <v>0.5066000000000001</v>
       </c>
       <c r="J287" t="n">
-        <v>13.4952</v>
+        <v>12.1584</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>0.96</v>
       </c>
       <c r="I288" t="n">
-        <v>-0.06610000000000001</v>
+        <v>-0.0544</v>
       </c>
       <c r="J288" t="n">
-        <v>-1.5864</v>
+        <v>-1.3056</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.09279999999999999</v>
+        <v>-0.0785</v>
       </c>
       <c r="J289" t="n">
-        <v>-2.2272</v>
+        <v>-1.884</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.79</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.2534</v>
+        <v>-0.2338</v>
       </c>
       <c r="J290" t="n">
-        <v>-6.0816</v>
+        <v>-5.6112</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.58</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.4465</v>
+        <v>-0.4402</v>
       </c>
       <c r="J291" t="n">
-        <v>-10.716</v>
+        <v>-10.5648</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.65</v>
       </c>
       <c r="I292" t="n">
-        <v>1.2987</v>
+        <v>1.3185</v>
       </c>
       <c r="J292" t="n">
-        <v>32.4675</v>
+        <v>32.9625</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.4</v>
       </c>
       <c r="I293" t="n">
-        <v>0.9426</v>
+        <v>0.931</v>
       </c>
       <c r="J293" t="n">
-        <v>23.565</v>
+        <v>23.275</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>1.13</v>
       </c>
       <c r="I294" t="n">
-        <v>0.3815</v>
+        <v>0.3481</v>
       </c>
       <c r="J294" t="n">
-        <v>9.5375</v>
+        <v>8.702500000000001</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>1.01</v>
       </c>
       <c r="I295" t="n">
-        <v>0.0214</v>
+        <v>0.0115</v>
       </c>
       <c r="J295" t="n">
-        <v>0.535</v>
+        <v>0.2875</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>0.95</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.2422</v>
+        <v>-0.206</v>
       </c>
       <c r="J296" t="n">
-        <v>-6.055</v>
+        <v>-5.15</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>1.01</v>
       </c>
       <c r="I297" t="n">
-        <v>0.0607</v>
+        <v>0.0422</v>
       </c>
       <c r="J297" t="n">
-        <v>1.5175</v>
+        <v>1.055</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>1.01</v>
       </c>
       <c r="I298" t="n">
-        <v>0.0607</v>
+        <v>0.0422</v>
       </c>
       <c r="J298" t="n">
-        <v>1.5175</v>
+        <v>1.055</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>0.91</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.1279</v>
+        <v>-0.1112</v>
       </c>
       <c r="J299" t="n">
-        <v>-3.1975</v>
+        <v>-2.78</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.78</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.2619</v>
+        <v>-0.2426</v>
       </c>
       <c r="J300" t="n">
-        <v>-6.5475</v>
+        <v>-6.065</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.76</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.2812</v>
+        <v>-0.2625</v>
       </c>
       <c r="J301" t="n">
-        <v>-7.03</v>
+        <v>-6.5625</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>1.27</v>
       </c>
       <c r="I302" t="n">
-        <v>0.437</v>
+        <v>0.4391</v>
       </c>
       <c r="J302" t="n">
-        <v>12.673</v>
+        <v>12.7339</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>1.07</v>
       </c>
       <c r="I303" t="n">
-        <v>0.1542</v>
+        <v>0.137</v>
       </c>
       <c r="J303" t="n">
-        <v>4.4718</v>
+        <v>3.973</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>1.03</v>
       </c>
       <c r="I304" t="n">
-        <v>0.08160000000000001</v>
+        <v>0.0674</v>
       </c>
       <c r="J304" t="n">
-        <v>2.3664</v>
+        <v>1.9546</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>0.96</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.0706</v>
+        <v>-0.0571</v>
       </c>
       <c r="J305" t="n">
-        <v>-2.0474</v>
+        <v>-1.6559</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>0.52</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.5038</v>
+        <v>-0.5054999999999999</v>
       </c>
       <c r="J306" t="n">
-        <v>-14.6102</v>
+        <v>-14.6595</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>1.47</v>
       </c>
       <c r="I307" t="n">
-        <v>0.5935</v>
+        <v>0.5224</v>
       </c>
       <c r="J307" t="n">
-        <v>17.2115</v>
+        <v>15.1496</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>1.46</v>
       </c>
       <c r="I308" t="n">
-        <v>0.5832000000000001</v>
+        <v>0.5124</v>
       </c>
       <c r="J308" t="n">
-        <v>16.9128</v>
+        <v>14.8596</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>1.27</v>
       </c>
       <c r="I309" t="n">
-        <v>0.379</v>
+        <v>0.3189</v>
       </c>
       <c r="J309" t="n">
-        <v>10.991</v>
+        <v>9.248100000000001</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>1.13</v>
       </c>
       <c r="I310" t="n">
-        <v>0.2111</v>
+        <v>0.1693</v>
       </c>
       <c r="J310" t="n">
-        <v>6.1219</v>
+        <v>4.9097</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.7</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.3635</v>
+        <v>-0.3522</v>
       </c>
       <c r="J311" t="n">
-        <v>-10.5415</v>
+        <v>-10.2138</v>
       </c>
     </row>
     <row r="312">
@@ -14829,10 +14829,10 @@
         <v>1.56</v>
       </c>
       <c r="I312" t="n">
-        <v>1.2399</v>
+        <v>1.2642</v>
       </c>
       <c r="J312" t="n">
-        <v>49.596</v>
+        <v>50.568</v>
       </c>
     </row>
     <row r="313">
@@ -14869,10 +14869,10 @@
         <v>0.96</v>
       </c>
       <c r="I313" t="n">
-        <v>-0.1722</v>
+        <v>-0.1398</v>
       </c>
       <c r="J313" t="n">
-        <v>-6.888</v>
+        <v>-5.592</v>
       </c>
     </row>
     <row r="314">
@@ -14909,10 +14909,10 @@
         <v>0.92</v>
       </c>
       <c r="I314" t="n">
-        <v>-0.2916</v>
+        <v>-0.251</v>
       </c>
       <c r="J314" t="n">
-        <v>-11.664</v>
+        <v>-10.04</v>
       </c>
     </row>
     <row r="315">
@@ -14949,10 +14949,10 @@
         <v>0.86</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.4484</v>
+        <v>-0.4055</v>
       </c>
       <c r="J315" t="n">
-        <v>-17.936</v>
+        <v>-16.22</v>
       </c>
     </row>
     <row r="316">
@@ -14989,10 +14989,10 @@
         <v>0.8</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.5916</v>
+        <v>-0.5526</v>
       </c>
       <c r="J316" t="n">
-        <v>-23.664</v>
+        <v>-22.104</v>
       </c>
     </row>
     <row r="317">
@@ -15029,10 +15029,10 @@
         <v>1.22</v>
       </c>
       <c r="I317" t="n">
-        <v>0.4466</v>
+        <v>0.3895</v>
       </c>
       <c r="J317" t="n">
-        <v>17.864</v>
+        <v>15.58</v>
       </c>
     </row>
     <row r="318">
@@ -15069,10 +15069,10 @@
         <v>1.15</v>
       </c>
       <c r="I318" t="n">
-        <v>0.3291</v>
+        <v>0.2787</v>
       </c>
       <c r="J318" t="n">
-        <v>13.164</v>
+        <v>11.148</v>
       </c>
     </row>
     <row r="319">
@@ -15109,10 +15109,10 @@
         <v>1.14</v>
       </c>
       <c r="I319" t="n">
-        <v>0.3116</v>
+        <v>0.2625</v>
       </c>
       <c r="J319" t="n">
-        <v>12.464</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="320">
@@ -15149,10 +15149,10 @@
         <v>1.11</v>
       </c>
       <c r="I320" t="n">
-        <v>0.2577</v>
+        <v>0.2136</v>
       </c>
       <c r="J320" t="n">
-        <v>10.308</v>
+        <v>8.544</v>
       </c>
     </row>
     <row r="321">
@@ -15189,10 +15189,10 @@
         <v>0.89</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.1669</v>
+        <v>-0.1467</v>
       </c>
       <c r="J321" t="n">
-        <v>-6.676</v>
+        <v>-5.868</v>
       </c>
     </row>
     <row r="322">
@@ -15229,10 +15229,10 @@
         <v>2.51</v>
       </c>
       <c r="I322" t="n">
-        <v>1.9372</v>
+        <v>1.9818</v>
       </c>
       <c r="J322" t="n">
-        <v>36.8068</v>
+        <v>37.6542</v>
       </c>
     </row>
     <row r="323">
@@ -15269,10 +15269,10 @@
         <v>1.43</v>
       </c>
       <c r="I323" t="n">
-        <v>0.9635</v>
+        <v>0.9646</v>
       </c>
       <c r="J323" t="n">
-        <v>18.3065</v>
+        <v>18.3274</v>
       </c>
     </row>
     <row r="324">
@@ -15309,10 +15309,10 @@
         <v>1.32</v>
       </c>
       <c r="I324" t="n">
-        <v>0.7596000000000001</v>
+        <v>0.7442</v>
       </c>
       <c r="J324" t="n">
-        <v>14.4324</v>
+        <v>14.1398</v>
       </c>
     </row>
     <row r="325">
@@ -15349,10 +15349,10 @@
         <v>1.2</v>
       </c>
       <c r="I325" t="n">
-        <v>0.5096000000000001</v>
+        <v>0.481</v>
       </c>
       <c r="J325" t="n">
-        <v>9.682399999999999</v>
+        <v>9.138999999999999</v>
       </c>
     </row>
     <row r="326">
@@ -15389,10 +15389,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.6392</v>
+        <v>-0.6137</v>
       </c>
       <c r="J326" t="n">
-        <v>-12.1448</v>
+        <v>-11.6603</v>
       </c>
     </row>
     <row r="327">
@@ -15429,10 +15429,10 @@
         <v>1.34</v>
       </c>
       <c r="I327" t="n">
-        <v>0.7705</v>
+        <v>0.7457</v>
       </c>
       <c r="J327" t="n">
-        <v>14.6395</v>
+        <v>14.1683</v>
       </c>
     </row>
     <row r="328">
@@ -15469,10 +15469,10 @@
         <v>0.75</v>
       </c>
       <c r="I328" t="n">
-        <v>-0.2771</v>
+        <v>-0.2611</v>
       </c>
       <c r="J328" t="n">
-        <v>-5.2649</v>
+        <v>-4.9609</v>
       </c>
     </row>
     <row r="329">
@@ -15509,10 +15509,10 @@
         <v>0.67</v>
       </c>
       <c r="I329" t="n">
-        <v>-0.3497</v>
+        <v>-0.3353</v>
       </c>
       <c r="J329" t="n">
-        <v>-6.6443</v>
+        <v>-6.3707</v>
       </c>
     </row>
     <row r="330">
@@ -15549,10 +15549,10 @@
         <v>0.61</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.4036</v>
+        <v>-0.3925</v>
       </c>
       <c r="J330" t="n">
-        <v>-7.6684</v>
+        <v>-7.4575</v>
       </c>
     </row>
     <row r="331">
@@ -15589,10 +15589,10 @@
         <v>0.4</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.5868</v>
+        <v>-0.5981</v>
       </c>
       <c r="J331" t="n">
-        <v>-11.1492</v>
+        <v>-11.3639</v>
       </c>
     </row>
   </sheetData>
